--- a/data/ANIM.MI.xlsx
+++ b/data/ANIM.MI.xlsx
@@ -62886,6 +62886,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2719">
+      <c r="A2719" s="1" t="n">
+        <v>46279.2916666667</v>
+      </c>
+      <c r="B2719" t="n">
+        <v>140776</v>
+      </c>
+      <c r="C2719" t="n">
+        <v>6.98000001907349</v>
+      </c>
+      <c r="D2719" t="n">
+        <v>6.86999988555908</v>
+      </c>
+      <c r="E2719" t="n">
+        <v>6.88000011444092</v>
+      </c>
+      <c r="F2719" t="n">
+        <v>6.96999979019165</v>
+      </c>
+      <c r="G2719" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/ANIM.MI.xlsx
+++ b/data/ANIM.MI.xlsx
@@ -62909,6 +62909,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2720">
+      <c r="A2720" s="1" t="n">
+        <v>46280.2916666667</v>
+      </c>
+      <c r="B2720" t="n">
+        <v>248778</v>
+      </c>
+      <c r="C2720" t="n">
+        <v>6.94000005722046</v>
+      </c>
+      <c r="D2720" t="n">
+        <v>6.84000015258789</v>
+      </c>
+      <c r="E2720" t="n">
+        <v>6.86999988555908</v>
+      </c>
+      <c r="F2720" t="n">
+        <v>6.92999982833862</v>
+      </c>
+      <c r="G2720" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/ANIM.MI.xlsx
+++ b/data/ANIM.MI.xlsx
@@ -62932,6 +62932,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2721">
+      <c r="A2721" s="1" t="n">
+        <v>46281.2916666667</v>
+      </c>
+      <c r="B2721" t="n">
+        <v>218326</v>
+      </c>
+      <c r="C2721" t="n">
+        <v>7</v>
+      </c>
+      <c r="D2721" t="n">
+        <v>6.92000007629395</v>
+      </c>
+      <c r="E2721" t="n">
+        <v>6.96000003814697</v>
+      </c>
+      <c r="F2721" t="n">
+        <v>7</v>
+      </c>
+      <c r="G2721" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/ANIM.MI.xlsx
+++ b/data/ANIM.MI.xlsx
@@ -62955,6 +62955,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2722">
+      <c r="A2722" s="1" t="n">
+        <v>46282.2916666667</v>
+      </c>
+      <c r="B2722" t="n">
+        <v>193375</v>
+      </c>
+      <c r="C2722" t="n">
+        <v>7.09000015258789</v>
+      </c>
+      <c r="D2722" t="n">
+        <v>6.94999980926514</v>
+      </c>
+      <c r="E2722" t="n">
+        <v>6.94999980926514</v>
+      </c>
+      <c r="F2722" t="n">
+        <v>7.07999992370605</v>
+      </c>
+      <c r="G2722" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/ANIM.MI.xlsx
+++ b/data/ANIM.MI.xlsx
@@ -62796,22 +62796,22 @@
     </row>
     <row r="2715">
       <c r="A2715" s="1" t="n">
-        <v>46273.2916666667</v>
+        <v>46272.2916666667</v>
       </c>
       <c r="B2715" t="n">
-        <v>189002</v>
+        <v>88212</v>
       </c>
       <c r="C2715" t="n">
-        <v>6.96999979019165</v>
+        <v>6.98000001907349</v>
       </c>
       <c r="D2715" t="n">
-        <v>6.84999990463257</v>
+        <v>6.92000007629395</v>
       </c>
       <c r="E2715" t="n">
-        <v>6.96999979019165</v>
+        <v>6.94999980926514</v>
       </c>
       <c r="F2715" t="n">
-        <v>6.86999988555908</v>
+        <v>6.92999982833862</v>
       </c>
       <c r="G2715" t="s">
         <v>7</v>
@@ -62819,22 +62819,22 @@
     </row>
     <row r="2716">
       <c r="A2716" s="1" t="n">
-        <v>46274.2916666667</v>
+        <v>46273.2916666667</v>
       </c>
       <c r="B2716" t="n">
-        <v>161967</v>
+        <v>189002</v>
       </c>
       <c r="C2716" t="n">
-        <v>6.90999984741211</v>
+        <v>6.96999979019165</v>
       </c>
       <c r="D2716" t="n">
-        <v>6.80000019073486</v>
+        <v>6.84999990463257</v>
       </c>
       <c r="E2716" t="n">
-        <v>6.90999984741211</v>
+        <v>6.96999979019165</v>
       </c>
       <c r="F2716" t="n">
-        <v>6.8600001335144</v>
+        <v>6.86999988555908</v>
       </c>
       <c r="G2716" t="s">
         <v>7</v>
@@ -62842,22 +62842,22 @@
     </row>
     <row r="2717">
       <c r="A2717" s="1" t="n">
-        <v>46275.2916666667</v>
+        <v>46274.2916666667</v>
       </c>
       <c r="B2717" t="n">
-        <v>171407</v>
+        <v>161967</v>
       </c>
       <c r="C2717" t="n">
-        <v>6.92999982833862</v>
+        <v>6.90999984741211</v>
       </c>
       <c r="D2717" t="n">
-        <v>6.76999998092651</v>
+        <v>6.80000019073486</v>
       </c>
       <c r="E2717" t="n">
-        <v>6.76999998092651</v>
+        <v>6.90999984741211</v>
       </c>
       <c r="F2717" t="n">
-        <v>6.92999982833862</v>
+        <v>6.8600001335144</v>
       </c>
       <c r="G2717" t="s">
         <v>7</v>
@@ -62865,22 +62865,22 @@
     </row>
     <row r="2718">
       <c r="A2718" s="1" t="n">
-        <v>46276.2916666667</v>
+        <v>46275.2916666667</v>
       </c>
       <c r="B2718" t="n">
-        <v>139981</v>
+        <v>171407</v>
       </c>
       <c r="C2718" t="n">
-        <v>6.98999977111816</v>
+        <v>6.92999982833862</v>
       </c>
       <c r="D2718" t="n">
-        <v>6.92000007629395</v>
+        <v>6.76999998092651</v>
       </c>
       <c r="E2718" t="n">
-        <v>6.96999979019165</v>
+        <v>6.76999998092651</v>
       </c>
       <c r="F2718" t="n">
-        <v>6.98000001907349</v>
+        <v>6.92999982833862</v>
       </c>
       <c r="G2718" t="s">
         <v>7</v>
@@ -62888,22 +62888,22 @@
     </row>
     <row r="2719">
       <c r="A2719" s="1" t="n">
-        <v>46279.2916666667</v>
+        <v>46276.2916666667</v>
       </c>
       <c r="B2719" t="n">
-        <v>140776</v>
+        <v>139981</v>
       </c>
       <c r="C2719" t="n">
+        <v>6.98999977111816</v>
+      </c>
+      <c r="D2719" t="n">
+        <v>6.92000007629395</v>
+      </c>
+      <c r="E2719" t="n">
+        <v>6.96999979019165</v>
+      </c>
+      <c r="F2719" t="n">
         <v>6.98000001907349</v>
-      </c>
-      <c r="D2719" t="n">
-        <v>6.86999988555908</v>
-      </c>
-      <c r="E2719" t="n">
-        <v>6.88000011444092</v>
-      </c>
-      <c r="F2719" t="n">
-        <v>6.96999979019165</v>
       </c>
       <c r="G2719" t="s">
         <v>7</v>
@@ -62911,22 +62911,22 @@
     </row>
     <row r="2720">
       <c r="A2720" s="1" t="n">
-        <v>46280.2916666667</v>
+        <v>46279.2916666667</v>
       </c>
       <c r="B2720" t="n">
-        <v>248778</v>
+        <v>140776</v>
       </c>
       <c r="C2720" t="n">
-        <v>6.94000005722046</v>
+        <v>6.98000001907349</v>
       </c>
       <c r="D2720" t="n">
-        <v>6.84000015258789</v>
+        <v>6.86999988555908</v>
       </c>
       <c r="E2720" t="n">
-        <v>6.86999988555908</v>
+        <v>6.88000011444092</v>
       </c>
       <c r="F2720" t="n">
-        <v>6.92999982833862</v>
+        <v>6.96999979019165</v>
       </c>
       <c r="G2720" t="s">
         <v>7</v>
@@ -62934,22 +62934,22 @@
     </row>
     <row r="2721">
       <c r="A2721" s="1" t="n">
-        <v>46281.2916666667</v>
+        <v>46280.2916666667</v>
       </c>
       <c r="B2721" t="n">
-        <v>218326</v>
+        <v>248778</v>
       </c>
       <c r="C2721" t="n">
-        <v>7</v>
+        <v>6.94000005722046</v>
       </c>
       <c r="D2721" t="n">
-        <v>6.92000007629395</v>
+        <v>6.84000015258789</v>
       </c>
       <c r="E2721" t="n">
-        <v>6.96000003814697</v>
+        <v>6.86999988555908</v>
       </c>
       <c r="F2721" t="n">
-        <v>7</v>
+        <v>6.92999982833862</v>
       </c>
       <c r="G2721" t="s">
         <v>7</v>
@@ -62957,24 +62957,47 @@
     </row>
     <row r="2722">
       <c r="A2722" s="1" t="n">
-        <v>46282.2916666667</v>
+        <v>46281.2916666667</v>
       </c>
       <c r="B2722" t="n">
-        <v>193375</v>
+        <v>218326</v>
       </c>
       <c r="C2722" t="n">
-        <v>7.09000015258789</v>
+        <v>7</v>
       </c>
       <c r="D2722" t="n">
-        <v>6.94999980926514</v>
+        <v>6.92000007629395</v>
       </c>
       <c r="E2722" t="n">
-        <v>6.94999980926514</v>
+        <v>6.96000003814697</v>
       </c>
       <c r="F2722" t="n">
+        <v>7</v>
+      </c>
+      <c r="G2722" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2723">
+      <c r="A2723" s="1" t="n">
+        <v>46283.2916666667</v>
+      </c>
+      <c r="B2723" t="n">
+        <v>338842</v>
+      </c>
+      <c r="C2723" t="n">
         <v>7.07999992370605</v>
       </c>
-      <c r="G2722" t="s">
+      <c r="D2723" t="n">
+        <v>6.94000005722046</v>
+      </c>
+      <c r="E2723" t="n">
+        <v>6.94000005722046</v>
+      </c>
+      <c r="F2723" t="n">
+        <v>7.01999998092651</v>
+      </c>
+      <c r="G2723" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/ANIM.MI.xlsx
+++ b/data/ANIM.MI.xlsx
@@ -421,7 +421,7 @@
         <v>7.32920980453491</v>
       </c>
       <c r="G2" t="n">
-        <v>3.94384074211121</v>
+        <v>3.94384050369263</v>
       </c>
       <c r="H2" t="s">
         <v>8</v>
@@ -525,7 +525,7 @@
         <v>6.8222770690918</v>
       </c>
       <c r="G6" t="n">
-        <v>3.67106008529663</v>
+        <v>3.67106032371521</v>
       </c>
       <c r="H6" t="s">
         <v>8</v>
@@ -551,7 +551,7 @@
         <v>6.80332612991333</v>
       </c>
       <c r="G7" t="n">
-        <v>3.66086292266846</v>
+        <v>3.66086268424988</v>
       </c>
       <c r="H7" t="s">
         <v>8</v>
@@ -603,7 +603,7 @@
         <v>6.78437614440918</v>
       </c>
       <c r="G9" t="n">
-        <v>3.6506655216217</v>
+        <v>3.65066576004028</v>
       </c>
       <c r="H9" t="s">
         <v>8</v>
@@ -681,7 +681,7 @@
         <v>6.34850788116455</v>
       </c>
       <c r="G12" t="n">
-        <v>3.41612529754639</v>
+        <v>3.41612553596497</v>
       </c>
       <c r="H12" t="s">
         <v>8</v>
@@ -733,7 +733,7 @@
         <v>5.87473917007446</v>
       </c>
       <c r="G14" t="n">
-        <v>3.16119074821472</v>
+        <v>3.16119122505188</v>
       </c>
       <c r="H14" t="s">
         <v>8</v>
@@ -837,7 +837,7 @@
         <v>6.55696582794189</v>
       </c>
       <c r="G18" t="n">
-        <v>3.52829670906067</v>
+        <v>3.52829647064209</v>
       </c>
       <c r="H18" t="s">
         <v>8</v>
@@ -863,7 +863,7 @@
         <v>6.70383501052856</v>
       </c>
       <c r="G19" t="n">
-        <v>3.60732674598694</v>
+        <v>3.6073272228241</v>
       </c>
       <c r="H19" t="s">
         <v>8</v>
@@ -889,7 +889,7 @@
         <v>6.34377002716064</v>
       </c>
       <c r="G20" t="n">
-        <v>3.41357684135437</v>
+        <v>3.41357612609863</v>
       </c>
       <c r="H20" t="s">
         <v>8</v>
@@ -915,7 +915,7 @@
         <v>6.39588499069214</v>
       </c>
       <c r="G21" t="n">
-        <v>3.44161939620972</v>
+        <v>3.44161915779114</v>
       </c>
       <c r="H21" t="s">
         <v>8</v>
@@ -941,7 +941,7 @@
         <v>6.2821798324585</v>
       </c>
       <c r="G22" t="n">
-        <v>3.3804349899292</v>
+        <v>3.38043475151062</v>
       </c>
       <c r="H22" t="s">
         <v>8</v>
@@ -967,7 +967,7 @@
         <v>6.17795085906982</v>
       </c>
       <c r="G23" t="n">
-        <v>3.32434868812561</v>
+        <v>3.32434821128845</v>
       </c>
       <c r="H23" t="s">
         <v>8</v>
@@ -993,7 +993,7 @@
         <v>5.79419803619385</v>
       </c>
       <c r="G24" t="n">
-        <v>3.11785244941711</v>
+        <v>3.11785173416138</v>
       </c>
       <c r="H24" t="s">
         <v>8</v>
@@ -1019,7 +1019,7 @@
         <v>5.9552788734436</v>
       </c>
       <c r="G25" t="n">
-        <v>3.20453000068665</v>
+        <v>3.20452952384949</v>
       </c>
       <c r="H25" t="s">
         <v>8</v>
@@ -1149,7 +1149,7 @@
         <v>5.14987182617188</v>
       </c>
       <c r="G30" t="n">
-        <v>2.77114057540894</v>
+        <v>2.77114033699036</v>
       </c>
       <c r="H30" t="s">
         <v>8</v>
@@ -1201,7 +1201,7 @@
         <v>5.59521484375</v>
       </c>
       <c r="G32" t="n">
-        <v>3.01077938079834</v>
+        <v>3.01077914237976</v>
       </c>
       <c r="H32" t="s">
         <v>8</v>
@@ -1279,7 +1279,7 @@
         <v>5.83683681488037</v>
       </c>
       <c r="G35" t="n">
-        <v>3.14079523086548</v>
+        <v>3.14079594612122</v>
       </c>
       <c r="H35" t="s">
         <v>8</v>
@@ -1305,7 +1305,7 @@
         <v>5.71365690231323</v>
       </c>
       <c r="G36" t="n">
-        <v>3.07451248168945</v>
+        <v>3.07451295852661</v>
       </c>
       <c r="H36" t="s">
         <v>8</v>
@@ -1331,7 +1331,7 @@
         <v>5.84631299972534</v>
       </c>
       <c r="G37" t="n">
-        <v>3.14589476585388</v>
+        <v>3.1458945274353</v>
       </c>
       <c r="H37" t="s">
         <v>8</v>
@@ -1357,7 +1357,7 @@
         <v>5.63785409927368</v>
       </c>
       <c r="G38" t="n">
-        <v>3.0337233543396</v>
+        <v>3.03372359275818</v>
       </c>
       <c r="H38" t="s">
         <v>8</v>
@@ -1383,7 +1383,7 @@
         <v>5.37254285812378</v>
       </c>
       <c r="G39" t="n">
-        <v>2.89095973968506</v>
+        <v>2.89096021652222</v>
       </c>
       <c r="H39" t="s">
         <v>8</v>
@@ -1461,7 +1461,7 @@
         <v>5.28252696990967</v>
       </c>
       <c r="G42" t="n">
-        <v>2.84252214431763</v>
+        <v>2.84252238273621</v>
       </c>
       <c r="H42" t="s">
         <v>8</v>
@@ -1487,7 +1487,7 @@
         <v>5.44834613800049</v>
       </c>
       <c r="G43" t="n">
-        <v>2.93174958229065</v>
+        <v>2.93174910545349</v>
       </c>
       <c r="H43" t="s">
         <v>8</v>
@@ -1513,7 +1513,7 @@
         <v>5.69944381713867</v>
       </c>
       <c r="G44" t="n">
-        <v>3.06686472892761</v>
+        <v>3.06686496734619</v>
       </c>
       <c r="H44" t="s">
         <v>8</v>
@@ -1565,7 +1565,7 @@
         <v>5.93632888793945</v>
       </c>
       <c r="G46" t="n">
-        <v>3.19433259963989</v>
+        <v>3.19433236122131</v>
       </c>
       <c r="H46" t="s">
         <v>8</v>
@@ -1617,7 +1617,7 @@
         <v>5.66627979278564</v>
       </c>
       <c r="G48" t="n">
-        <v>3.04901933670044</v>
+        <v>3.04901957511902</v>
       </c>
       <c r="H48" t="s">
         <v>8</v>
@@ -1643,7 +1643,7 @@
         <v>5.56205081939697</v>
       </c>
       <c r="G49" t="n">
-        <v>2.99293375015259</v>
+        <v>2.99293398857117</v>
       </c>
       <c r="H49" t="s">
         <v>8</v>
@@ -1721,7 +1721,7 @@
         <v>6.17321300506592</v>
       </c>
       <c r="G52" t="n">
-        <v>3.32179927825928</v>
+        <v>3.32179975509644</v>
       </c>
       <c r="H52" t="s">
         <v>8</v>
@@ -1799,7 +1799,7 @@
         <v>5.97896814346313</v>
       </c>
       <c r="G55" t="n">
-        <v>3.21727633476257</v>
+        <v>3.21727681159973</v>
       </c>
       <c r="H55" t="s">
         <v>8</v>
@@ -1825,7 +1825,7 @@
         <v>6.19690179824829</v>
       </c>
       <c r="G56" t="n">
-        <v>3.33454656600952</v>
+        <v>3.33454632759094</v>
       </c>
       <c r="H56" t="s">
         <v>8</v>
@@ -1851,7 +1851,7 @@
         <v>6.14952516555786</v>
       </c>
       <c r="G57" t="n">
-        <v>3.30905318260193</v>
+        <v>3.30905294418335</v>
       </c>
       <c r="H57" t="s">
         <v>8</v>
@@ -1877,7 +1877,7 @@
         <v>6.23480319976807</v>
       </c>
       <c r="G58" t="n">
-        <v>3.35494065284729</v>
+        <v>3.35494112968445</v>
       </c>
       <c r="H58" t="s">
         <v>8</v>
@@ -1903,7 +1903,7 @@
         <v>6.06898403167725</v>
       </c>
       <c r="G59" t="n">
-        <v>3.26571393013</v>
+        <v>3.26571345329285</v>
       </c>
       <c r="H59" t="s">
         <v>8</v>
@@ -1955,7 +1955,7 @@
         <v>5.8178858757019</v>
       </c>
       <c r="G61" t="n">
-        <v>3.13059878349304</v>
+        <v>3.13059854507446</v>
       </c>
       <c r="H61" t="s">
         <v>8</v>
@@ -2007,7 +2007,7 @@
         <v>6.09267282485962</v>
       </c>
       <c r="G63" t="n">
-        <v>3.27846121788025</v>
+        <v>3.27846050262451</v>
       </c>
       <c r="H63" t="s">
         <v>8</v>
@@ -2033,7 +2033,7 @@
         <v>6.23480319976807</v>
       </c>
       <c r="G64" t="n">
-        <v>3.35494065284729</v>
+        <v>3.35494112968445</v>
       </c>
       <c r="H64" t="s">
         <v>8</v>
@@ -2085,7 +2085,7 @@
         <v>5.74682092666626</v>
       </c>
       <c r="G66" t="n">
-        <v>3.09235811233521</v>
+        <v>3.09235858917236</v>
       </c>
       <c r="H66" t="s">
         <v>8</v>
@@ -2111,7 +2111,7 @@
         <v>5.64732885360718</v>
       </c>
       <c r="G67" t="n">
-        <v>3.03882193565369</v>
+        <v>3.03882241249084</v>
       </c>
       <c r="H67" t="s">
         <v>8</v>
@@ -2137,7 +2137,7 @@
         <v>5.33464193344116</v>
       </c>
       <c r="G68" t="n">
-        <v>2.87056565284729</v>
+        <v>2.87056517601013</v>
       </c>
       <c r="H68" t="s">
         <v>8</v>
@@ -2163,7 +2163,7 @@
         <v>5.58573913574219</v>
       </c>
       <c r="G69" t="n">
-        <v>3.00568008422852</v>
+        <v>3.00568056106567</v>
       </c>
       <c r="H69" t="s">
         <v>8</v>
@@ -2189,7 +2189,7 @@
         <v>5.76577186584473</v>
       </c>
       <c r="G70" t="n">
-        <v>3.10255599021912</v>
+        <v>3.10255575180054</v>
       </c>
       <c r="H70" t="s">
         <v>8</v>
@@ -2215,7 +2215,7 @@
         <v>5.56205081939697</v>
       </c>
       <c r="G71" t="n">
-        <v>2.99293375015259</v>
+        <v>2.99293398857117</v>
       </c>
       <c r="H71" t="s">
         <v>8</v>
@@ -2267,7 +2267,7 @@
         <v>5.72786998748779</v>
       </c>
       <c r="G73" t="n">
-        <v>3.08216094970703</v>
+        <v>3.08216047286987</v>
       </c>
       <c r="H73" t="s">
         <v>8</v>
@@ -2319,7 +2319,7 @@
         <v>5.91264009475708</v>
       </c>
       <c r="G75" t="n">
-        <v>3.18158555030823</v>
+        <v>3.18158531188965</v>
       </c>
       <c r="H75" t="s">
         <v>8</v>
@@ -2345,7 +2345,7 @@
         <v>5.89842700958252</v>
       </c>
       <c r="G76" t="n">
-        <v>3.17393732070923</v>
+        <v>3.17393779754639</v>
       </c>
       <c r="H76" t="s">
         <v>8</v>
@@ -2371,7 +2371,7 @@
         <v>5.88421392440796</v>
       </c>
       <c r="G77" t="n">
-        <v>3.16628932952881</v>
+        <v>3.16628909111023</v>
       </c>
       <c r="H77" t="s">
         <v>8</v>
@@ -2449,7 +2449,7 @@
         <v>5.84631299972534</v>
       </c>
       <c r="G80" t="n">
-        <v>3.14589476585388</v>
+        <v>3.1458945274353</v>
       </c>
       <c r="H80" t="s">
         <v>8</v>
@@ -2475,7 +2475,7 @@
         <v>5.97422981262207</v>
       </c>
       <c r="G81" t="n">
-        <v>3.21472692489624</v>
+        <v>3.21472668647766</v>
       </c>
       <c r="H81" t="s">
         <v>8</v>
@@ -2501,7 +2501,7 @@
         <v>5.95054197311401</v>
       </c>
       <c r="G82" t="n">
-        <v>3.20198059082031</v>
+        <v>3.20198011398315</v>
       </c>
       <c r="H82" t="s">
         <v>8</v>
@@ -2527,7 +2527,7 @@
         <v>6.03582000732422</v>
       </c>
       <c r="G83" t="n">
-        <v>3.24786829948425</v>
+        <v>3.24786853790283</v>
       </c>
       <c r="H83" t="s">
         <v>8</v>
@@ -2579,7 +2579,7 @@
         <v>5.82262420654297</v>
       </c>
       <c r="G85" t="n">
-        <v>3.13314819335938</v>
+        <v>3.13314843177795</v>
       </c>
       <c r="H85" t="s">
         <v>8</v>
@@ -2631,7 +2631,7 @@
         <v>5.64259195327759</v>
       </c>
       <c r="G87" t="n">
-        <v>3.03627347946167</v>
+        <v>3.03627276420593</v>
       </c>
       <c r="H87" t="s">
         <v>8</v>
@@ -2657,7 +2657,7 @@
         <v>5.4436092376709</v>
       </c>
       <c r="G88" t="n">
-        <v>2.9292004108429</v>
+        <v>2.92920088768005</v>
       </c>
       <c r="H88" t="s">
         <v>8</v>
@@ -2683,7 +2683,7 @@
         <v>5.4578218460083</v>
       </c>
       <c r="G89" t="n">
-        <v>2.93684792518616</v>
+        <v>2.93684840202332</v>
       </c>
       <c r="H89" t="s">
         <v>8</v>
@@ -2709,7 +2709,7 @@
         <v>5.21146202087402</v>
       </c>
       <c r="G90" t="n">
-        <v>2.80428242683411</v>
+        <v>2.80428218841553</v>
       </c>
       <c r="H90" t="s">
         <v>8</v>
@@ -2735,7 +2735,7 @@
         <v>5.08828210830688</v>
       </c>
       <c r="G91" t="n">
-        <v>2.73799920082092</v>
+        <v>2.73799896240234</v>
       </c>
       <c r="H91" t="s">
         <v>8</v>
@@ -2787,7 +2787,7 @@
         <v>5.05985593795776</v>
       </c>
       <c r="G93" t="n">
-        <v>2.7227029800415</v>
+        <v>2.72270321846008</v>
       </c>
       <c r="H93" t="s">
         <v>8</v>
@@ -2813,7 +2813,7 @@
         <v>5.29674005508423</v>
       </c>
       <c r="G94" t="n">
-        <v>2.85017061233521</v>
+        <v>2.85017013549805</v>
       </c>
       <c r="H94" t="s">
         <v>8</v>
@@ -2969,7 +2969,7 @@
         <v>4.88456106185913</v>
       </c>
       <c r="G100" t="n">
-        <v>2.75940322875977</v>
+        <v>2.75940346717834</v>
       </c>
       <c r="H100" t="s">
         <v>8</v>
@@ -2995,7 +2995,7 @@
         <v>5.03616714477539</v>
       </c>
       <c r="G101" t="n">
-        <v>2.84504914283752</v>
+        <v>2.8450493812561</v>
       </c>
       <c r="H101" t="s">
         <v>8</v>
@@ -3021,7 +3021,7 @@
         <v>5.3204288482666</v>
       </c>
       <c r="G102" t="n">
-        <v>3.00563549995422</v>
+        <v>3.00563502311707</v>
       </c>
       <c r="H102" t="s">
         <v>8</v>
@@ -3047,7 +3047,7 @@
         <v>5.32990407943726</v>
       </c>
       <c r="G103" t="n">
-        <v>3.01098775863647</v>
+        <v>3.01098799705505</v>
       </c>
       <c r="H103" t="s">
         <v>8</v>
@@ -3073,7 +3073,7 @@
         <v>5.32990407943726</v>
       </c>
       <c r="G104" t="n">
-        <v>3.01098775863647</v>
+        <v>3.01098799705505</v>
       </c>
       <c r="H104" t="s">
         <v>8</v>
@@ -3099,7 +3099,7 @@
         <v>5.42465782165527</v>
       </c>
       <c r="G105" t="n">
-        <v>3.0645170211792</v>
+        <v>3.06451654434204</v>
       </c>
       <c r="H105" t="s">
         <v>8</v>
@@ -3125,7 +3125,7 @@
         <v>5.22567510604858</v>
       </c>
       <c r="G106" t="n">
-        <v>2.95210599899292</v>
+        <v>2.95210671424866</v>
       </c>
       <c r="H106" t="s">
         <v>8</v>
@@ -3151,7 +3151,7 @@
         <v>5.19251108169556</v>
       </c>
       <c r="G107" t="n">
-        <v>2.9333713054657</v>
+        <v>2.93337154388428</v>
       </c>
       <c r="H107" t="s">
         <v>8</v>
@@ -3177,7 +3177,7 @@
         <v>4.99826622009277</v>
       </c>
       <c r="G108" t="n">
-        <v>2.82363796234131</v>
+        <v>2.82363820075989</v>
       </c>
       <c r="H108" t="s">
         <v>8</v>
@@ -3203,7 +3203,7 @@
         <v>4.89877414703369</v>
       </c>
       <c r="G109" t="n">
-        <v>2.76743292808533</v>
+        <v>2.76743268966675</v>
       </c>
       <c r="H109" t="s">
         <v>8</v>
@@ -3229,7 +3229,7 @@
         <v>4.87034797668457</v>
       </c>
       <c r="G110" t="n">
-        <v>2.75137376785278</v>
+        <v>2.75137400627136</v>
       </c>
       <c r="H110" t="s">
         <v>8</v>
@@ -3255,7 +3255,7 @@
         <v>4.96983909606934</v>
       </c>
       <c r="G111" t="n">
-        <v>2.80757904052734</v>
+        <v>2.80757880210876</v>
       </c>
       <c r="H111" t="s">
         <v>8</v>
@@ -3281,7 +3281,7 @@
         <v>4.93193817138672</v>
       </c>
       <c r="G112" t="n">
-        <v>2.78616786003113</v>
+        <v>2.78616738319397</v>
       </c>
       <c r="H112" t="s">
         <v>8</v>
@@ -3307,7 +3307,7 @@
         <v>4.8608717918396</v>
       </c>
       <c r="G113" t="n">
-        <v>2.74602055549622</v>
+        <v>2.74602079391479</v>
       </c>
       <c r="H113" t="s">
         <v>8</v>
@@ -3333,7 +3333,7 @@
         <v>4.63346290588379</v>
       </c>
       <c r="G114" t="n">
-        <v>2.61755180358887</v>
+        <v>2.61755228042603</v>
       </c>
       <c r="H114" t="s">
         <v>8</v>
@@ -3359,7 +3359,7 @@
         <v>4.59745693206787</v>
       </c>
       <c r="G115" t="n">
-        <v>2.59721159934998</v>
+        <v>2.5972113609314</v>
       </c>
       <c r="H115" t="s">
         <v>8</v>
@@ -3411,7 +3411,7 @@
         <v>4.29803419113159</v>
       </c>
       <c r="G117" t="n">
-        <v>2.42806053161621</v>
+        <v>2.42806029319763</v>
       </c>
       <c r="H117" t="s">
         <v>8</v>
@@ -3437,7 +3437,7 @@
         <v>4.18811988830566</v>
       </c>
       <c r="G118" t="n">
-        <v>2.36596727371216</v>
+        <v>2.36596751213074</v>
       </c>
       <c r="H118" t="s">
         <v>8</v>
@@ -3463,7 +3463,7 @@
         <v>4.4439549446106</v>
       </c>
       <c r="G119" t="n">
-        <v>2.51049447059631</v>
+        <v>2.51049423217773</v>
       </c>
       <c r="H119" t="s">
         <v>8</v>
@@ -3489,7 +3489,7 @@
         <v>4.52544403076172</v>
       </c>
       <c r="G120" t="n">
-        <v>2.55652952194214</v>
+        <v>2.55652928352356</v>
       </c>
       <c r="H120" t="s">
         <v>8</v>
@@ -3515,7 +3515,7 @@
         <v>4.77559423446655</v>
       </c>
       <c r="G121" t="n">
-        <v>2.6978452205658</v>
+        <v>2.69784545898438</v>
       </c>
       <c r="H121" t="s">
         <v>8</v>
@@ -3567,7 +3567,7 @@
         <v>4.87982320785522</v>
       </c>
       <c r="G123" t="n">
-        <v>2.75672674179077</v>
+        <v>2.75672650337219</v>
       </c>
       <c r="H123" t="s">
         <v>8</v>
@@ -3593,7 +3593,7 @@
         <v>4.1691689491272</v>
       </c>
       <c r="G124" t="n">
-        <v>2.35526156425476</v>
+        <v>2.35526132583618</v>
       </c>
       <c r="H124" t="s">
         <v>8</v>
@@ -3619,7 +3619,7 @@
         <v>3.71814107894897</v>
       </c>
       <c r="G125" t="n">
-        <v>2.1004650592804</v>
+        <v>2.10046529769897</v>
       </c>
       <c r="H125" t="s">
         <v>8</v>
@@ -3645,7 +3645,7 @@
         <v>4.09336614608765</v>
       </c>
       <c r="G126" t="n">
-        <v>2.31243848800659</v>
+        <v>2.31243872642517</v>
       </c>
       <c r="H126" t="s">
         <v>8</v>
@@ -3671,7 +3671,7 @@
         <v>3.9777660369873</v>
       </c>
       <c r="G127" t="n">
-        <v>2.24713349342346</v>
+        <v>2.24713373184204</v>
       </c>
       <c r="H127" t="s">
         <v>8</v>
@@ -3697,7 +3697,7 @@
         <v>3.9891369342804</v>
       </c>
       <c r="G128" t="n">
-        <v>2.25355696678162</v>
+        <v>2.2535572052002</v>
       </c>
       <c r="H128" t="s">
         <v>8</v>
@@ -3723,7 +3723,7 @@
         <v>4.09715604782104</v>
       </c>
       <c r="G129" t="n">
-        <v>2.31457948684692</v>
+        <v>2.3145797252655</v>
       </c>
       <c r="H129" t="s">
         <v>8</v>
@@ -3775,7 +3775,7 @@
         <v>3.76172804832458</v>
       </c>
       <c r="G131" t="n">
-        <v>2.12508845329285</v>
+        <v>2.12508869171143</v>
       </c>
       <c r="H131" t="s">
         <v>8</v>
@@ -3827,7 +3827,7 @@
         <v>3.79015398025513</v>
       </c>
       <c r="G133" t="n">
-        <v>2.14114689826965</v>
+        <v>2.14114665985107</v>
       </c>
       <c r="H133" t="s">
         <v>8</v>
@@ -3879,7 +3879,7 @@
         <v>3.99861192703247</v>
       </c>
       <c r="G135" t="n">
-        <v>2.25890970230103</v>
+        <v>2.2589099407196</v>
       </c>
       <c r="H135" t="s">
         <v>8</v>
@@ -3905,7 +3905,7 @@
         <v>4.29234886169434</v>
       </c>
       <c r="G136" t="n">
-        <v>2.42484879493713</v>
+        <v>2.42484855651855</v>
       </c>
       <c r="H136" t="s">
         <v>8</v>
@@ -3931,7 +3931,7 @@
         <v>4.26392316818237</v>
       </c>
       <c r="G137" t="n">
-        <v>2.40879058837891</v>
+        <v>2.40879034996033</v>
       </c>
       <c r="H137" t="s">
         <v>8</v>
@@ -3983,7 +3983,7 @@
         <v>4.26960802078247</v>
       </c>
       <c r="G139" t="n">
-        <v>2.41200160980225</v>
+        <v>2.41200184822083</v>
       </c>
       <c r="H139" t="s">
         <v>8</v>
@@ -4061,7 +4061,7 @@
         <v>4.32077503204346</v>
       </c>
       <c r="G142" t="n">
-        <v>2.44090747833252</v>
+        <v>2.44090723991394</v>
       </c>
       <c r="H142" t="s">
         <v>8</v>
@@ -4113,7 +4113,7 @@
         <v>4.26581811904907</v>
       </c>
       <c r="G144" t="n">
-        <v>2.40986061096191</v>
+        <v>2.40986084938049</v>
       </c>
       <c r="H144" t="s">
         <v>8</v>
@@ -4139,7 +4139,7 @@
         <v>4.30182504653931</v>
       </c>
       <c r="G145" t="n">
-        <v>2.43020224571228</v>
+        <v>2.4302020072937</v>
       </c>
       <c r="H145" t="s">
         <v>8</v>
@@ -4165,7 +4165,7 @@
         <v>4.18622493743896</v>
       </c>
       <c r="G146" t="n">
-        <v>2.36489653587341</v>
+        <v>2.36489677429199</v>
       </c>
       <c r="H146" t="s">
         <v>8</v>
@@ -4191,7 +4191,7 @@
         <v>4.33025121688843</v>
       </c>
       <c r="G147" t="n">
-        <v>2.44626069068909</v>
+        <v>2.44626045227051</v>
       </c>
       <c r="H147" t="s">
         <v>8</v>
@@ -4217,7 +4217,7 @@
         <v>4.26392316818237</v>
       </c>
       <c r="G148" t="n">
-        <v>2.40879058837891</v>
+        <v>2.40879034996033</v>
       </c>
       <c r="H148" t="s">
         <v>8</v>
@@ -4243,7 +4243,7 @@
         <v>4.24497222900391</v>
       </c>
       <c r="G149" t="n">
-        <v>2.39808464050293</v>
+        <v>2.39808440208435</v>
       </c>
       <c r="H149" t="s">
         <v>8</v>
@@ -4321,7 +4321,7 @@
         <v>3.97018599510193</v>
       </c>
       <c r="G152" t="n">
-        <v>2.24285125732422</v>
+        <v>2.24285101890564</v>
       </c>
       <c r="H152" t="s">
         <v>8</v>
@@ -4399,7 +4399,7 @@
         <v>4.25065803527832</v>
       </c>
       <c r="G155" t="n">
-        <v>2.40129661560059</v>
+        <v>2.40129685401917</v>
       </c>
       <c r="H155" t="s">
         <v>8</v>
@@ -4425,7 +4425,7 @@
         <v>4.35867691040039</v>
       </c>
       <c r="G156" t="n">
-        <v>2.46231865882874</v>
+        <v>2.46231889724731</v>
       </c>
       <c r="H156" t="s">
         <v>8</v>
@@ -4451,7 +4451,7 @@
         <v>4.36436176300049</v>
       </c>
       <c r="G157" t="n">
-        <v>2.46553015708923</v>
+        <v>2.46553039550781</v>
       </c>
       <c r="H157" t="s">
         <v>8</v>
@@ -4503,7 +4503,7 @@
         <v>4.32077503204346</v>
       </c>
       <c r="G159" t="n">
-        <v>2.44090747833252</v>
+        <v>2.44090723991394</v>
       </c>
       <c r="H159" t="s">
         <v>8</v>
@@ -4529,7 +4529,7 @@
         <v>4.18054008483887</v>
       </c>
       <c r="G160" t="n">
-        <v>2.36168503761292</v>
+        <v>2.36168551445007</v>
       </c>
       <c r="H160" t="s">
         <v>8</v>
@@ -4555,7 +4555,7 @@
         <v>3.97587108612061</v>
       </c>
       <c r="G161" t="n">
-        <v>2.24606251716614</v>
+        <v>2.24606275558472</v>
       </c>
       <c r="H161" t="s">
         <v>8</v>
@@ -4581,7 +4581,7 @@
         <v>3.9777660369873</v>
       </c>
       <c r="G162" t="n">
-        <v>2.24713349342346</v>
+        <v>2.24713373184204</v>
       </c>
       <c r="H162" t="s">
         <v>8</v>
@@ -4607,7 +4607,7 @@
         <v>3.8962779045105</v>
       </c>
       <c r="G163" t="n">
-        <v>2.20109891891479</v>
+        <v>2.20109868049622</v>
       </c>
       <c r="H163" t="s">
         <v>8</v>
@@ -4685,7 +4685,7 @@
         <v>4.12558221817017</v>
       </c>
       <c r="G166" t="n">
-        <v>2.33063817024231</v>
+        <v>2.33063840866089</v>
       </c>
       <c r="H166" t="s">
         <v>8</v>
@@ -4711,7 +4711,7 @@
         <v>4.04598903656006</v>
       </c>
       <c r="G167" t="n">
-        <v>2.28567457199097</v>
+        <v>2.28567433357239</v>
       </c>
       <c r="H167" t="s">
         <v>8</v>
@@ -4737,7 +4737,7 @@
         <v>4.09336614608765</v>
       </c>
       <c r="G168" t="n">
-        <v>2.31243848800659</v>
+        <v>2.31243872642517</v>
       </c>
       <c r="H168" t="s">
         <v>8</v>
@@ -4789,7 +4789,7 @@
         <v>4.12179183959961</v>
       </c>
       <c r="G170" t="n">
-        <v>2.3284969329834</v>
+        <v>2.32849717140198</v>
       </c>
       <c r="H170" t="s">
         <v>8</v>
@@ -4815,7 +4815,7 @@
         <v>4.11231708526611</v>
       </c>
       <c r="G171" t="n">
-        <v>2.32314395904541</v>
+        <v>2.32314419746399</v>
       </c>
       <c r="H171" t="s">
         <v>8</v>
@@ -4841,7 +4841,7 @@
         <v>4.09336614608765</v>
       </c>
       <c r="G172" t="n">
-        <v>2.31243848800659</v>
+        <v>2.31243872642517</v>
       </c>
       <c r="H172" t="s">
         <v>8</v>
@@ -4867,7 +4867,7 @@
         <v>4.10473680496216</v>
       </c>
       <c r="G173" t="n">
-        <v>2.3188624382019</v>
+        <v>2.31886219978333</v>
       </c>
       <c r="H173" t="s">
         <v>8</v>
@@ -4893,7 +4893,7 @@
         <v>4.18811988830566</v>
       </c>
       <c r="G174" t="n">
-        <v>2.36596727371216</v>
+        <v>2.36596751213074</v>
       </c>
       <c r="H174" t="s">
         <v>8</v>
@@ -4945,7 +4945,7 @@
         <v>4.1596941947937</v>
       </c>
       <c r="G176" t="n">
-        <v>2.34990906715393</v>
+        <v>2.34990882873535</v>
       </c>
       <c r="H176" t="s">
         <v>8</v>
@@ -4971,7 +4971,7 @@
         <v>4.22981214523315</v>
       </c>
       <c r="G177" t="n">
-        <v>2.38951992988586</v>
+        <v>2.38952016830444</v>
       </c>
       <c r="H177" t="s">
         <v>8</v>
@@ -4997,7 +4997,7 @@
         <v>4.37573289871216</v>
       </c>
       <c r="G178" t="n">
-        <v>2.47195410728455</v>
+        <v>2.47195434570312</v>
       </c>
       <c r="H178" t="s">
         <v>8</v>
@@ -5023,7 +5023,7 @@
         <v>4.31888008117676</v>
       </c>
       <c r="G179" t="n">
-        <v>2.43983674049377</v>
+        <v>2.4398365020752</v>
       </c>
       <c r="H179" t="s">
         <v>8</v>
@@ -5075,7 +5075,7 @@
         <v>4.65241384506226</v>
       </c>
       <c r="G181" t="n">
-        <v>2.62825751304626</v>
+        <v>2.62825775146484</v>
       </c>
       <c r="H181" t="s">
         <v>8</v>
@@ -5101,7 +5101,7 @@
         <v>4.58798122406006</v>
       </c>
       <c r="G182" t="n">
-        <v>2.59185838699341</v>
+        <v>2.59185862541199</v>
       </c>
       <c r="H182" t="s">
         <v>8</v>
@@ -5153,7 +5153,7 @@
         <v>4.39657878875732</v>
       </c>
       <c r="G184" t="n">
-        <v>2.48373055458069</v>
+        <v>2.48373079299927</v>
       </c>
       <c r="H184" t="s">
         <v>8</v>
@@ -5257,7 +5257,7 @@
         <v>4.34920215606689</v>
       </c>
       <c r="G188" t="n">
-        <v>2.45696663856506</v>
+        <v>2.45696616172791</v>
       </c>
       <c r="H188" t="s">
         <v>8</v>
@@ -5283,7 +5283,7 @@
         <v>4.1691689491272</v>
       </c>
       <c r="G189" t="n">
-        <v>2.35526156425476</v>
+        <v>2.35526132583618</v>
       </c>
       <c r="H189" t="s">
         <v>8</v>
@@ -5309,7 +5309,7 @@
         <v>4.14263820648193</v>
       </c>
       <c r="G190" t="n">
-        <v>2.34027361869812</v>
+        <v>2.3402738571167</v>
       </c>
       <c r="H190" t="s">
         <v>8</v>
@@ -5335,7 +5335,7 @@
         <v>4.14074277877808</v>
       </c>
       <c r="G191" t="n">
-        <v>2.33920288085938</v>
+        <v>2.3392026424408</v>
       </c>
       <c r="H191" t="s">
         <v>8</v>
@@ -5387,7 +5387,7 @@
         <v>4.12179183959961</v>
       </c>
       <c r="G193" t="n">
-        <v>2.3284969329834</v>
+        <v>2.32849717140198</v>
       </c>
       <c r="H193" t="s">
         <v>8</v>
@@ -5465,7 +5465,7 @@
         <v>4.17864513397217</v>
       </c>
       <c r="G196" t="n">
-        <v>2.36061453819275</v>
+        <v>2.36061477661133</v>
       </c>
       <c r="H196" t="s">
         <v>8</v>
@@ -5491,7 +5491,7 @@
         <v>4.06493997573853</v>
       </c>
       <c r="G197" t="n">
-        <v>2.29637980461121</v>
+        <v>2.29638004302979</v>
       </c>
       <c r="H197" t="s">
         <v>8</v>
@@ -5517,7 +5517,7 @@
         <v>4.05925512313843</v>
       </c>
       <c r="G198" t="n">
-        <v>2.29316854476929</v>
+        <v>2.29316878318787</v>
       </c>
       <c r="H198" t="s">
         <v>8</v>
@@ -5595,7 +5595,7 @@
         <v>3.82237005233765</v>
       </c>
       <c r="G201" t="n">
-        <v>2.15934681892395</v>
+        <v>2.15934658050537</v>
       </c>
       <c r="H201" t="s">
         <v>8</v>
@@ -5647,7 +5647,7 @@
         <v>3.72382593154907</v>
       </c>
       <c r="G203" t="n">
-        <v>2.10367703437805</v>
+        <v>2.10367679595947</v>
       </c>
       <c r="H203" t="s">
         <v>8</v>
@@ -5673,7 +5673,7 @@
         <v>3.82426500320435</v>
       </c>
       <c r="G204" t="n">
-        <v>2.16041707992554</v>
+        <v>2.16041731834412</v>
       </c>
       <c r="H204" t="s">
         <v>8</v>
@@ -5777,7 +5777,7 @@
         <v>4.02135276794434</v>
       </c>
       <c r="G208" t="n">
-        <v>2.27175641059875</v>
+        <v>2.27175664901733</v>
       </c>
       <c r="H208" t="s">
         <v>8</v>
@@ -5829,7 +5829,7 @@
         <v>4.2260217666626</v>
       </c>
       <c r="G210" t="n">
-        <v>2.38737893104553</v>
+        <v>2.38737916946411</v>
       </c>
       <c r="H210" t="s">
         <v>8</v>
@@ -5855,7 +5855,7 @@
         <v>4.24118185043335</v>
       </c>
       <c r="G211" t="n">
-        <v>2.39594316482544</v>
+        <v>2.39594340324402</v>
       </c>
       <c r="H211" t="s">
         <v>8</v>
@@ -5881,7 +5881,7 @@
         <v>4.21275615692139</v>
       </c>
       <c r="G212" t="n">
-        <v>2.37988519668579</v>
+        <v>2.37988471984863</v>
       </c>
       <c r="H212" t="s">
         <v>8</v>
@@ -5907,7 +5907,7 @@
         <v>4.2260217666626</v>
       </c>
       <c r="G213" t="n">
-        <v>2.38737893104553</v>
+        <v>2.38737916946411</v>
       </c>
       <c r="H213" t="s">
         <v>8</v>
@@ -5959,7 +5959,7 @@
         <v>4.14263820648193</v>
       </c>
       <c r="G215" t="n">
-        <v>2.34027361869812</v>
+        <v>2.3402738571167</v>
       </c>
       <c r="H215" t="s">
         <v>8</v>
@@ -5985,7 +5985,7 @@
         <v>3.99861192703247</v>
       </c>
       <c r="G216" t="n">
-        <v>2.25890970230103</v>
+        <v>2.2589099407196</v>
       </c>
       <c r="H216" t="s">
         <v>8</v>
@@ -6011,7 +6011,7 @@
         <v>3.9891369342804</v>
       </c>
       <c r="G217" t="n">
-        <v>2.25355696678162</v>
+        <v>2.2535572052002</v>
       </c>
       <c r="H217" t="s">
         <v>8</v>
@@ -6037,7 +6037,7 @@
         <v>3.9891369342804</v>
       </c>
       <c r="G218" t="n">
-        <v>2.25355696678162</v>
+        <v>2.2535572052002</v>
       </c>
       <c r="H218" t="s">
         <v>8</v>
@@ -6089,7 +6089,7 @@
         <v>4.11800193786621</v>
       </c>
       <c r="G220" t="n">
-        <v>2.32635617256165</v>
+        <v>2.32635569572449</v>
       </c>
       <c r="H220" t="s">
         <v>8</v>
@@ -6115,7 +6115,7 @@
         <v>3.97018599510193</v>
       </c>
       <c r="G221" t="n">
-        <v>2.24285125732422</v>
+        <v>2.24285101890564</v>
       </c>
       <c r="H221" t="s">
         <v>8</v>
@@ -6141,7 +6141,7 @@
         <v>3.91522908210754</v>
       </c>
       <c r="G222" t="n">
-        <v>2.21180462837219</v>
+        <v>2.21180486679077</v>
       </c>
       <c r="H222" t="s">
         <v>8</v>
@@ -6167,7 +6167,7 @@
         <v>4.63346290588379</v>
       </c>
       <c r="G223" t="n">
-        <v>2.61755180358887</v>
+        <v>2.61755228042603</v>
       </c>
       <c r="H223" t="s">
         <v>8</v>
@@ -6193,7 +6193,7 @@
         <v>4.39657878875732</v>
       </c>
       <c r="G224" t="n">
-        <v>2.48373055458069</v>
+        <v>2.48373079299927</v>
       </c>
       <c r="H224" t="s">
         <v>8</v>
@@ -6219,7 +6219,7 @@
         <v>4.33025121688843</v>
       </c>
       <c r="G225" t="n">
-        <v>2.44626069068909</v>
+        <v>2.44626045227051</v>
       </c>
       <c r="H225" t="s">
         <v>8</v>
@@ -6245,7 +6245,7 @@
         <v>4.31888008117676</v>
       </c>
       <c r="G226" t="n">
-        <v>2.43983674049377</v>
+        <v>2.4398365020752</v>
       </c>
       <c r="H226" t="s">
         <v>8</v>
@@ -6271,7 +6271,7 @@
         <v>4.34920215606689</v>
       </c>
       <c r="G227" t="n">
-        <v>2.45696663856506</v>
+        <v>2.45696616172791</v>
       </c>
       <c r="H227" t="s">
         <v>8</v>
@@ -6297,7 +6297,7 @@
         <v>4.29045391082764</v>
       </c>
       <c r="G228" t="n">
-        <v>2.42377805709839</v>
+        <v>2.42377829551697</v>
       </c>
       <c r="H228" t="s">
         <v>8</v>
@@ -6323,7 +6323,7 @@
         <v>4.27339792251587</v>
       </c>
       <c r="G229" t="n">
-        <v>2.41414308547974</v>
+        <v>2.41414260864258</v>
       </c>
       <c r="H229" t="s">
         <v>8</v>
@@ -6349,7 +6349,7 @@
         <v>4.39657878875732</v>
       </c>
       <c r="G230" t="n">
-        <v>2.48373055458069</v>
+        <v>2.48373079299927</v>
       </c>
       <c r="H230" t="s">
         <v>8</v>
@@ -6375,7 +6375,7 @@
         <v>4.33025121688843</v>
       </c>
       <c r="G231" t="n">
-        <v>2.44626069068909</v>
+        <v>2.44626045227051</v>
       </c>
       <c r="H231" t="s">
         <v>8</v>
@@ -6401,7 +6401,7 @@
         <v>4.33025121688843</v>
       </c>
       <c r="G232" t="n">
-        <v>2.44626069068909</v>
+        <v>2.44626045227051</v>
       </c>
       <c r="H232" t="s">
         <v>8</v>
@@ -6427,7 +6427,7 @@
         <v>4.35867691040039</v>
       </c>
       <c r="G233" t="n">
-        <v>2.46231865882874</v>
+        <v>2.46231889724731</v>
       </c>
       <c r="H233" t="s">
         <v>8</v>
@@ -6505,7 +6505,7 @@
         <v>4.39657878875732</v>
       </c>
       <c r="G236" t="n">
-        <v>2.48373055458069</v>
+        <v>2.48373079299927</v>
       </c>
       <c r="H236" t="s">
         <v>8</v>
@@ -6531,7 +6531,7 @@
         <v>4.45343112945557</v>
       </c>
       <c r="G237" t="n">
-        <v>2.5158474445343</v>
+        <v>2.51584768295288</v>
       </c>
       <c r="H237" t="s">
         <v>8</v>
@@ -6557,7 +6557,7 @@
         <v>4.40415906906128</v>
       </c>
       <c r="G238" t="n">
-        <v>2.48801279067993</v>
+        <v>2.48801255226135</v>
       </c>
       <c r="H238" t="s">
         <v>8</v>
@@ -6583,7 +6583,7 @@
         <v>4.24307680130005</v>
       </c>
       <c r="G239" t="n">
-        <v>2.39701342582703</v>
+        <v>2.39701366424561</v>
       </c>
       <c r="H239" t="s">
         <v>8</v>
@@ -6687,7 +6687,7 @@
         <v>4.47617197036743</v>
       </c>
       <c r="G243" t="n">
-        <v>2.52869439125061</v>
+        <v>2.52869462966919</v>
       </c>
       <c r="H243" t="s">
         <v>8</v>
@@ -6713,7 +6713,7 @@
         <v>4.45343112945557</v>
       </c>
       <c r="G244" t="n">
-        <v>2.5158474445343</v>
+        <v>2.51584768295288</v>
       </c>
       <c r="H244" t="s">
         <v>8</v>
@@ -6739,7 +6739,7 @@
         <v>4.57471609115601</v>
       </c>
       <c r="G245" t="n">
-        <v>2.58436417579651</v>
+        <v>2.58436441421509</v>
       </c>
       <c r="H245" t="s">
         <v>8</v>
@@ -6765,7 +6765,7 @@
         <v>4.64483404159546</v>
       </c>
       <c r="G246" t="n">
-        <v>2.62397575378418</v>
+        <v>2.62397599220276</v>
       </c>
       <c r="H246" t="s">
         <v>8</v>
@@ -6791,7 +6791,7 @@
         <v>4.80875778198242</v>
       </c>
       <c r="G247" t="n">
-        <v>2.7165801525116</v>
+        <v>2.71657991409302</v>
       </c>
       <c r="H247" t="s">
         <v>8</v>
@@ -6843,7 +6843,7 @@
         <v>4.78506898880005</v>
       </c>
       <c r="G249" t="n">
-        <v>2.70319819450378</v>
+        <v>2.70319795608521</v>
       </c>
       <c r="H249" t="s">
         <v>8</v>
@@ -6869,7 +6869,7 @@
         <v>4.8608717918396</v>
       </c>
       <c r="G250" t="n">
-        <v>2.74602055549622</v>
+        <v>2.74602079391479</v>
       </c>
       <c r="H250" t="s">
         <v>8</v>
@@ -6895,7 +6895,7 @@
         <v>4.94141292572021</v>
       </c>
       <c r="G251" t="n">
-        <v>2.79152035713196</v>
+        <v>2.79152011871338</v>
       </c>
       <c r="H251" t="s">
         <v>8</v>
@@ -6921,7 +6921,7 @@
         <v>4.9887900352478</v>
       </c>
       <c r="G252" t="n">
-        <v>2.81828451156616</v>
+        <v>2.81828474998474</v>
       </c>
       <c r="H252" t="s">
         <v>8</v>
@@ -6947,7 +6947,7 @@
         <v>4.92719984054565</v>
       </c>
       <c r="G253" t="n">
-        <v>2.78349089622498</v>
+        <v>2.78349113464355</v>
       </c>
       <c r="H253" t="s">
         <v>8</v>
@@ -6973,7 +6973,7 @@
         <v>4.90824890136719</v>
       </c>
       <c r="G254" t="n">
-        <v>2.77278566360474</v>
+        <v>2.77278470993042</v>
       </c>
       <c r="H254" t="s">
         <v>8</v>
@@ -6999,7 +6999,7 @@
         <v>4.8466591835022</v>
       </c>
       <c r="G255" t="n">
-        <v>2.73799133300781</v>
+        <v>2.73799180984497</v>
       </c>
       <c r="H255" t="s">
         <v>8</v>
@@ -7051,7 +7051,7 @@
         <v>4.88929891586304</v>
       </c>
       <c r="G257" t="n">
-        <v>2.76207971572876</v>
+        <v>2.76207995414734</v>
       </c>
       <c r="H257" t="s">
         <v>8</v>
@@ -7077,7 +7077,7 @@
         <v>4.91772508621216</v>
       </c>
       <c r="G258" t="n">
-        <v>2.77813863754272</v>
+        <v>2.77813839912415</v>
       </c>
       <c r="H258" t="s">
         <v>8</v>
@@ -7103,7 +7103,7 @@
         <v>4.95562601089478</v>
       </c>
       <c r="G259" t="n">
-        <v>2.79954934120178</v>
+        <v>2.79954957962036</v>
       </c>
       <c r="H259" t="s">
         <v>8</v>
@@ -7129,7 +7129,7 @@
         <v>4.9840521812439</v>
       </c>
       <c r="G260" t="n">
-        <v>2.81560802459717</v>
+        <v>2.81560778617859</v>
       </c>
       <c r="H260" t="s">
         <v>8</v>
@@ -7181,7 +7181,7 @@
         <v>5.15934705734253</v>
       </c>
       <c r="G262" t="n">
-        <v>2.9146363735199</v>
+        <v>2.91463661193848</v>
       </c>
       <c r="H262" t="s">
         <v>8</v>
@@ -7207,7 +7207,7 @@
         <v>5.11670780181885</v>
       </c>
       <c r="G263" t="n">
-        <v>2.89054822921753</v>
+        <v>2.89054846763611</v>
       </c>
       <c r="H263" t="s">
         <v>8</v>
@@ -7233,7 +7233,7 @@
         <v>5.14513397216797</v>
       </c>
       <c r="G264" t="n">
-        <v>2.90660691261292</v>
+        <v>2.90660715103149</v>
       </c>
       <c r="H264" t="s">
         <v>8</v>
@@ -7259,7 +7259,7 @@
         <v>5.26831388473511</v>
       </c>
       <c r="G265" t="n">
-        <v>2.97619462013245</v>
+        <v>2.97619414329529</v>
       </c>
       <c r="H265" t="s">
         <v>8</v>
@@ -7285,7 +7285,7 @@
         <v>5.20198583602905</v>
       </c>
       <c r="G266" t="n">
-        <v>2.93872380256653</v>
+        <v>2.93872404098511</v>
       </c>
       <c r="H266" t="s">
         <v>8</v>
@@ -7337,7 +7337,7 @@
         <v>5.25883913040161</v>
       </c>
       <c r="G268" t="n">
-        <v>2.97084188461304</v>
+        <v>2.97084164619446</v>
       </c>
       <c r="H268" t="s">
         <v>8</v>
@@ -7363,7 +7363,7 @@
         <v>5.19251108169556</v>
       </c>
       <c r="G269" t="n">
-        <v>2.9333713054657</v>
+        <v>2.93337154388428</v>
       </c>
       <c r="H269" t="s">
         <v>8</v>
@@ -7389,7 +7389,7 @@
         <v>5.13565921783447</v>
       </c>
       <c r="G270" t="n">
-        <v>2.90125489234924</v>
+        <v>2.90125441551208</v>
       </c>
       <c r="H270" t="s">
         <v>8</v>
@@ -7415,7 +7415,7 @@
         <v>5.14513397216797</v>
       </c>
       <c r="G271" t="n">
-        <v>2.90660691261292</v>
+        <v>2.90660715103149</v>
       </c>
       <c r="H271" t="s">
         <v>8</v>
@@ -7493,7 +7493,7 @@
         <v>5.42939615249634</v>
       </c>
       <c r="G274" t="n">
-        <v>3.06719350814819</v>
+        <v>3.06719326972961</v>
       </c>
       <c r="H274" t="s">
         <v>8</v>
@@ -7545,7 +7545,7 @@
         <v>5.23988819122314</v>
       </c>
       <c r="G276" t="n">
-        <v>2.96013569831848</v>
+        <v>2.96013593673706</v>
       </c>
       <c r="H276" t="s">
         <v>8</v>
@@ -7571,7 +7571,7 @@
         <v>5.4009690284729</v>
       </c>
       <c r="G277" t="n">
-        <v>3.05113458633423</v>
+        <v>3.05113434791565</v>
       </c>
       <c r="H277" t="s">
         <v>8</v>
@@ -7597,7 +7597,7 @@
         <v>5.30621576309204</v>
       </c>
       <c r="G278" t="n">
-        <v>2.99760603904724</v>
+        <v>2.99760556221008</v>
       </c>
       <c r="H278" t="s">
         <v>8</v>
@@ -7623,7 +7623,7 @@
         <v>5.22093677520752</v>
       </c>
       <c r="G279" t="n">
-        <v>2.94942951202393</v>
+        <v>2.94942998886108</v>
       </c>
       <c r="H279" t="s">
         <v>8</v>
@@ -7649,7 +7649,7 @@
         <v>5.33937883377075</v>
       </c>
       <c r="G280" t="n">
-        <v>3.0163402557373</v>
+        <v>3.01634049415588</v>
       </c>
       <c r="H280" t="s">
         <v>8</v>
@@ -7727,7 +7727,7 @@
         <v>5.14513397216797</v>
       </c>
       <c r="G283" t="n">
-        <v>2.90660691261292</v>
+        <v>2.90660715103149</v>
       </c>
       <c r="H283" t="s">
         <v>8</v>
@@ -7753,7 +7753,7 @@
         <v>5.11670780181885</v>
       </c>
       <c r="G284" t="n">
-        <v>2.89054822921753</v>
+        <v>2.89054846763611</v>
       </c>
       <c r="H284" t="s">
         <v>8</v>
@@ -7805,7 +7805,7 @@
         <v>5.09775686264038</v>
       </c>
       <c r="G286" t="n">
-        <v>2.87984251976013</v>
+        <v>2.87984275817871</v>
       </c>
       <c r="H286" t="s">
         <v>8</v>
@@ -7857,7 +7857,7 @@
         <v>5.06459283828735</v>
       </c>
       <c r="G288" t="n">
-        <v>2.86110782623291</v>
+        <v>2.86110758781433</v>
       </c>
       <c r="H288" t="s">
         <v>8</v>
@@ -7883,7 +7883,7 @@
         <v>5.1261830329895</v>
       </c>
       <c r="G289" t="n">
-        <v>2.8959014415741</v>
+        <v>2.89590072631836</v>
       </c>
       <c r="H289" t="s">
         <v>8</v>
@@ -7909,7 +7909,7 @@
         <v>5.178297996521</v>
       </c>
       <c r="G290" t="n">
-        <v>2.92534208297729</v>
+        <v>2.92534160614014</v>
       </c>
       <c r="H290" t="s">
         <v>8</v>
@@ -7935,7 +7935,7 @@
         <v>5.14513397216797</v>
       </c>
       <c r="G291" t="n">
-        <v>2.90660691261292</v>
+        <v>2.90660715103149</v>
       </c>
       <c r="H291" t="s">
         <v>8</v>
@@ -7961,7 +7961,7 @@
         <v>4.91772508621216</v>
       </c>
       <c r="G292" t="n">
-        <v>2.77813863754272</v>
+        <v>2.77813839912415</v>
       </c>
       <c r="H292" t="s">
         <v>8</v>
@@ -7987,7 +7987,7 @@
         <v>4.95088911056519</v>
       </c>
       <c r="G293" t="n">
-        <v>2.79687333106995</v>
+        <v>2.79687356948853</v>
       </c>
       <c r="H293" t="s">
         <v>8</v>
@@ -8039,7 +8039,7 @@
         <v>4.85613489151001</v>
       </c>
       <c r="G295" t="n">
-        <v>2.7433443069458</v>
+        <v>2.74334454536438</v>
       </c>
       <c r="H295" t="s">
         <v>8</v>
@@ -8065,7 +8065,7 @@
         <v>4.78506898880005</v>
       </c>
       <c r="G296" t="n">
-        <v>2.70319819450378</v>
+        <v>2.70319795608521</v>
       </c>
       <c r="H296" t="s">
         <v>8</v>
@@ -8117,7 +8117,7 @@
         <v>4.5785059928894</v>
       </c>
       <c r="G298" t="n">
-        <v>2.58650588989258</v>
+        <v>2.586505651474</v>
       </c>
       <c r="H298" t="s">
         <v>8</v>
@@ -8143,7 +8143,7 @@
         <v>4.78980684280396</v>
       </c>
       <c r="G299" t="n">
-        <v>2.70587420463562</v>
+        <v>2.7058744430542</v>
       </c>
       <c r="H299" t="s">
         <v>8</v>
@@ -8169,7 +8169,7 @@
         <v>4.91298723220825</v>
       </c>
       <c r="G300" t="n">
-        <v>2.77546167373657</v>
+        <v>2.77546191215515</v>
       </c>
       <c r="H300" t="s">
         <v>8</v>
@@ -8221,7 +8221,7 @@
         <v>4.93667507171631</v>
       </c>
       <c r="G302" t="n">
-        <v>2.78884387016296</v>
+        <v>2.78884339332581</v>
       </c>
       <c r="H302" t="s">
         <v>8</v>
@@ -8247,7 +8247,7 @@
         <v>4.97457695007324</v>
       </c>
       <c r="G303" t="n">
-        <v>2.8102548122406</v>
+        <v>2.81025528907776</v>
       </c>
       <c r="H303" t="s">
         <v>8</v>
@@ -8273,7 +8273,7 @@
         <v>5.05985593795776</v>
       </c>
       <c r="G304" t="n">
-        <v>2.85843133926392</v>
+        <v>2.85843110084534</v>
       </c>
       <c r="H304" t="s">
         <v>8</v>
@@ -8299,7 +8299,7 @@
         <v>5.13565921783447</v>
       </c>
       <c r="G305" t="n">
-        <v>2.90125489234924</v>
+        <v>2.90125441551208</v>
       </c>
       <c r="H305" t="s">
         <v>8</v>
@@ -8325,7 +8325,7 @@
         <v>5.02669191360474</v>
       </c>
       <c r="G306" t="n">
-        <v>2.83969640731812</v>
+        <v>2.83969616889954</v>
       </c>
       <c r="H306" t="s">
         <v>8</v>
@@ -8351,7 +8351,7 @@
         <v>5.06459283828735</v>
       </c>
       <c r="G307" t="n">
-        <v>2.86110782623291</v>
+        <v>2.86110758781433</v>
       </c>
       <c r="H307" t="s">
         <v>8</v>
@@ -8377,7 +8377,7 @@
         <v>5.23041200637817</v>
       </c>
       <c r="G308" t="n">
-        <v>2.95478248596191</v>
+        <v>2.95478224754333</v>
       </c>
       <c r="H308" t="s">
         <v>8</v>
@@ -8403,7 +8403,7 @@
         <v>5.21146202087402</v>
       </c>
       <c r="G309" t="n">
-        <v>2.94407725334167</v>
+        <v>2.9440770149231</v>
       </c>
       <c r="H309" t="s">
         <v>8</v>
@@ -8429,7 +8429,7 @@
         <v>5.21146202087402</v>
       </c>
       <c r="G310" t="n">
-        <v>2.94407725334167</v>
+        <v>2.9440770149231</v>
       </c>
       <c r="H310" t="s">
         <v>8</v>
@@ -8455,7 +8455,7 @@
         <v>5.3156909942627</v>
       </c>
       <c r="G311" t="n">
-        <v>3.00295853614807</v>
+        <v>3.00295829772949</v>
       </c>
       <c r="H311" t="s">
         <v>8</v>
@@ -8481,7 +8481,7 @@
         <v>5.33464193344116</v>
       </c>
       <c r="G312" t="n">
-        <v>3.01366424560547</v>
+        <v>3.01366448402405</v>
       </c>
       <c r="H312" t="s">
         <v>8</v>
@@ -8559,7 +8559,7 @@
         <v>5.23988819122314</v>
       </c>
       <c r="G315" t="n">
-        <v>2.96013569831848</v>
+        <v>2.96013593673706</v>
       </c>
       <c r="H315" t="s">
         <v>8</v>
@@ -8611,7 +8611,7 @@
         <v>5.38201904296875</v>
       </c>
       <c r="G317" t="n">
-        <v>3.04042887687683</v>
+        <v>3.04042863845825</v>
       </c>
       <c r="H317" t="s">
         <v>8</v>
@@ -8637,7 +8637,7 @@
         <v>5.39623212814331</v>
       </c>
       <c r="G318" t="n">
-        <v>3.04845809936523</v>
+        <v>3.04845857620239</v>
       </c>
       <c r="H318" t="s">
         <v>8</v>
@@ -8689,7 +8689,7 @@
         <v>5.23514986038208</v>
       </c>
       <c r="G320" t="n">
-        <v>2.95745897293091</v>
+        <v>2.95745873451233</v>
       </c>
       <c r="H320" t="s">
         <v>8</v>
@@ -8715,7 +8715,7 @@
         <v>5.22093677520752</v>
       </c>
       <c r="G321" t="n">
-        <v>2.94942951202393</v>
+        <v>2.94942998886108</v>
       </c>
       <c r="H321" t="s">
         <v>8</v>
@@ -8741,7 +8741,7 @@
         <v>5.30621576309204</v>
       </c>
       <c r="G322" t="n">
-        <v>2.99760603904724</v>
+        <v>2.99760556221008</v>
       </c>
       <c r="H322" t="s">
         <v>8</v>
@@ -8793,7 +8793,7 @@
         <v>5.38201904296875</v>
       </c>
       <c r="G324" t="n">
-        <v>3.04042887687683</v>
+        <v>3.04042863845825</v>
       </c>
       <c r="H324" t="s">
         <v>8</v>
@@ -8845,7 +8845,7 @@
         <v>5.33937883377075</v>
       </c>
       <c r="G326" t="n">
-        <v>3.0163402557373</v>
+        <v>3.01634049415588</v>
       </c>
       <c r="H326" t="s">
         <v>8</v>
@@ -8871,7 +8871,7 @@
         <v>5.33937883377075</v>
       </c>
       <c r="G327" t="n">
-        <v>3.0163402557373</v>
+        <v>3.01634049415588</v>
       </c>
       <c r="H327" t="s">
         <v>8</v>
@@ -8923,7 +8923,7 @@
         <v>5.23514986038208</v>
       </c>
       <c r="G329" t="n">
-        <v>2.95745897293091</v>
+        <v>2.95745873451233</v>
       </c>
       <c r="H329" t="s">
         <v>8</v>
@@ -8949,7 +8949,7 @@
         <v>5.178297996521</v>
       </c>
       <c r="G330" t="n">
-        <v>2.92534208297729</v>
+        <v>2.92534160614014</v>
       </c>
       <c r="H330" t="s">
         <v>8</v>
@@ -8975,7 +8975,7 @@
         <v>5.11670780181885</v>
       </c>
       <c r="G331" t="n">
-        <v>2.89054822921753</v>
+        <v>2.89054846763611</v>
       </c>
       <c r="H331" t="s">
         <v>8</v>
@@ -9001,7 +9001,7 @@
         <v>4.9887900352478</v>
       </c>
       <c r="G332" t="n">
-        <v>2.81828451156616</v>
+        <v>2.81828474998474</v>
       </c>
       <c r="H332" t="s">
         <v>8</v>
@@ -9027,7 +9027,7 @@
         <v>5.10249519348145</v>
       </c>
       <c r="G333" t="n">
-        <v>2.88251972198486</v>
+        <v>2.88251948356628</v>
       </c>
       <c r="H333" t="s">
         <v>8</v>
@@ -9131,7 +9131,7 @@
         <v>5.66154289245605</v>
       </c>
       <c r="G337" t="n">
-        <v>3.19833827018738</v>
+        <v>3.19833850860596</v>
       </c>
       <c r="H337" t="s">
         <v>8</v>
@@ -9157,7 +9157,7 @@
         <v>5.64259195327759</v>
       </c>
       <c r="G338" t="n">
-        <v>3.18763327598572</v>
+        <v>3.1876323223114</v>
       </c>
       <c r="H338" t="s">
         <v>8</v>
@@ -9209,7 +9209,7 @@
         <v>5.68523120880127</v>
       </c>
       <c r="G340" t="n">
-        <v>3.21172046661377</v>
+        <v>3.21172070503235</v>
       </c>
       <c r="H340" t="s">
         <v>8</v>
@@ -9235,7 +9235,7 @@
         <v>5.74208307266235</v>
       </c>
       <c r="G341" t="n">
-        <v>3.24383735656738</v>
+        <v>3.24383759498596</v>
       </c>
       <c r="H341" t="s">
         <v>8</v>
@@ -9261,7 +9261,7 @@
         <v>5.66627979278564</v>
       </c>
       <c r="G342" t="n">
-        <v>3.20101451873779</v>
+        <v>3.20101475715637</v>
       </c>
       <c r="H342" t="s">
         <v>8</v>
@@ -9287,7 +9287,7 @@
         <v>5.76103401184082</v>
       </c>
       <c r="G343" t="n">
-        <v>3.25454354286194</v>
+        <v>3.25454330444336</v>
       </c>
       <c r="H343" t="s">
         <v>8</v>
@@ -9313,7 +9313,7 @@
         <v>5.92211580276489</v>
       </c>
       <c r="G344" t="n">
-        <v>3.34554171562195</v>
+        <v>3.34554219245911</v>
       </c>
       <c r="H344" t="s">
         <v>8</v>
@@ -9339,7 +9339,7 @@
         <v>5.74208307266235</v>
       </c>
       <c r="G345" t="n">
-        <v>3.24383735656738</v>
+        <v>3.24383759498596</v>
       </c>
       <c r="H345" t="s">
         <v>8</v>
@@ -9365,7 +9365,7 @@
         <v>5.77998495101929</v>
       </c>
       <c r="G346" t="n">
-        <v>3.26524901390076</v>
+        <v>3.26524949073792</v>
       </c>
       <c r="H346" t="s">
         <v>8</v>
@@ -9391,7 +9391,7 @@
         <v>5.70418214797974</v>
       </c>
       <c r="G347" t="n">
-        <v>3.22242617607117</v>
+        <v>3.22242665290833</v>
       </c>
       <c r="H347" t="s">
         <v>8</v>
@@ -9417,7 +9417,7 @@
         <v>5.65680503845215</v>
       </c>
       <c r="G348" t="n">
-        <v>3.19566226005554</v>
+        <v>3.19566178321838</v>
       </c>
       <c r="H348" t="s">
         <v>8</v>
@@ -9469,7 +9469,7 @@
         <v>5.60942792892456</v>
       </c>
       <c r="G350" t="n">
-        <v>3.1688973903656</v>
+        <v>3.16889762878418</v>
       </c>
       <c r="H350" t="s">
         <v>8</v>
@@ -9573,7 +9573,7 @@
         <v>5.54309988021851</v>
       </c>
       <c r="G354" t="n">
-        <v>3.13142681121826</v>
+        <v>3.131427526474</v>
       </c>
       <c r="H354" t="s">
         <v>8</v>
@@ -9599,7 +9599,7 @@
         <v>5.49098587036133</v>
       </c>
       <c r="G355" t="n">
-        <v>3.24046874046326</v>
+        <v>3.2404682636261</v>
       </c>
       <c r="H355" t="s">
         <v>8</v>
@@ -9625,7 +9625,7 @@
         <v>5.49572277069092</v>
       </c>
       <c r="G356" t="n">
-        <v>3.2432644367218</v>
+        <v>3.24326372146606</v>
       </c>
       <c r="H356" t="s">
         <v>8</v>
@@ -9651,7 +9651,7 @@
         <v>5.65680503845215</v>
       </c>
       <c r="G357" t="n">
-        <v>3.33832573890686</v>
+        <v>3.33832550048828</v>
       </c>
       <c r="H357" t="s">
         <v>8</v>
@@ -9703,7 +9703,7 @@
         <v>5.84631299972534</v>
       </c>
       <c r="G359" t="n">
-        <v>3.45016241073608</v>
+        <v>3.4501621723175</v>
       </c>
       <c r="H359" t="s">
         <v>8</v>
@@ -9729,7 +9729,7 @@
         <v>5.64732885360718</v>
       </c>
       <c r="G360" t="n">
-        <v>3.33273339271545</v>
+        <v>3.33273410797119</v>
       </c>
       <c r="H360" t="s">
         <v>8</v>
@@ -9755,7 +9755,7 @@
         <v>5.4578218460083</v>
       </c>
       <c r="G361" t="n">
-        <v>3.22089672088623</v>
+        <v>3.22089719772339</v>
       </c>
       <c r="H361" t="s">
         <v>8</v>
@@ -9807,7 +9807,7 @@
         <v>5.50519895553589</v>
       </c>
       <c r="G363" t="n">
-        <v>3.24885606765747</v>
+        <v>3.24885654449463</v>
       </c>
       <c r="H363" t="s">
         <v>8</v>
@@ -9859,7 +9859,7 @@
         <v>5.51467418670654</v>
       </c>
       <c r="G365" t="n">
-        <v>3.25444793701172</v>
+        <v>3.2544481754303</v>
       </c>
       <c r="H365" t="s">
         <v>8</v>
@@ -9885,7 +9885,7 @@
         <v>5.53362512588501</v>
       </c>
       <c r="G366" t="n">
-        <v>3.26563167572021</v>
+        <v>3.26563143730164</v>
       </c>
       <c r="H366" t="s">
         <v>8</v>
@@ -9911,7 +9911,7 @@
         <v>5.58573913574219</v>
       </c>
       <c r="G367" t="n">
-        <v>3.29638624191284</v>
+        <v>3.29638671875</v>
       </c>
       <c r="H367" t="s">
         <v>8</v>
@@ -9937,7 +9937,7 @@
         <v>5.83683681488037</v>
       </c>
       <c r="G368" t="n">
-        <v>3.44457030296326</v>
+        <v>3.4445698261261</v>
       </c>
       <c r="H368" t="s">
         <v>8</v>
@@ -9963,7 +9963,7 @@
         <v>5.8605260848999</v>
       </c>
       <c r="G369" t="n">
-        <v>3.45855069160461</v>
+        <v>3.45854997634888</v>
       </c>
       <c r="H369" t="s">
         <v>8</v>
@@ -9989,7 +9989,7 @@
         <v>5.74208307266235</v>
       </c>
       <c r="G370" t="n">
-        <v>3.38865184783936</v>
+        <v>3.38865208625793</v>
       </c>
       <c r="H370" t="s">
         <v>8</v>
@@ -10015,7 +10015,7 @@
         <v>5.90316486358643</v>
       </c>
       <c r="G371" t="n">
-        <v>3.48371267318726</v>
+        <v>3.48371362686157</v>
       </c>
       <c r="H371" t="s">
         <v>8</v>
@@ -10041,7 +10041,7 @@
         <v>5.86526298522949</v>
       </c>
       <c r="G372" t="n">
-        <v>3.461345911026</v>
+        <v>3.46134614944458</v>
       </c>
       <c r="H372" t="s">
         <v>8</v>
@@ -10067,7 +10067,7 @@
         <v>5.8605260848999</v>
       </c>
       <c r="G373" t="n">
-        <v>3.45855069160461</v>
+        <v>3.45854997634888</v>
       </c>
       <c r="H373" t="s">
         <v>8</v>
@@ -10093,7 +10093,7 @@
         <v>5.83683681488037</v>
       </c>
       <c r="G374" t="n">
-        <v>3.44457030296326</v>
+        <v>3.4445698261261</v>
       </c>
       <c r="H374" t="s">
         <v>8</v>
@@ -10119,7 +10119,7 @@
         <v>5.92211580276489</v>
       </c>
       <c r="G375" t="n">
-        <v>3.49489665031433</v>
+        <v>3.49489688873291</v>
       </c>
       <c r="H375" t="s">
         <v>8</v>
@@ -10145,7 +10145,7 @@
         <v>5.88421392440796</v>
       </c>
       <c r="G376" t="n">
-        <v>3.47252941131592</v>
+        <v>3.47252917289734</v>
       </c>
       <c r="H376" t="s">
         <v>8</v>
@@ -10171,7 +10171,7 @@
         <v>5.89368915557861</v>
       </c>
       <c r="G377" t="n">
-        <v>3.47812151908875</v>
+        <v>3.47812080383301</v>
       </c>
       <c r="H377" t="s">
         <v>8</v>
@@ -10223,7 +10223,7 @@
         <v>5.86526298522949</v>
       </c>
       <c r="G379" t="n">
-        <v>3.461345911026</v>
+        <v>3.46134614944458</v>
       </c>
       <c r="H379" t="s">
         <v>8</v>
@@ -10249,7 +10249,7 @@
         <v>5.84157514572144</v>
       </c>
       <c r="G380" t="n">
-        <v>3.44736647605896</v>
+        <v>3.44736695289612</v>
       </c>
       <c r="H380" t="s">
         <v>8</v>
@@ -10353,7 +10353,7 @@
         <v>5.94580411911011</v>
       </c>
       <c r="G384" t="n">
-        <v>3.50887680053711</v>
+        <v>3.50887656211853</v>
       </c>
       <c r="H384" t="s">
         <v>8</v>
@@ -10379,7 +10379,7 @@
         <v>6.04529619216919</v>
       </c>
       <c r="G385" t="n">
-        <v>3.56759142875671</v>
+        <v>3.56759119033813</v>
       </c>
       <c r="H385" t="s">
         <v>8</v>
@@ -10405,7 +10405,7 @@
         <v>6.07372188568115</v>
       </c>
       <c r="G386" t="n">
-        <v>3.58436632156372</v>
+        <v>3.5843665599823</v>
       </c>
       <c r="H386" t="s">
         <v>8</v>
@@ -10431,7 +10431,7 @@
         <v>6.04529619216919</v>
       </c>
       <c r="G387" t="n">
-        <v>3.56759142875671</v>
+        <v>3.56759119033813</v>
       </c>
       <c r="H387" t="s">
         <v>8</v>
@@ -10457,7 +10457,7 @@
         <v>6.02160692214966</v>
       </c>
       <c r="G388" t="n">
-        <v>3.55361104011536</v>
+        <v>3.55361127853394</v>
       </c>
       <c r="H388" t="s">
         <v>8</v>
@@ -10483,7 +10483,7 @@
         <v>6.07372188568115</v>
       </c>
       <c r="G389" t="n">
-        <v>3.58436632156372</v>
+        <v>3.5843665599823</v>
       </c>
       <c r="H389" t="s">
         <v>8</v>
@@ -10587,7 +10587,7 @@
         <v>6.56644201278687</v>
       </c>
       <c r="G393" t="n">
-        <v>3.87514162063599</v>
+        <v>3.87514209747314</v>
       </c>
       <c r="H393" t="s">
         <v>8</v>
@@ -10639,7 +10639,7 @@
         <v>6.64224481582642</v>
       </c>
       <c r="G395" t="n">
-        <v>3.91987633705139</v>
+        <v>3.91987657546997</v>
       </c>
       <c r="H395" t="s">
         <v>8</v>
@@ -10691,7 +10691,7 @@
         <v>6.68014621734619</v>
       </c>
       <c r="G397" t="n">
-        <v>3.94224309921265</v>
+        <v>3.94224333763123</v>
       </c>
       <c r="H397" t="s">
         <v>8</v>
@@ -10717,7 +10717,7 @@
         <v>6.71804809570312</v>
       </c>
       <c r="G398" t="n">
-        <v>3.96461129188538</v>
+        <v>3.9646110534668</v>
       </c>
       <c r="H398" t="s">
         <v>8</v>
@@ -10743,7 +10743,7 @@
         <v>6.70857286453247</v>
       </c>
       <c r="G399" t="n">
-        <v>3.95901989936829</v>
+        <v>3.95901918411255</v>
       </c>
       <c r="H399" t="s">
         <v>8</v>
@@ -10769,7 +10769,7 @@
         <v>6.63277006149292</v>
       </c>
       <c r="G400" t="n">
-        <v>3.91428470611572</v>
+        <v>3.91428518295288</v>
       </c>
       <c r="H400" t="s">
         <v>8</v>
@@ -10795,7 +10795,7 @@
         <v>6.70857286453247</v>
       </c>
       <c r="G401" t="n">
-        <v>3.95901989936829</v>
+        <v>3.95901918411255</v>
       </c>
       <c r="H401" t="s">
         <v>8</v>
@@ -10821,7 +10821,7 @@
         <v>6.53801584243774</v>
       </c>
       <c r="G402" t="n">
-        <v>3.85836625099182</v>
+        <v>3.85836577415466</v>
       </c>
       <c r="H402" t="s">
         <v>8</v>
@@ -10847,7 +10847,7 @@
         <v>6.52380323410034</v>
       </c>
       <c r="G403" t="n">
-        <v>3.84997892379761</v>
+        <v>3.84997940063477</v>
       </c>
       <c r="H403" t="s">
         <v>8</v>
@@ -10873,7 +10873,7 @@
         <v>6.50959014892578</v>
       </c>
       <c r="G404" t="n">
-        <v>3.84159135818481</v>
+        <v>3.84159064292908</v>
       </c>
       <c r="H404" t="s">
         <v>8</v>
@@ -10899,7 +10899,7 @@
         <v>6.50959014892578</v>
       </c>
       <c r="G405" t="n">
-        <v>3.84159135818481</v>
+        <v>3.84159064292908</v>
       </c>
       <c r="H405" t="s">
         <v>8</v>
@@ -10925,7 +10925,7 @@
         <v>6.64698314666748</v>
       </c>
       <c r="G406" t="n">
-        <v>3.92267227172852</v>
+        <v>3.92267203330994</v>
       </c>
       <c r="H406" t="s">
         <v>8</v>
@@ -10951,7 +10951,7 @@
         <v>6.65172004699707</v>
       </c>
       <c r="G407" t="n">
-        <v>3.92546772956848</v>
+        <v>3.92546796798706</v>
       </c>
       <c r="H407" t="s">
         <v>8</v>
@@ -10977,7 +10977,7 @@
         <v>6.65172004699707</v>
       </c>
       <c r="G408" t="n">
-        <v>3.92546772956848</v>
+        <v>3.92546796798706</v>
       </c>
       <c r="H408" t="s">
         <v>8</v>
@@ -11029,7 +11029,7 @@
         <v>6.689621925354</v>
       </c>
       <c r="G410" t="n">
-        <v>3.94783592224121</v>
+        <v>3.94783520698547</v>
       </c>
       <c r="H410" t="s">
         <v>8</v>
@@ -11055,7 +11055,7 @@
         <v>6.74647378921509</v>
       </c>
       <c r="G411" t="n">
-        <v>3.98138618469238</v>
+        <v>3.98138642311096</v>
       </c>
       <c r="H411" t="s">
         <v>8</v>
@@ -11081,7 +11081,7 @@
         <v>6.63277006149292</v>
       </c>
       <c r="G412" t="n">
-        <v>3.91428470611572</v>
+        <v>3.91428518295288</v>
       </c>
       <c r="H412" t="s">
         <v>8</v>
@@ -11107,7 +11107,7 @@
         <v>6.56644201278687</v>
       </c>
       <c r="G413" t="n">
-        <v>3.87514162063599</v>
+        <v>3.87514209747314</v>
       </c>
       <c r="H413" t="s">
         <v>8</v>
@@ -11159,7 +11159,7 @@
         <v>6.53801584243774</v>
       </c>
       <c r="G415" t="n">
-        <v>3.85836625099182</v>
+        <v>3.85836577415466</v>
       </c>
       <c r="H415" t="s">
         <v>8</v>
@@ -11237,7 +11237,7 @@
         <v>6.63277006149292</v>
       </c>
       <c r="G418" t="n">
-        <v>3.91428470611572</v>
+        <v>3.91428518295288</v>
       </c>
       <c r="H418" t="s">
         <v>8</v>
@@ -11315,7 +11315,7 @@
         <v>6.43378591537476</v>
       </c>
       <c r="G421" t="n">
-        <v>3.79685568809509</v>
+        <v>3.79685544967651</v>
       </c>
       <c r="H421" t="s">
         <v>8</v>
@@ -11341,7 +11341,7 @@
         <v>6.35798311233521</v>
       </c>
       <c r="G422" t="n">
-        <v>3.75212121009827</v>
+        <v>3.75212144851685</v>
       </c>
       <c r="H422" t="s">
         <v>8</v>
@@ -11367,7 +11367,7 @@
         <v>6.37693405151367</v>
       </c>
       <c r="G423" t="n">
-        <v>3.76330542564392</v>
+        <v>3.7633056640625</v>
       </c>
       <c r="H423" t="s">
         <v>8</v>
@@ -11393,7 +11393,7 @@
         <v>6.23006582260132</v>
       </c>
       <c r="G424" t="n">
-        <v>3.67663145065308</v>
+        <v>3.67663192749023</v>
       </c>
       <c r="H424" t="s">
         <v>8</v>
@@ -11445,7 +11445,7 @@
         <v>6.07372188568115</v>
       </c>
       <c r="G426" t="n">
-        <v>3.58436632156372</v>
+        <v>3.5843665599823</v>
       </c>
       <c r="H426" t="s">
         <v>8</v>
@@ -11471,7 +11471,7 @@
         <v>6.08319711685181</v>
       </c>
       <c r="G427" t="n">
-        <v>3.58995819091797</v>
+        <v>3.58995866775513</v>
       </c>
       <c r="H427" t="s">
         <v>8</v>
@@ -11497,7 +11497,7 @@
         <v>6.20637702941895</v>
       </c>
       <c r="G428" t="n">
-        <v>3.66265201568604</v>
+        <v>3.66265153884888</v>
       </c>
       <c r="H428" t="s">
         <v>8</v>
@@ -11523,7 +11523,7 @@
         <v>6.20637702941895</v>
       </c>
       <c r="G429" t="n">
-        <v>3.66265201568604</v>
+        <v>3.66265153884888</v>
       </c>
       <c r="H429" t="s">
         <v>8</v>
@@ -11549,7 +11549,7 @@
         <v>6.21111488342285</v>
       </c>
       <c r="G430" t="n">
-        <v>3.66544818878174</v>
+        <v>3.66544771194458</v>
       </c>
       <c r="H430" t="s">
         <v>8</v>
@@ -11575,7 +11575,7 @@
         <v>6.22532796859741</v>
       </c>
       <c r="G431" t="n">
-        <v>3.67383551597595</v>
+        <v>3.67383575439453</v>
       </c>
       <c r="H431" t="s">
         <v>8</v>
@@ -11601,7 +11601,7 @@
         <v>6.26322984695435</v>
       </c>
       <c r="G432" t="n">
-        <v>3.69620299339294</v>
+        <v>3.6962034702301</v>
       </c>
       <c r="H432" t="s">
         <v>8</v>
@@ -11627,7 +11627,7 @@
         <v>6.25375413894653</v>
       </c>
       <c r="G433" t="n">
-        <v>3.69061160087585</v>
+        <v>3.6906111240387</v>
       </c>
       <c r="H433" t="s">
         <v>8</v>
@@ -11653,7 +11653,7 @@
         <v>6.4100980758667</v>
       </c>
       <c r="G434" t="n">
-        <v>3.78287649154663</v>
+        <v>3.78287625312805</v>
       </c>
       <c r="H434" t="s">
         <v>8</v>
@@ -11731,7 +11731,7 @@
         <v>6.21111488342285</v>
       </c>
       <c r="G437" t="n">
-        <v>3.66544818878174</v>
+        <v>3.66544771194458</v>
       </c>
       <c r="H437" t="s">
         <v>8</v>
@@ -11757,7 +11757,7 @@
         <v>6.23480319976807</v>
       </c>
       <c r="G438" t="n">
-        <v>3.67942690849304</v>
+        <v>3.6794273853302</v>
       </c>
       <c r="H438" t="s">
         <v>8</v>
@@ -11809,7 +11809,7 @@
         <v>6.34850788116455</v>
       </c>
       <c r="G440" t="n">
-        <v>3.7465295791626</v>
+        <v>3.74652934074402</v>
       </c>
       <c r="H440" t="s">
         <v>8</v>
@@ -11835,7 +11835,7 @@
         <v>6.30113077163696</v>
       </c>
       <c r="G441" t="n">
-        <v>3.71856999397278</v>
+        <v>3.71857023239136</v>
       </c>
       <c r="H441" t="s">
         <v>8</v>
@@ -11861,7 +11861,7 @@
         <v>6.30113077163696</v>
       </c>
       <c r="G442" t="n">
-        <v>3.71856999397278</v>
+        <v>3.71857023239136</v>
       </c>
       <c r="H442" t="s">
         <v>8</v>
@@ -11913,7 +11913,7 @@
         <v>6.14952516555786</v>
       </c>
       <c r="G444" t="n">
-        <v>3.62910127639771</v>
+        <v>3.62910079956055</v>
       </c>
       <c r="H444" t="s">
         <v>8</v>
@@ -11965,7 +11965,7 @@
         <v>6.22059011459351</v>
       </c>
       <c r="G446" t="n">
-        <v>3.67103910446167</v>
+        <v>3.67103934288025</v>
       </c>
       <c r="H446" t="s">
         <v>8</v>
@@ -11991,7 +11991,7 @@
         <v>6.31060600280762</v>
       </c>
       <c r="G447" t="n">
-        <v>3.72416186332703</v>
+        <v>3.72416210174561</v>
       </c>
       <c r="H447" t="s">
         <v>8</v>
@@ -12017,7 +12017,7 @@
         <v>6.47168779373169</v>
       </c>
       <c r="G448" t="n">
-        <v>3.81922316551208</v>
+        <v>3.81922268867493</v>
       </c>
       <c r="H448" t="s">
         <v>8</v>
@@ -12043,7 +12043,7 @@
         <v>6.54275321960449</v>
       </c>
       <c r="G449" t="n">
-        <v>3.86116218566895</v>
+        <v>3.8611626625061</v>
       </c>
       <c r="H449" t="s">
         <v>8</v>
@@ -12069,7 +12069,7 @@
         <v>6.40062284469604</v>
       </c>
       <c r="G450" t="n">
-        <v>3.77728486061096</v>
+        <v>3.77728509902954</v>
       </c>
       <c r="H450" t="s">
         <v>8</v>
@@ -12147,7 +12147,7 @@
         <v>6.08319711685181</v>
       </c>
       <c r="G453" t="n">
-        <v>3.58995819091797</v>
+        <v>3.58995866775513</v>
       </c>
       <c r="H453" t="s">
         <v>8</v>
@@ -12173,7 +12173,7 @@
         <v>6.14004898071289</v>
       </c>
       <c r="G454" t="n">
-        <v>3.6235089302063</v>
+        <v>3.62350916862488</v>
       </c>
       <c r="H454" t="s">
         <v>8</v>
@@ -12199,7 +12199,7 @@
         <v>6.09741020202637</v>
       </c>
       <c r="G455" t="n">
-        <v>3.59834575653076</v>
+        <v>3.59834551811218</v>
       </c>
       <c r="H455" t="s">
         <v>8</v>
@@ -12225,7 +12225,7 @@
         <v>6.06424617767334</v>
       </c>
       <c r="G456" t="n">
-        <v>3.57877373695374</v>
+        <v>3.57877445220947</v>
       </c>
       <c r="H456" t="s">
         <v>8</v>
@@ -12251,7 +12251,7 @@
         <v>6.01686906814575</v>
       </c>
       <c r="G457" t="n">
-        <v>3.55081534385681</v>
+        <v>3.55081510543823</v>
       </c>
       <c r="H457" t="s">
         <v>8</v>
@@ -12277,7 +12277,7 @@
         <v>6.13057422637939</v>
       </c>
       <c r="G458" t="n">
-        <v>3.61791753768921</v>
+        <v>3.61791729927063</v>
       </c>
       <c r="H458" t="s">
         <v>8</v>
@@ -12303,7 +12303,7 @@
         <v>6.05477094650269</v>
       </c>
       <c r="G459" t="n">
-        <v>3.5731828212738</v>
+        <v>3.57318234443665</v>
       </c>
       <c r="H459" t="s">
         <v>8</v>
@@ -12329,7 +12329,7 @@
         <v>6.03108310699463</v>
       </c>
       <c r="G460" t="n">
-        <v>3.55920338630676</v>
+        <v>3.5592029094696</v>
       </c>
       <c r="H460" t="s">
         <v>8</v>
@@ -12355,7 +12355,7 @@
         <v>6.10688591003418</v>
       </c>
       <c r="G461" t="n">
-        <v>3.60393714904785</v>
+        <v>3.60393762588501</v>
       </c>
       <c r="H461" t="s">
         <v>8</v>
@@ -12381,7 +12381,7 @@
         <v>6.06424617767334</v>
       </c>
       <c r="G462" t="n">
-        <v>3.57877373695374</v>
+        <v>3.57877445220947</v>
       </c>
       <c r="H462" t="s">
         <v>8</v>
@@ -12407,7 +12407,7 @@
         <v>6.11162281036377</v>
       </c>
       <c r="G463" t="n">
-        <v>3.60673260688782</v>
+        <v>3.60673308372498</v>
       </c>
       <c r="H463" t="s">
         <v>8</v>
@@ -12433,7 +12433,7 @@
         <v>6.14004898071289</v>
       </c>
       <c r="G464" t="n">
-        <v>3.6235089302063</v>
+        <v>3.62350916862488</v>
       </c>
       <c r="H464" t="s">
         <v>8</v>
@@ -12459,7 +12459,7 @@
         <v>6.17795085906982</v>
       </c>
       <c r="G465" t="n">
-        <v>3.64587664604187</v>
+        <v>3.64587593078613</v>
       </c>
       <c r="H465" t="s">
         <v>8</v>
@@ -12485,7 +12485,7 @@
         <v>6.18268918991089</v>
       </c>
       <c r="G466" t="n">
-        <v>3.64867234230042</v>
+        <v>3.64867329597473</v>
       </c>
       <c r="H466" t="s">
         <v>8</v>
@@ -12511,7 +12511,7 @@
         <v>6.14004898071289</v>
       </c>
       <c r="G467" t="n">
-        <v>3.6235089302063</v>
+        <v>3.62350916862488</v>
       </c>
       <c r="H467" t="s">
         <v>8</v>
@@ -12563,7 +12563,7 @@
         <v>6.11636114120483</v>
       </c>
       <c r="G469" t="n">
-        <v>3.60952949523926</v>
+        <v>3.609530210495</v>
       </c>
       <c r="H469" t="s">
         <v>8</v>
@@ -12615,7 +12615,7 @@
         <v>6.15899991989136</v>
       </c>
       <c r="G471" t="n">
-        <v>3.63469243049622</v>
+        <v>3.63469290733337</v>
       </c>
       <c r="H471" t="s">
         <v>8</v>
@@ -12641,7 +12641,7 @@
         <v>6.15426301956177</v>
       </c>
       <c r="G472" t="n">
-        <v>3.63189744949341</v>
+        <v>3.63189697265625</v>
       </c>
       <c r="H472" t="s">
         <v>8</v>
@@ -12667,7 +12667,7 @@
         <v>6.22059011459351</v>
       </c>
       <c r="G473" t="n">
-        <v>3.67103910446167</v>
+        <v>3.67103934288025</v>
       </c>
       <c r="H473" t="s">
         <v>8</v>
@@ -12693,7 +12693,7 @@
         <v>6.31060600280762</v>
       </c>
       <c r="G474" t="n">
-        <v>3.72416186332703</v>
+        <v>3.72416210174561</v>
       </c>
       <c r="H474" t="s">
         <v>8</v>
@@ -12719,7 +12719,7 @@
         <v>6.05003309249878</v>
       </c>
       <c r="G475" t="n">
-        <v>3.57038640975952</v>
+        <v>3.57038688659668</v>
       </c>
       <c r="H475" t="s">
         <v>8</v>
@@ -12771,7 +12771,7 @@
         <v>5.80841112136841</v>
       </c>
       <c r="G477" t="n">
-        <v>3.42779517173767</v>
+        <v>3.42779469490051</v>
       </c>
       <c r="H477" t="s">
         <v>8</v>
@@ -12849,7 +12849,7 @@
         <v>5.46729707717896</v>
       </c>
       <c r="G480" t="n">
-        <v>3.22648882865906</v>
+        <v>3.22648906707764</v>
       </c>
       <c r="H480" t="s">
         <v>8</v>
@@ -12875,7 +12875,7 @@
         <v>5.24936294555664</v>
       </c>
       <c r="G481" t="n">
-        <v>3.09787607192993</v>
+        <v>3.09787631034851</v>
       </c>
       <c r="H481" t="s">
         <v>8</v>
@@ -12953,7 +12953,7 @@
         <v>5.57626390457153</v>
       </c>
       <c r="G484" t="n">
-        <v>3.29079532623291</v>
+        <v>3.29079484939575</v>
       </c>
       <c r="H484" t="s">
         <v>8</v>
@@ -12979,7 +12979,7 @@
         <v>5.55731296539307</v>
       </c>
       <c r="G485" t="n">
-        <v>3.27961111068726</v>
+        <v>3.27961087226868</v>
       </c>
       <c r="H485" t="s">
         <v>8</v>
@@ -13005,7 +13005,7 @@
         <v>5.62364101409912</v>
       </c>
       <c r="G486" t="n">
-        <v>3.31875419616699</v>
+        <v>3.31875395774841</v>
       </c>
       <c r="H486" t="s">
         <v>8</v>
@@ -13031,7 +13031,7 @@
         <v>5.66627979278564</v>
       </c>
       <c r="G487" t="n">
-        <v>3.34391736984253</v>
+        <v>3.34391713142395</v>
       </c>
       <c r="H487" t="s">
         <v>8</v>
@@ -13057,7 +13057,7 @@
         <v>5.62837886810303</v>
       </c>
       <c r="G488" t="n">
-        <v>3.32155013084412</v>
+        <v>3.32154989242554</v>
       </c>
       <c r="H488" t="s">
         <v>8</v>
@@ -13083,7 +13083,7 @@
         <v>5.56678915023804</v>
       </c>
       <c r="G489" t="n">
-        <v>3.28520345687866</v>
+        <v>3.28520321846008</v>
       </c>
       <c r="H489" t="s">
         <v>8</v>
@@ -13109,7 +13109,7 @@
         <v>5.59047698974609</v>
       </c>
       <c r="G490" t="n">
-        <v>3.29918241500854</v>
+        <v>3.29918217658997</v>
       </c>
       <c r="H490" t="s">
         <v>8</v>
@@ -13135,7 +13135,7 @@
         <v>5.57626390457153</v>
       </c>
       <c r="G491" t="n">
-        <v>3.29079532623291</v>
+        <v>3.29079484939575</v>
       </c>
       <c r="H491" t="s">
         <v>8</v>
@@ -13161,7 +13161,7 @@
         <v>5.50993585586548</v>
       </c>
       <c r="G492" t="n">
-        <v>3.25165152549744</v>
+        <v>3.25165176391602</v>
       </c>
       <c r="H492" t="s">
         <v>8</v>
@@ -13187,7 +13187,7 @@
         <v>5.42939615249634</v>
       </c>
       <c r="G493" t="n">
-        <v>3.20412158966064</v>
+        <v>3.20412182807922</v>
       </c>
       <c r="H493" t="s">
         <v>8</v>
@@ -13213,7 +13213,7 @@
         <v>5.52414894104004</v>
       </c>
       <c r="G494" t="n">
-        <v>3.26003980636597</v>
+        <v>3.26003956794739</v>
       </c>
       <c r="H494" t="s">
         <v>8</v>
@@ -13239,7 +13239,7 @@
         <v>5.48624801635742</v>
       </c>
       <c r="G495" t="n">
-        <v>3.23767256736755</v>
+        <v>3.23767304420471</v>
       </c>
       <c r="H495" t="s">
         <v>8</v>
@@ -13265,7 +13265,7 @@
         <v>5.41044521331787</v>
       </c>
       <c r="G496" t="n">
-        <v>3.19293785095215</v>
+        <v>3.19293808937073</v>
       </c>
       <c r="H496" t="s">
         <v>8</v>
@@ -13317,7 +13317,7 @@
         <v>5.56205081939697</v>
       </c>
       <c r="G498" t="n">
-        <v>3.28240656852722</v>
+        <v>3.28240752220154</v>
       </c>
       <c r="H498" t="s">
         <v>8</v>
@@ -13343,7 +13343,7 @@
         <v>5.64732885360718</v>
       </c>
       <c r="G499" t="n">
-        <v>3.33273339271545</v>
+        <v>3.33273410797119</v>
       </c>
       <c r="H499" t="s">
         <v>8</v>
@@ -13369,7 +13369,7 @@
         <v>5.68049287796021</v>
       </c>
       <c r="G500" t="n">
-        <v>3.35230445861816</v>
+        <v>3.35230469703674</v>
       </c>
       <c r="H500" t="s">
         <v>8</v>
@@ -13395,7 +13395,7 @@
         <v>5.52414894104004</v>
       </c>
       <c r="G501" t="n">
-        <v>3.26003980636597</v>
+        <v>3.26003956794739</v>
       </c>
       <c r="H501" t="s">
         <v>8</v>
@@ -13421,7 +13421,7 @@
         <v>5.42939615249634</v>
       </c>
       <c r="G502" t="n">
-        <v>3.20412158966064</v>
+        <v>3.20412182807922</v>
       </c>
       <c r="H502" t="s">
         <v>8</v>
@@ -13447,7 +13447,7 @@
         <v>5.27778911590576</v>
       </c>
       <c r="G503" t="n">
-        <v>3.11465191841125</v>
+        <v>3.11465167999268</v>
       </c>
       <c r="H503" t="s">
         <v>8</v>
@@ -13499,7 +13499,7 @@
         <v>5.41991996765137</v>
       </c>
       <c r="G505" t="n">
-        <v>3.19852900505066</v>
+        <v>3.1985297203064</v>
       </c>
       <c r="H505" t="s">
         <v>8</v>
@@ -13525,7 +13525,7 @@
         <v>5.23041200637817</v>
       </c>
       <c r="G506" t="n">
-        <v>3.08669257164001</v>
+        <v>3.08669233322144</v>
       </c>
       <c r="H506" t="s">
         <v>8</v>
@@ -13551,7 +13551,7 @@
         <v>5.33464193344116</v>
       </c>
       <c r="G507" t="n">
-        <v>3.14820313453674</v>
+        <v>3.14820337295532</v>
       </c>
       <c r="H507" t="s">
         <v>8</v>
@@ -13577,7 +13577,7 @@
         <v>5.68523120880127</v>
       </c>
       <c r="G508" t="n">
-        <v>3.35510087013245</v>
+        <v>3.3551013469696</v>
       </c>
       <c r="H508" t="s">
         <v>8</v>
@@ -13603,7 +13603,7 @@
         <v>5.8700008392334</v>
       </c>
       <c r="G509" t="n">
-        <v>3.46414160728455</v>
+        <v>3.46414184570312</v>
       </c>
       <c r="H509" t="s">
         <v>8</v>
@@ -13629,7 +13629,7 @@
         <v>5.68049287796021</v>
       </c>
       <c r="G510" t="n">
-        <v>3.35230445861816</v>
+        <v>3.35230469703674</v>
       </c>
       <c r="H510" t="s">
         <v>8</v>
@@ -13655,7 +13655,7 @@
         <v>5.64732885360718</v>
       </c>
       <c r="G511" t="n">
-        <v>3.33273339271545</v>
+        <v>3.33273410797119</v>
       </c>
       <c r="H511" t="s">
         <v>8</v>
@@ -13681,7 +13681,7 @@
         <v>5.68049287796021</v>
       </c>
       <c r="G512" t="n">
-        <v>3.35230445861816</v>
+        <v>3.35230469703674</v>
       </c>
       <c r="H512" t="s">
         <v>8</v>
@@ -13707,7 +13707,7 @@
         <v>5.77050876617432</v>
       </c>
       <c r="G513" t="n">
-        <v>3.4054274559021</v>
+        <v>3.40542697906494</v>
       </c>
       <c r="H513" t="s">
         <v>8</v>
@@ -13733,7 +13733,7 @@
         <v>5.89368915557861</v>
       </c>
       <c r="G514" t="n">
-        <v>3.47812151908875</v>
+        <v>3.47812080383301</v>
       </c>
       <c r="H514" t="s">
         <v>8</v>
@@ -13759,7 +13759,7 @@
         <v>5.77050876617432</v>
       </c>
       <c r="G515" t="n">
-        <v>3.4054274559021</v>
+        <v>3.40542697906494</v>
       </c>
       <c r="H515" t="s">
         <v>8</v>
@@ -13785,7 +13785,7 @@
         <v>5.73734617233276</v>
       </c>
       <c r="G516" t="n">
-        <v>3.38585615158081</v>
+        <v>3.38585686683655</v>
       </c>
       <c r="H516" t="s">
         <v>8</v>
@@ -13811,7 +13811,7 @@
         <v>5.80841112136841</v>
       </c>
       <c r="G517" t="n">
-        <v>3.42779517173767</v>
+        <v>3.42779469490051</v>
       </c>
       <c r="H517" t="s">
         <v>8</v>
@@ -13837,7 +13837,7 @@
         <v>5.7183952331543</v>
       </c>
       <c r="G518" t="n">
-        <v>3.37467265129089</v>
+        <v>3.37467288970947</v>
       </c>
       <c r="H518" t="s">
         <v>8</v>
@@ -13889,7 +13889,7 @@
         <v>6.08793497085571</v>
       </c>
       <c r="G520" t="n">
-        <v>3.59275412559509</v>
+        <v>3.59275364875793</v>
       </c>
       <c r="H520" t="s">
         <v>8</v>
@@ -13915,7 +13915,7 @@
         <v>6.19216394424438</v>
       </c>
       <c r="G521" t="n">
-        <v>3.65426421165466</v>
+        <v>3.65426445007324</v>
       </c>
       <c r="H521" t="s">
         <v>8</v>
@@ -13941,7 +13941,7 @@
         <v>6.36272096633911</v>
       </c>
       <c r="G522" t="n">
-        <v>3.75491714477539</v>
+        <v>3.75491690635681</v>
       </c>
       <c r="H522" t="s">
         <v>8</v>
@@ -13967,7 +13967,7 @@
         <v>6.2821798324585</v>
       </c>
       <c r="G523" t="n">
-        <v>3.70738649368286</v>
+        <v>3.70738673210144</v>
       </c>
       <c r="H523" t="s">
         <v>8</v>
@@ -13993,7 +13993,7 @@
         <v>6.26322984695435</v>
       </c>
       <c r="G524" t="n">
-        <v>3.69620299339294</v>
+        <v>3.6962034702301</v>
       </c>
       <c r="H524" t="s">
         <v>8</v>
@@ -14019,7 +14019,7 @@
         <v>6.30113077163696</v>
       </c>
       <c r="G525" t="n">
-        <v>3.71856999397278</v>
+        <v>3.71857023239136</v>
       </c>
       <c r="H525" t="s">
         <v>8</v>
@@ -14045,7 +14045,7 @@
         <v>6.26796722412109</v>
       </c>
       <c r="G526" t="n">
-        <v>3.69899845123291</v>
+        <v>3.69899892807007</v>
       </c>
       <c r="H526" t="s">
         <v>8</v>
@@ -14123,7 +14123,7 @@
         <v>6.43378591537476</v>
       </c>
       <c r="G529" t="n">
-        <v>3.79685568809509</v>
+        <v>3.79685544967651</v>
       </c>
       <c r="H529" t="s">
         <v>8</v>
@@ -14175,7 +14175,7 @@
         <v>6.5474910736084</v>
       </c>
       <c r="G531" t="n">
-        <v>3.86395812034607</v>
+        <v>3.86395835876465</v>
       </c>
       <c r="H531" t="s">
         <v>8</v>
@@ -14201,7 +14201,7 @@
         <v>6.40536022186279</v>
       </c>
       <c r="G532" t="n">
-        <v>3.78008079528809</v>
+        <v>3.78008055686951</v>
       </c>
       <c r="H532" t="s">
         <v>8</v>
@@ -14227,7 +14227,7 @@
         <v>6.40062284469604</v>
       </c>
       <c r="G533" t="n">
-        <v>3.77728486061096</v>
+        <v>3.77728509902954</v>
       </c>
       <c r="H533" t="s">
         <v>8</v>
@@ -14253,7 +14253,7 @@
         <v>6.42431116104126</v>
       </c>
       <c r="G534" t="n">
-        <v>3.791264295578</v>
+        <v>3.79126381874084</v>
       </c>
       <c r="H534" t="s">
         <v>8</v>
@@ -14279,7 +14279,7 @@
         <v>6.25375413894653</v>
       </c>
       <c r="G535" t="n">
-        <v>3.69061160087585</v>
+        <v>3.6906111240387</v>
       </c>
       <c r="H535" t="s">
         <v>8</v>
@@ -14305,7 +14305,7 @@
         <v>6.19216394424438</v>
       </c>
       <c r="G536" t="n">
-        <v>3.65426421165466</v>
+        <v>3.65426445007324</v>
       </c>
       <c r="H536" t="s">
         <v>8</v>
@@ -14357,7 +14357,7 @@
         <v>6.22532796859741</v>
       </c>
       <c r="G538" t="n">
-        <v>3.67383551597595</v>
+        <v>3.67383575439453</v>
       </c>
       <c r="H538" t="s">
         <v>8</v>
@@ -14383,7 +14383,7 @@
         <v>6.1353120803833</v>
       </c>
       <c r="G539" t="n">
-        <v>3.62071394920349</v>
+        <v>3.62071347236633</v>
       </c>
       <c r="H539" t="s">
         <v>8</v>
@@ -14409,7 +14409,7 @@
         <v>6.17795085906982</v>
       </c>
       <c r="G540" t="n">
-        <v>3.64587664604187</v>
+        <v>3.64587593078613</v>
       </c>
       <c r="H540" t="s">
         <v>8</v>
@@ -14435,7 +14435,7 @@
         <v>6.16847610473633</v>
       </c>
       <c r="G541" t="n">
-        <v>3.64028525352478</v>
+        <v>3.64028453826904</v>
       </c>
       <c r="H541" t="s">
         <v>8</v>
@@ -14461,7 +14461,7 @@
         <v>5.9552788734436</v>
       </c>
       <c r="G542" t="n">
-        <v>3.51446795463562</v>
+        <v>3.51446843147278</v>
       </c>
       <c r="H542" t="s">
         <v>8</v>
@@ -14487,7 +14487,7 @@
         <v>5.93632888793945</v>
       </c>
       <c r="G543" t="n">
-        <v>3.50328516960144</v>
+        <v>3.5032844543457</v>
       </c>
       <c r="H543" t="s">
         <v>8</v>
@@ -14513,7 +14513,7 @@
         <v>5.90316486358643</v>
       </c>
       <c r="G544" t="n">
-        <v>3.48371267318726</v>
+        <v>3.48371362686157</v>
       </c>
       <c r="H544" t="s">
         <v>8</v>
@@ -14565,7 +14565,7 @@
         <v>5.90316486358643</v>
       </c>
       <c r="G546" t="n">
-        <v>3.48371267318726</v>
+        <v>3.48371362686157</v>
       </c>
       <c r="H546" t="s">
         <v>8</v>
@@ -14591,7 +14591,7 @@
         <v>5.87947607040405</v>
       </c>
       <c r="G547" t="n">
-        <v>3.46973299980164</v>
+        <v>3.46973323822021</v>
       </c>
       <c r="H547" t="s">
         <v>8</v>
@@ -14617,7 +14617,7 @@
         <v>5.86526298522949</v>
       </c>
       <c r="G548" t="n">
-        <v>3.461345911026</v>
+        <v>3.46134614944458</v>
       </c>
       <c r="H548" t="s">
         <v>8</v>
@@ -14643,7 +14643,7 @@
         <v>5.90790319442749</v>
       </c>
       <c r="G549" t="n">
-        <v>3.4865095615387</v>
+        <v>3.48650932312012</v>
       </c>
       <c r="H549" t="s">
         <v>8</v>
@@ -14669,7 +14669,7 @@
         <v>5.83683681488037</v>
       </c>
       <c r="G550" t="n">
-        <v>3.44457030296326</v>
+        <v>3.4445698261261</v>
       </c>
       <c r="H550" t="s">
         <v>8</v>
@@ -14721,7 +14721,7 @@
         <v>5.92211580276489</v>
       </c>
       <c r="G552" t="n">
-        <v>3.49489665031433</v>
+        <v>3.49489688873291</v>
       </c>
       <c r="H552" t="s">
         <v>8</v>
@@ -14747,7 +14747,7 @@
         <v>5.92685317993164</v>
       </c>
       <c r="G553" t="n">
-        <v>3.49769258499146</v>
+        <v>3.49769282341003</v>
       </c>
       <c r="H553" t="s">
         <v>8</v>
@@ -14773,7 +14773,7 @@
         <v>5.8605260848999</v>
       </c>
       <c r="G554" t="n">
-        <v>3.45855069160461</v>
+        <v>3.45854997634888</v>
       </c>
       <c r="H554" t="s">
         <v>8</v>
@@ -14799,7 +14799,7 @@
         <v>5.72786998748779</v>
       </c>
       <c r="G555" t="n">
-        <v>3.3802638053894</v>
+        <v>3.38026404380798</v>
       </c>
       <c r="H555" t="s">
         <v>8</v>
@@ -14825,7 +14825,7 @@
         <v>5.60469007492065</v>
       </c>
       <c r="G556" t="n">
-        <v>3.30757069587708</v>
+        <v>3.30757117271423</v>
       </c>
       <c r="H556" t="s">
         <v>8</v>
@@ -14877,7 +14877,7 @@
         <v>5.92211580276489</v>
       </c>
       <c r="G558" t="n">
-        <v>3.49489665031433</v>
+        <v>3.49489688873291</v>
       </c>
       <c r="H558" t="s">
         <v>8</v>
@@ -14903,7 +14903,7 @@
         <v>6.11162281036377</v>
       </c>
       <c r="G559" t="n">
-        <v>3.60673260688782</v>
+        <v>3.60673308372498</v>
       </c>
       <c r="H559" t="s">
         <v>8</v>
@@ -14929,7 +14929,7 @@
         <v>6.23954105377197</v>
       </c>
       <c r="G560" t="n">
-        <v>3.68222332000732</v>
+        <v>3.6822235584259</v>
       </c>
       <c r="H560" t="s">
         <v>8</v>
@@ -14955,7 +14955,7 @@
         <v>6.14952516555786</v>
       </c>
       <c r="G561" t="n">
-        <v>3.62910127639771</v>
+        <v>3.62910079956055</v>
       </c>
       <c r="H561" t="s">
         <v>8</v>
@@ -14981,7 +14981,7 @@
         <v>5.96949291229248</v>
       </c>
       <c r="G562" t="n">
-        <v>3.52285671234131</v>
+        <v>3.52285599708557</v>
       </c>
       <c r="H562" t="s">
         <v>8</v>
@@ -15007,7 +15007,7 @@
         <v>5.88895177841187</v>
       </c>
       <c r="G563" t="n">
-        <v>3.4753258228302</v>
+        <v>3.47532534599304</v>
       </c>
       <c r="H563" t="s">
         <v>8</v>
@@ -15033,7 +15033,7 @@
         <v>5.94580411911011</v>
       </c>
       <c r="G564" t="n">
-        <v>3.50887680053711</v>
+        <v>3.50887656211853</v>
       </c>
       <c r="H564" t="s">
         <v>8</v>
@@ -15059,7 +15059,7 @@
         <v>5.90316486358643</v>
       </c>
       <c r="G565" t="n">
-        <v>3.48371267318726</v>
+        <v>3.48371362686157</v>
       </c>
       <c r="H565" t="s">
         <v>8</v>
@@ -15111,7 +15111,7 @@
         <v>5.76103401184082</v>
       </c>
       <c r="G567" t="n">
-        <v>3.50678420066833</v>
+        <v>3.50678396224976</v>
       </c>
       <c r="H567" t="s">
         <v>8</v>
@@ -15137,7 +15137,7 @@
         <v>5.77998495101929</v>
       </c>
       <c r="G568" t="n">
-        <v>3.51831912994385</v>
+        <v>3.51832008361816</v>
       </c>
       <c r="H568" t="s">
         <v>8</v>
@@ -15163,7 +15163,7 @@
         <v>5.65206718444824</v>
       </c>
       <c r="G569" t="n">
-        <v>3.44045543670654</v>
+        <v>3.44045519828796</v>
       </c>
       <c r="H569" t="s">
         <v>8</v>
@@ -15189,7 +15189,7 @@
         <v>5.46729707717896</v>
       </c>
       <c r="G570" t="n">
-        <v>3.32798409461975</v>
+        <v>3.32798433303833</v>
       </c>
       <c r="H570" t="s">
         <v>8</v>
@@ -15267,7 +15267,7 @@
         <v>5.3600001335144</v>
       </c>
       <c r="G573" t="n">
-        <v>3.26267170906067</v>
+        <v>3.26267218589783</v>
       </c>
       <c r="H573" t="s">
         <v>8</v>
@@ -15293,7 +15293,7 @@
         <v>5.51000022888184</v>
       </c>
       <c r="G574" t="n">
-        <v>3.35397791862488</v>
+        <v>3.35397815704346</v>
       </c>
       <c r="H574" t="s">
         <v>8</v>
@@ -15319,7 +15319,7 @@
         <v>5.46999979019165</v>
       </c>
       <c r="G575" t="n">
-        <v>3.32962918281555</v>
+        <v>3.32962942123413</v>
       </c>
       <c r="H575" t="s">
         <v>8</v>
@@ -15345,7 +15345,7 @@
         <v>5.75</v>
       </c>
       <c r="G576" t="n">
-        <v>3.50006747245789</v>
+        <v>3.50006723403931</v>
       </c>
       <c r="H576" t="s">
         <v>8</v>
@@ -15371,7 +15371,7 @@
         <v>5.94999980926514</v>
       </c>
       <c r="G577" t="n">
-        <v>3.62180924415588</v>
+        <v>3.62180948257446</v>
       </c>
       <c r="H577" t="s">
         <v>8</v>
@@ -15397,7 +15397,7 @@
         <v>5.94000005722046</v>
       </c>
       <c r="G578" t="n">
-        <v>3.61572241783142</v>
+        <v>3.6157214641571</v>
       </c>
       <c r="H578" t="s">
         <v>8</v>
@@ -15423,7 +15423,7 @@
         <v>5.875</v>
       </c>
       <c r="G579" t="n">
-        <v>3.5761559009552</v>
+        <v>3.57615613937378</v>
       </c>
       <c r="H579" t="s">
         <v>8</v>
@@ -15449,7 +15449,7 @@
         <v>5.81500005722046</v>
       </c>
       <c r="G580" t="n">
-        <v>3.53963327407837</v>
+        <v>3.53963398933411</v>
       </c>
       <c r="H580" t="s">
         <v>8</v>
@@ -15475,7 +15475,7 @@
         <v>5.55000019073486</v>
       </c>
       <c r="G581" t="n">
-        <v>3.37832617759705</v>
+        <v>3.37832593917847</v>
       </c>
       <c r="H581" t="s">
         <v>8</v>
@@ -15501,7 +15501,7 @@
         <v>5.73000001907349</v>
       </c>
       <c r="G582" t="n">
-        <v>3.48789381980896</v>
+        <v>3.4878933429718</v>
       </c>
       <c r="H582" t="s">
         <v>8</v>
@@ -15527,7 +15527,7 @@
         <v>5.73000001907349</v>
       </c>
       <c r="G583" t="n">
-        <v>3.48789381980896</v>
+        <v>3.4878933429718</v>
       </c>
       <c r="H583" t="s">
         <v>8</v>
@@ -15579,7 +15579,7 @@
         <v>5.8899998664856</v>
       </c>
       <c r="G585" t="n">
-        <v>3.58528661727905</v>
+        <v>3.58528637886047</v>
       </c>
       <c r="H585" t="s">
         <v>8</v>
@@ -15605,7 +15605,7 @@
         <v>5.8600001335144</v>
       </c>
       <c r="G586" t="n">
-        <v>3.56702518463135</v>
+        <v>3.56702542304993</v>
       </c>
       <c r="H586" t="s">
         <v>8</v>
@@ -15631,7 +15631,7 @@
         <v>5.82499980926514</v>
       </c>
       <c r="G587" t="n">
-        <v>3.54572057723999</v>
+        <v>3.54572033882141</v>
       </c>
       <c r="H587" t="s">
         <v>8</v>
@@ -15657,7 +15657,7 @@
         <v>6.05000019073486</v>
       </c>
       <c r="G588" t="n">
-        <v>3.68268013000488</v>
+        <v>3.68267965316772</v>
       </c>
       <c r="H588" t="s">
         <v>8</v>
@@ -15683,7 +15683,7 @@
         <v>6.08500003814697</v>
       </c>
       <c r="G589" t="n">
-        <v>3.70398497581482</v>
+        <v>3.70398449897766</v>
       </c>
       <c r="H589" t="s">
         <v>8</v>
@@ -15735,7 +15735,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G591" t="n">
-        <v>3.59137344360352</v>
+        <v>3.59137392044067</v>
       </c>
       <c r="H591" t="s">
         <v>8</v>
@@ -15761,7 +15761,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G592" t="n">
-        <v>3.59137344360352</v>
+        <v>3.59137392044067</v>
       </c>
       <c r="H592" t="s">
         <v>8</v>
@@ -15813,7 +15813,7 @@
         <v>5.96999979019165</v>
       </c>
       <c r="G594" t="n">
-        <v>3.63398289680481</v>
+        <v>3.63398313522339</v>
       </c>
       <c r="H594" t="s">
         <v>8</v>
@@ -15839,7 +15839,7 @@
         <v>5.94999980926514</v>
       </c>
       <c r="G595" t="n">
-        <v>3.62180924415588</v>
+        <v>3.62180948257446</v>
       </c>
       <c r="H595" t="s">
         <v>8</v>
@@ -15865,7 +15865,7 @@
         <v>5.82999992370605</v>
       </c>
       <c r="G596" t="n">
-        <v>3.54876351356506</v>
+        <v>3.54876399040222</v>
       </c>
       <c r="H596" t="s">
         <v>8</v>
@@ -15917,7 +15917,7 @@
         <v>6.17000007629395</v>
       </c>
       <c r="G598" t="n">
-        <v>3.75572466850281</v>
+        <v>3.75572443008423</v>
       </c>
       <c r="H598" t="s">
         <v>8</v>
@@ -15943,7 +15943,7 @@
         <v>6.1399998664856</v>
       </c>
       <c r="G599" t="n">
-        <v>3.7374632358551</v>
+        <v>3.73746347427368</v>
       </c>
       <c r="H599" t="s">
         <v>8</v>
@@ -15995,7 +15995,7 @@
         <v>5.96000003814697</v>
       </c>
       <c r="G601" t="n">
-        <v>3.62789607048035</v>
+        <v>3.62789630889893</v>
       </c>
       <c r="H601" t="s">
         <v>8</v>
@@ -16047,7 +16047,7 @@
         <v>6.1399998664856</v>
       </c>
       <c r="G603" t="n">
-        <v>3.7374632358551</v>
+        <v>3.73746347427368</v>
       </c>
       <c r="H603" t="s">
         <v>8</v>
@@ -16099,7 +16099,7 @@
         <v>5.76000022888184</v>
       </c>
       <c r="G605" t="n">
-        <v>3.50615477561951</v>
+        <v>3.50615501403809</v>
       </c>
       <c r="H605" t="s">
         <v>8</v>
@@ -16125,7 +16125,7 @@
         <v>5.74499988555908</v>
       </c>
       <c r="G606" t="n">
-        <v>3.49702405929565</v>
+        <v>3.49702429771423</v>
       </c>
       <c r="H606" t="s">
         <v>8</v>
@@ -16177,7 +16177,7 @@
         <v>5.67000007629395</v>
       </c>
       <c r="G608" t="n">
-        <v>3.45137047767639</v>
+        <v>3.45137095451355</v>
       </c>
       <c r="H608" t="s">
         <v>8</v>
@@ -16203,7 +16203,7 @@
         <v>5.67000007629395</v>
       </c>
       <c r="G609" t="n">
-        <v>3.45137047767639</v>
+        <v>3.45137095451355</v>
       </c>
       <c r="H609" t="s">
         <v>8</v>
@@ -16229,7 +16229,7 @@
         <v>5.44500017166138</v>
       </c>
       <c r="G610" t="n">
-        <v>3.31441164016724</v>
+        <v>3.31441211700439</v>
       </c>
       <c r="H610" t="s">
         <v>8</v>
@@ -16255,7 +16255,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G611" t="n">
-        <v>3.25658488273621</v>
+        <v>3.25658440589905</v>
       </c>
       <c r="H611" t="s">
         <v>8</v>
@@ -16281,7 +16281,7 @@
         <v>5.28999996185303</v>
       </c>
       <c r="G612" t="n">
-        <v>3.2200620174408</v>
+        <v>3.22006225585938</v>
       </c>
       <c r="H612" t="s">
         <v>8</v>
@@ -16307,7 +16307,7 @@
         <v>4.99599981307983</v>
       </c>
       <c r="G613" t="n">
-        <v>3.04110217094421</v>
+        <v>3.04110193252563</v>
       </c>
       <c r="H613" t="s">
         <v>8</v>
@@ -16333,7 +16333,7 @@
         <v>4.48000001907349</v>
       </c>
       <c r="G614" t="n">
-        <v>2.72700929641724</v>
+        <v>2.72700905799866</v>
       </c>
       <c r="H614" t="s">
         <v>8</v>
@@ -16359,7 +16359,7 @@
         <v>4.63000011444092</v>
       </c>
       <c r="G615" t="n">
-        <v>2.81831550598145</v>
+        <v>2.81831526756287</v>
       </c>
       <c r="H615" t="s">
         <v>8</v>
@@ -16385,7 +16385,7 @@
         <v>4.86800003051758</v>
       </c>
       <c r="G616" t="n">
-        <v>2.96318769454956</v>
+        <v>2.96318745613098</v>
       </c>
       <c r="H616" t="s">
         <v>8</v>
@@ -16411,7 +16411,7 @@
         <v>5.21999979019165</v>
       </c>
       <c r="G617" t="n">
-        <v>3.17745280265808</v>
+        <v>3.1774525642395</v>
       </c>
       <c r="H617" t="s">
         <v>8</v>
@@ -16463,7 +16463,7 @@
         <v>5.09000015258789</v>
       </c>
       <c r="G619" t="n">
-        <v>3.09832048416138</v>
+        <v>3.09832072257996</v>
       </c>
       <c r="H619" t="s">
         <v>8</v>
@@ -16489,7 +16489,7 @@
         <v>5.05999994277954</v>
       </c>
       <c r="G620" t="n">
-        <v>3.08005952835083</v>
+        <v>3.08005976676941</v>
       </c>
       <c r="H620" t="s">
         <v>8</v>
@@ -16515,7 +16515,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G621" t="n">
-        <v>3.11658143997192</v>
+        <v>3.11658215522766</v>
       </c>
       <c r="H621" t="s">
         <v>8</v>
@@ -16541,7 +16541,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G622" t="n">
-        <v>2.98266625404358</v>
+        <v>2.98266649246216</v>
       </c>
       <c r="H622" t="s">
         <v>8</v>
@@ -16567,7 +16567,7 @@
         <v>5.05999994277954</v>
       </c>
       <c r="G623" t="n">
-        <v>3.08005952835083</v>
+        <v>3.08005976676941</v>
       </c>
       <c r="H623" t="s">
         <v>8</v>
@@ -16697,7 +16697,7 @@
         <v>5.01999998092651</v>
       </c>
       <c r="G628" t="n">
-        <v>3.05571126937866</v>
+        <v>3.0557107925415</v>
       </c>
       <c r="H628" t="s">
         <v>8</v>
@@ -16723,7 +16723,7 @@
         <v>5</v>
       </c>
       <c r="G629" t="n">
-        <v>3.043536901474</v>
+        <v>3.04353713989258</v>
       </c>
       <c r="H629" t="s">
         <v>8</v>
@@ -16775,7 +16775,7 @@
         <v>4.85599994659424</v>
       </c>
       <c r="G631" t="n">
-        <v>2.95588326454163</v>
+        <v>2.95588302612305</v>
       </c>
       <c r="H631" t="s">
         <v>8</v>
@@ -16801,7 +16801,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G632" t="n">
-        <v>2.98266625404358</v>
+        <v>2.98266649246216</v>
       </c>
       <c r="H632" t="s">
         <v>8</v>
@@ -16827,7 +16827,7 @@
         <v>4.76399993896484</v>
       </c>
       <c r="G633" t="n">
-        <v>2.8998818397522</v>
+        <v>2.89988207817078</v>
       </c>
       <c r="H633" t="s">
         <v>8</v>
@@ -16853,7 +16853,7 @@
         <v>4.68599987030029</v>
       </c>
       <c r="G634" t="n">
-        <v>2.85240292549133</v>
+        <v>2.85240268707275</v>
       </c>
       <c r="H634" t="s">
         <v>8</v>
@@ -16931,7 +16931,7 @@
         <v>4.60599994659424</v>
       </c>
       <c r="G637" t="n">
-        <v>2.803706407547</v>
+        <v>2.80370616912842</v>
       </c>
       <c r="H637" t="s">
         <v>8</v>
@@ -16957,7 +16957,7 @@
         <v>4.59800004959106</v>
       </c>
       <c r="G638" t="n">
-        <v>2.79883694648743</v>
+        <v>2.79883670806885</v>
       </c>
       <c r="H638" t="s">
         <v>8</v>
@@ -16983,7 +16983,7 @@
         <v>4.65199995040894</v>
       </c>
       <c r="G639" t="n">
-        <v>2.83170676231384</v>
+        <v>2.83170700073242</v>
       </c>
       <c r="H639" t="s">
         <v>8</v>
@@ -17035,7 +17035,7 @@
         <v>4.63000011444092</v>
       </c>
       <c r="G641" t="n">
-        <v>2.81831550598145</v>
+        <v>2.81831526756287</v>
       </c>
       <c r="H641" t="s">
         <v>8</v>
@@ -17113,7 +17113,7 @@
         <v>4.73600006103516</v>
       </c>
       <c r="G644" t="n">
-        <v>2.88283824920654</v>
+        <v>2.88283801078796</v>
       </c>
       <c r="H644" t="s">
         <v>8</v>
@@ -17139,7 +17139,7 @@
         <v>4.64200019836426</v>
       </c>
       <c r="G645" t="n">
-        <v>2.82561993598938</v>
+        <v>2.82562017440796</v>
       </c>
       <c r="H645" t="s">
         <v>8</v>
@@ -17165,7 +17165,7 @@
         <v>4.64200019836426</v>
       </c>
       <c r="G646" t="n">
-        <v>2.82561993598938</v>
+        <v>2.82562017440796</v>
       </c>
       <c r="H646" t="s">
         <v>8</v>
@@ -17243,7 +17243,7 @@
         <v>4.58400011062622</v>
       </c>
       <c r="G649" t="n">
-        <v>2.79031467437744</v>
+        <v>2.79031491279602</v>
       </c>
       <c r="H649" t="s">
         <v>8</v>
@@ -17295,7 +17295,7 @@
         <v>4.55600023269653</v>
       </c>
       <c r="G651" t="n">
-        <v>2.77327108383179</v>
+        <v>2.77327084541321</v>
       </c>
       <c r="H651" t="s">
         <v>8</v>
@@ -17373,7 +17373,7 @@
         <v>4.48000001907349</v>
       </c>
       <c r="G654" t="n">
-        <v>2.72700929641724</v>
+        <v>2.72700905799866</v>
       </c>
       <c r="H654" t="s">
         <v>8</v>
@@ -17451,7 +17451,7 @@
         <v>4.57800006866455</v>
       </c>
       <c r="G657" t="n">
-        <v>2.78666257858276</v>
+        <v>2.78666234016418</v>
       </c>
       <c r="H657" t="s">
         <v>8</v>
@@ -17477,7 +17477,7 @@
         <v>4.57800006866455</v>
       </c>
       <c r="G658" t="n">
-        <v>2.78666257858276</v>
+        <v>2.78666234016418</v>
       </c>
       <c r="H658" t="s">
         <v>8</v>
@@ -17529,7 +17529,7 @@
         <v>4.63399982452393</v>
       </c>
       <c r="G660" t="n">
-        <v>2.82074975967407</v>
+        <v>2.82075023651123</v>
       </c>
       <c r="H660" t="s">
         <v>8</v>
@@ -17581,7 +17581,7 @@
         <v>4.46199989318848</v>
       </c>
       <c r="G662" t="n">
-        <v>2.71605205535889</v>
+        <v>2.71605229377747</v>
       </c>
       <c r="H662" t="s">
         <v>8</v>
@@ -17633,7 +17633,7 @@
         <v>4.54199981689453</v>
       </c>
       <c r="G664" t="n">
-        <v>2.7647488117218</v>
+        <v>2.76474857330322</v>
       </c>
       <c r="H664" t="s">
         <v>8</v>
@@ -17659,7 +17659,7 @@
         <v>4.58799982070923</v>
       </c>
       <c r="G665" t="n">
-        <v>2.79274916648865</v>
+        <v>2.79274940490723</v>
       </c>
       <c r="H665" t="s">
         <v>8</v>
@@ -17685,7 +17685,7 @@
         <v>4.55600023269653</v>
       </c>
       <c r="G666" t="n">
-        <v>2.77327108383179</v>
+        <v>2.77327084541321</v>
       </c>
       <c r="H666" t="s">
         <v>8</v>
@@ -17789,7 +17789,7 @@
         <v>4.16599988937378</v>
       </c>
       <c r="G670" t="n">
-        <v>2.53587508201599</v>
+        <v>2.53587484359741</v>
       </c>
       <c r="H670" t="s">
         <v>8</v>
@@ -17815,7 +17815,7 @@
         <v>4.13800001144409</v>
       </c>
       <c r="G671" t="n">
-        <v>2.51883125305176</v>
+        <v>2.51883101463318</v>
       </c>
       <c r="H671" t="s">
         <v>8</v>
@@ -17841,7 +17841,7 @@
         <v>4.11999988555908</v>
       </c>
       <c r="G672" t="n">
-        <v>2.50787425041199</v>
+        <v>2.50787448883057</v>
       </c>
       <c r="H672" t="s">
         <v>8</v>
@@ -17867,7 +17867,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G673" t="n">
-        <v>2.58091902732849</v>
+        <v>2.58091926574707</v>
       </c>
       <c r="H673" t="s">
         <v>8</v>
@@ -17893,7 +17893,7 @@
         <v>4.22599983215332</v>
       </c>
       <c r="G674" t="n">
-        <v>2.57239747047424</v>
+        <v>2.57239723205566</v>
       </c>
       <c r="H674" t="s">
         <v>8</v>
@@ -17971,7 +17971,7 @@
         <v>4.13800001144409</v>
       </c>
       <c r="G677" t="n">
-        <v>2.51883125305176</v>
+        <v>2.51883101463318</v>
       </c>
       <c r="H677" t="s">
         <v>8</v>
@@ -17997,7 +17997,7 @@
         <v>4.10400009155273</v>
       </c>
       <c r="G678" t="n">
-        <v>2.49813532829285</v>
+        <v>2.49813508987427</v>
       </c>
       <c r="H678" t="s">
         <v>8</v>
@@ -18023,7 +18023,7 @@
         <v>4.02199983596802</v>
       </c>
       <c r="G679" t="n">
-        <v>2.44822096824646</v>
+        <v>2.44822144508362</v>
       </c>
       <c r="H679" t="s">
         <v>8</v>
@@ -18049,7 +18049,7 @@
         <v>4.04199981689453</v>
       </c>
       <c r="G680" t="n">
-        <v>2.46039485931396</v>
+        <v>2.46039509773254</v>
       </c>
       <c r="H680" t="s">
         <v>8</v>
@@ -18075,7 +18075,7 @@
         <v>3.99799990653992</v>
       </c>
       <c r="G681" t="n">
-        <v>2.43361210823059</v>
+        <v>2.43361234664917</v>
       </c>
       <c r="H681" t="s">
         <v>8</v>
@@ -18153,7 +18153,7 @@
         <v>4.38800001144409</v>
       </c>
       <c r="G684" t="n">
-        <v>2.67100811004639</v>
+        <v>2.67100834846497</v>
       </c>
       <c r="H684" t="s">
         <v>8</v>
@@ -18179,7 +18179,7 @@
         <v>4.34999990463257</v>
       </c>
       <c r="G685" t="n">
-        <v>2.64787697792053</v>
+        <v>2.64787721633911</v>
       </c>
       <c r="H685" t="s">
         <v>8</v>
@@ -18205,7 +18205,7 @@
         <v>4.37400007247925</v>
       </c>
       <c r="G686" t="n">
-        <v>2.66248607635498</v>
+        <v>2.6624858379364</v>
       </c>
       <c r="H686" t="s">
         <v>8</v>
@@ -18283,7 +18283,7 @@
         <v>4.44199991226196</v>
       </c>
       <c r="G689" t="n">
-        <v>2.7038779258728</v>
+        <v>2.70387816429138</v>
       </c>
       <c r="H689" t="s">
         <v>8</v>
@@ -18361,7 +18361,7 @@
         <v>4.48799991607666</v>
       </c>
       <c r="G692" t="n">
-        <v>2.73187875747681</v>
+        <v>2.73187851905823</v>
       </c>
       <c r="H692" t="s">
         <v>8</v>
@@ -18387,7 +18387,7 @@
         <v>4.57399988174438</v>
       </c>
       <c r="G693" t="n">
-        <v>2.7842276096344</v>
+        <v>2.78422737121582</v>
       </c>
       <c r="H693" t="s">
         <v>8</v>
@@ -18439,7 +18439,7 @@
         <v>4.57200002670288</v>
       </c>
       <c r="G695" t="n">
-        <v>2.78301024436951</v>
+        <v>2.78301048278809</v>
       </c>
       <c r="H695" t="s">
         <v>8</v>
@@ -18465,7 +18465,7 @@
         <v>4.56799983978271</v>
       </c>
       <c r="G696" t="n">
-        <v>2.78057479858398</v>
+        <v>2.78057527542114</v>
       </c>
       <c r="H696" t="s">
         <v>8</v>
@@ -18543,7 +18543,7 @@
         <v>4.51599979400635</v>
       </c>
       <c r="G699" t="n">
-        <v>2.74892258644104</v>
+        <v>2.74892282485962</v>
       </c>
       <c r="H699" t="s">
         <v>8</v>
@@ -18569,7 +18569,7 @@
         <v>4.44399976730347</v>
       </c>
       <c r="G700" t="n">
-        <v>2.70509552955627</v>
+        <v>2.70509576797485</v>
       </c>
       <c r="H700" t="s">
         <v>8</v>
@@ -18595,7 +18595,7 @@
         <v>4.23400020599365</v>
       </c>
       <c r="G701" t="n">
-        <v>2.57726740837097</v>
+        <v>2.57726716995239</v>
       </c>
       <c r="H701" t="s">
         <v>8</v>
@@ -18647,7 +18647,7 @@
         <v>4.10200023651123</v>
       </c>
       <c r="G703" t="n">
-        <v>2.49691772460938</v>
+        <v>2.49691796302795</v>
       </c>
       <c r="H703" t="s">
         <v>8</v>
@@ -18725,7 +18725,7 @@
         <v>4.11999988555908</v>
       </c>
       <c r="G706" t="n">
-        <v>2.50787425041199</v>
+        <v>2.50787448883057</v>
       </c>
       <c r="H706" t="s">
         <v>8</v>
@@ -18777,7 +18777,7 @@
         <v>4.03000020980835</v>
       </c>
       <c r="G708" t="n">
-        <v>2.45309114456177</v>
+        <v>2.45309090614319</v>
       </c>
       <c r="H708" t="s">
         <v>8</v>
@@ -18907,7 +18907,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G713" t="n">
-        <v>2.31308794021606</v>
+        <v>2.31308770179749</v>
       </c>
       <c r="H713" t="s">
         <v>8</v>
@@ -18933,7 +18933,7 @@
         <v>3.76999998092651</v>
       </c>
       <c r="G714" t="n">
-        <v>2.2948272228241</v>
+        <v>2.29482698440552</v>
       </c>
       <c r="H714" t="s">
         <v>8</v>
@@ -18959,7 +18959,7 @@
         <v>3.79399991035461</v>
       </c>
       <c r="G715" t="n">
-        <v>2.30943584442139</v>
+        <v>2.30943560600281</v>
       </c>
       <c r="H715" t="s">
         <v>8</v>
@@ -19037,7 +19037,7 @@
         <v>3.44600009918213</v>
       </c>
       <c r="G718" t="n">
-        <v>2.09760570526123</v>
+        <v>2.09760594367981</v>
       </c>
       <c r="H718" t="s">
         <v>8</v>
@@ -19115,7 +19115,7 @@
         <v>3.48600006103516</v>
       </c>
       <c r="G721" t="n">
-        <v>2.12195420265198</v>
+        <v>2.1219539642334</v>
       </c>
       <c r="H721" t="s">
         <v>8</v>
@@ -19141,7 +19141,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G722" t="n">
-        <v>2.21569514274597</v>
+        <v>2.21569466590881</v>
       </c>
       <c r="H722" t="s">
         <v>8</v>
@@ -19193,7 +19193,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G724" t="n">
-        <v>2.25221753120422</v>
+        <v>2.25221729278564</v>
       </c>
       <c r="H724" t="s">
         <v>8</v>
@@ -19219,7 +19219,7 @@
         <v>3.75200009346008</v>
       </c>
       <c r="G725" t="n">
-        <v>2.28387022018433</v>
+        <v>2.28386998176575</v>
       </c>
       <c r="H725" t="s">
         <v>8</v>
@@ -19245,7 +19245,7 @@
         <v>3.89000010490417</v>
       </c>
       <c r="G726" t="n">
-        <v>2.36787176132202</v>
+        <v>2.36787152290344</v>
       </c>
       <c r="H726" t="s">
         <v>8</v>
@@ -19271,7 +19271,7 @@
         <v>3.7720000743866</v>
       </c>
       <c r="G727" t="n">
-        <v>2.29604458808899</v>
+        <v>2.29604434967041</v>
       </c>
       <c r="H727" t="s">
         <v>8</v>
@@ -19323,7 +19323,7 @@
         <v>3.75</v>
       </c>
       <c r="G729" t="n">
-        <v>2.28265285491943</v>
+        <v>2.28265261650085</v>
       </c>
       <c r="H729" t="s">
         <v>8</v>
@@ -19349,7 +19349,7 @@
         <v>3.77600002288818</v>
       </c>
       <c r="G730" t="n">
-        <v>2.29847931861877</v>
+        <v>2.2984790802002</v>
       </c>
       <c r="H730" t="s">
         <v>8</v>
@@ -19375,7 +19375,7 @@
         <v>3.88800001144409</v>
       </c>
       <c r="G731" t="n">
-        <v>2.36665415763855</v>
+        <v>2.36665439605713</v>
       </c>
       <c r="H731" t="s">
         <v>8</v>
@@ -19453,7 +19453,7 @@
         <v>3.5699999332428</v>
       </c>
       <c r="G734" t="n">
-        <v>2.1730854511261</v>
+        <v>2.17308521270752</v>
       </c>
       <c r="H734" t="s">
         <v>8</v>
@@ -19479,7 +19479,7 @@
         <v>3.49200010299683</v>
       </c>
       <c r="G735" t="n">
-        <v>2.12560629844666</v>
+        <v>2.12560606002808</v>
       </c>
       <c r="H735" t="s">
         <v>8</v>
@@ -19505,7 +19505,7 @@
         <v>3.4779999256134</v>
       </c>
       <c r="G736" t="n">
-        <v>2.11708402633667</v>
+        <v>2.11708426475525</v>
       </c>
       <c r="H736" t="s">
         <v>8</v>
@@ -19531,7 +19531,7 @@
         <v>3.44400000572205</v>
       </c>
       <c r="G737" t="n">
-        <v>2.09638833999634</v>
+        <v>2.09638810157776</v>
       </c>
       <c r="H737" t="s">
         <v>8</v>
@@ -19609,7 +19609,7 @@
         <v>3.25200009346008</v>
       </c>
       <c r="G740" t="n">
-        <v>1.97951662540436</v>
+        <v>1.97951650619507</v>
       </c>
       <c r="H740" t="s">
         <v>8</v>
@@ -19661,7 +19661,7 @@
         <v>3.58800005912781</v>
       </c>
       <c r="G742" t="n">
-        <v>2.18404221534729</v>
+        <v>2.18404197692871</v>
       </c>
       <c r="H742" t="s">
         <v>8</v>
@@ -19791,7 +19791,7 @@
         <v>3.75</v>
       </c>
       <c r="G747" t="n">
-        <v>2.28265285491943</v>
+        <v>2.28265261650085</v>
       </c>
       <c r="H747" t="s">
         <v>8</v>
@@ -19817,7 +19817,7 @@
         <v>3.67600011825562</v>
       </c>
       <c r="G748" t="n">
-        <v>2.2376081943512</v>
+        <v>2.23760843276978</v>
       </c>
       <c r="H748" t="s">
         <v>8</v>
@@ -19843,7 +19843,7 @@
         <v>3.66199994087219</v>
       </c>
       <c r="G749" t="n">
-        <v>2.22908639907837</v>
+        <v>2.22908663749695</v>
       </c>
       <c r="H749" t="s">
         <v>8</v>
@@ -19895,7 +19895,7 @@
         <v>3.38599991798401</v>
       </c>
       <c r="G751" t="n">
-        <v>2.06108331680298</v>
+        <v>2.06108355522156</v>
       </c>
       <c r="H751" t="s">
         <v>8</v>
@@ -19947,7 +19947,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G753" t="n">
-        <v>2.09395337104797</v>
+        <v>2.09395360946655</v>
       </c>
       <c r="H753" t="s">
         <v>8</v>
@@ -20103,7 +20103,7 @@
         <v>3.2739999294281</v>
       </c>
       <c r="G759" t="n">
-        <v>1.99290776252747</v>
+        <v>1.99290788173676</v>
       </c>
       <c r="H759" t="s">
         <v>8</v>
@@ -20129,7 +20129,7 @@
         <v>3.23799991607666</v>
       </c>
       <c r="G760" t="n">
-        <v>1.97099435329437</v>
+        <v>1.97099447250366</v>
       </c>
       <c r="H760" t="s">
         <v>8</v>
@@ -20181,7 +20181,7 @@
         <v>3.20799994468689</v>
       </c>
       <c r="G762" t="n">
-        <v>1.95273351669312</v>
+        <v>1.95273315906525</v>
       </c>
       <c r="H762" t="s">
         <v>8</v>
@@ -20207,7 +20207,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G763" t="n">
-        <v>1.96612513065338</v>
+        <v>1.96612501144409</v>
       </c>
       <c r="H763" t="s">
         <v>8</v>
@@ -20233,7 +20233,7 @@
         <v>3.27600002288818</v>
       </c>
       <c r="G764" t="n">
-        <v>1.99412572383881</v>
+        <v>1.99412536621094</v>
       </c>
       <c r="H764" t="s">
         <v>8</v>
@@ -20259,7 +20259,7 @@
         <v>3.28200006484985</v>
       </c>
       <c r="G765" t="n">
-        <v>1.9977775812149</v>
+        <v>1.99777770042419</v>
       </c>
       <c r="H765" t="s">
         <v>8</v>
@@ -20337,7 +20337,7 @@
         <v>3.36800003051758</v>
       </c>
       <c r="G768" t="n">
-        <v>2.05012655258179</v>
+        <v>2.05012679100037</v>
       </c>
       <c r="H768" t="s">
         <v>8</v>
@@ -20363,7 +20363,7 @@
         <v>3.60800004005432</v>
       </c>
       <c r="G769" t="n">
-        <v>2.19621634483337</v>
+        <v>2.19621610641479</v>
       </c>
       <c r="H769" t="s">
         <v>8</v>
@@ -20467,7 +20467,7 @@
         <v>3.43400001525879</v>
       </c>
       <c r="G773" t="n">
-        <v>2.0903012752533</v>
+        <v>2.09030103683472</v>
       </c>
       <c r="H773" t="s">
         <v>8</v>
@@ -20493,7 +20493,7 @@
         <v>3.65400004386902</v>
       </c>
       <c r="G774" t="n">
-        <v>2.2242169380188</v>
+        <v>2.22421669960022</v>
       </c>
       <c r="H774" t="s">
         <v>8</v>
@@ -20519,7 +20519,7 @@
         <v>3.59400010108948</v>
       </c>
       <c r="G775" t="n">
-        <v>2.18769478797913</v>
+        <v>2.18769454956055</v>
       </c>
       <c r="H775" t="s">
         <v>8</v>
@@ -20545,7 +20545,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G776" t="n">
-        <v>2.25221753120422</v>
+        <v>2.25221729278564</v>
       </c>
       <c r="H776" t="s">
         <v>8</v>
@@ -20571,7 +20571,7 @@
         <v>3.68199992179871</v>
       </c>
       <c r="G777" t="n">
-        <v>2.24126076698303</v>
+        <v>2.24126052856445</v>
       </c>
       <c r="H777" t="s">
         <v>8</v>
@@ -20597,7 +20597,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G778" t="n">
-        <v>2.25221753120422</v>
+        <v>2.25221729278564</v>
       </c>
       <c r="H778" t="s">
         <v>8</v>
@@ -20623,7 +20623,7 @@
         <v>3.66199994087219</v>
       </c>
       <c r="G779" t="n">
-        <v>2.22908639907837</v>
+        <v>2.22908663749695</v>
       </c>
       <c r="H779" t="s">
         <v>8</v>
@@ -20675,7 +20675,7 @@
         <v>3.73000001907349</v>
       </c>
       <c r="G781" t="n">
-        <v>2.27047872543335</v>
+        <v>2.27047848701477</v>
       </c>
       <c r="H781" t="s">
         <v>8</v>
@@ -20701,7 +20701,7 @@
         <v>3.7260000705719</v>
       </c>
       <c r="G782" t="n">
-        <v>2.26804375648499</v>
+        <v>2.26804399490356</v>
       </c>
       <c r="H782" t="s">
         <v>8</v>
@@ -20753,7 +20753,7 @@
         <v>3.63800001144409</v>
       </c>
       <c r="G784" t="n">
-        <v>2.2144775390625</v>
+        <v>2.21447777748108</v>
       </c>
       <c r="H784" t="s">
         <v>8</v>
@@ -20831,7 +20831,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G787" t="n">
-        <v>2.17917227745056</v>
+        <v>2.17917251586914</v>
       </c>
       <c r="H787" t="s">
         <v>8</v>
@@ -20883,7 +20883,7 @@
         <v>3.61800003051758</v>
       </c>
       <c r="G789" t="n">
-        <v>2.20230340957642</v>
+        <v>2.202303647995</v>
       </c>
       <c r="H789" t="s">
         <v>8</v>
@@ -20935,7 +20935,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G791" t="n">
-        <v>2.10612773895264</v>
+        <v>2.10612750053406</v>
       </c>
       <c r="H791" t="s">
         <v>8</v>
@@ -20961,7 +20961,7 @@
         <v>3.52600002288818</v>
       </c>
       <c r="G792" t="n">
-        <v>2.14630198478699</v>
+        <v>2.14630246162415</v>
       </c>
       <c r="H792" t="s">
         <v>8</v>
@@ -21013,7 +21013,7 @@
         <v>3.73000001907349</v>
       </c>
       <c r="G794" t="n">
-        <v>2.27047872543335</v>
+        <v>2.27047848701477</v>
       </c>
       <c r="H794" t="s">
         <v>8</v>
@@ -21091,7 +21091,7 @@
         <v>3.67000007629395</v>
       </c>
       <c r="G797" t="n">
-        <v>2.23395609855652</v>
+        <v>2.2339563369751</v>
       </c>
       <c r="H797" t="s">
         <v>8</v>
@@ -21117,7 +21117,7 @@
         <v>3.6159999370575</v>
       </c>
       <c r="G798" t="n">
-        <v>2.20108556747437</v>
+        <v>2.20108580589294</v>
       </c>
       <c r="H798" t="s">
         <v>8</v>
@@ -21169,7 +21169,7 @@
         <v>3.56399989128113</v>
       </c>
       <c r="G800" t="n">
-        <v>2.16943311691284</v>
+        <v>2.16943287849426</v>
       </c>
       <c r="H800" t="s">
         <v>8</v>
@@ -21195,7 +21195,7 @@
         <v>3.59400010108948</v>
       </c>
       <c r="G801" t="n">
-        <v>2.18769478797913</v>
+        <v>2.18769454956055</v>
       </c>
       <c r="H801" t="s">
         <v>8</v>
@@ -21247,7 +21247,7 @@
         <v>3.62599992752075</v>
       </c>
       <c r="G803" t="n">
-        <v>2.20717310905457</v>
+        <v>2.20717287063599</v>
       </c>
       <c r="H803" t="s">
         <v>8</v>
@@ -21351,7 +21351,7 @@
         <v>3.85400009155273</v>
       </c>
       <c r="G807" t="n">
-        <v>2.34595823287964</v>
+        <v>2.34595847129822</v>
       </c>
       <c r="H807" t="s">
         <v>8</v>
@@ -21377,7 +21377,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G808" t="n">
-        <v>2.32526183128357</v>
+        <v>2.32526206970215</v>
       </c>
       <c r="H808" t="s">
         <v>8</v>
@@ -21403,7 +21403,7 @@
         <v>3.80399990081787</v>
       </c>
       <c r="G809" t="n">
-        <v>2.31552290916443</v>
+        <v>2.31552314758301</v>
       </c>
       <c r="H809" t="s">
         <v>8</v>
@@ -21429,7 +21429,7 @@
         <v>3.7039999961853</v>
       </c>
       <c r="G810" t="n">
-        <v>2.25465226173401</v>
+        <v>2.25465202331543</v>
       </c>
       <c r="H810" t="s">
         <v>8</v>
@@ -21455,7 +21455,7 @@
         <v>3.65599989891052</v>
       </c>
       <c r="G811" t="n">
-        <v>2.22543430328369</v>
+        <v>2.22543406486511</v>
       </c>
       <c r="H811" t="s">
         <v>8</v>
@@ -21559,7 +21559,7 @@
         <v>3.61800003051758</v>
       </c>
       <c r="G815" t="n">
-        <v>2.20230340957642</v>
+        <v>2.202303647995</v>
       </c>
       <c r="H815" t="s">
         <v>8</v>
@@ -21663,7 +21663,7 @@
         <v>3.56800007820129</v>
       </c>
       <c r="G819" t="n">
-        <v>2.17186784744263</v>
+        <v>2.17186808586121</v>
       </c>
       <c r="H819" t="s">
         <v>8</v>
@@ -21689,7 +21689,7 @@
         <v>3.56800007820129</v>
       </c>
       <c r="G820" t="n">
-        <v>2.17186784744263</v>
+        <v>2.17186808586121</v>
       </c>
       <c r="H820" t="s">
         <v>8</v>
@@ -21767,7 +21767,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G823" t="n">
-        <v>2.17917227745056</v>
+        <v>2.17917251586914</v>
       </c>
       <c r="H823" t="s">
         <v>8</v>
@@ -21819,7 +21819,7 @@
         <v>3.51600003242493</v>
       </c>
       <c r="G825" t="n">
-        <v>2.1402153968811</v>
+        <v>2.14021515846252</v>
       </c>
       <c r="H825" t="s">
         <v>8</v>
@@ -21897,7 +21897,7 @@
         <v>3.73000001907349</v>
       </c>
       <c r="G828" t="n">
-        <v>2.27047872543335</v>
+        <v>2.27047848701477</v>
       </c>
       <c r="H828" t="s">
         <v>8</v>
@@ -21923,7 +21923,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G829" t="n">
-        <v>2.31308794021606</v>
+        <v>2.31308770179749</v>
       </c>
       <c r="H829" t="s">
         <v>8</v>
@@ -21975,7 +21975,7 @@
         <v>3.79399991035461</v>
       </c>
       <c r="G831" t="n">
-        <v>2.30943584442139</v>
+        <v>2.30943560600281</v>
       </c>
       <c r="H831" t="s">
         <v>8</v>
@@ -22001,7 +22001,7 @@
         <v>3.73000001907349</v>
       </c>
       <c r="G832" t="n">
-        <v>2.27047872543335</v>
+        <v>2.27047848701477</v>
       </c>
       <c r="H832" t="s">
         <v>8</v>
@@ -22027,7 +22027,7 @@
         <v>3.66400003433228</v>
       </c>
       <c r="G833" t="n">
-        <v>2.23030424118042</v>
+        <v>2.23030400276184</v>
       </c>
       <c r="H833" t="s">
         <v>8</v>
@@ -22053,7 +22053,7 @@
         <v>3.57200002670288</v>
       </c>
       <c r="G834" t="n">
-        <v>2.17430305480957</v>
+        <v>2.17430281639099</v>
       </c>
       <c r="H834" t="s">
         <v>8</v>
@@ -22157,7 +22157,7 @@
         <v>3.63599991798401</v>
       </c>
       <c r="G838" t="n">
-        <v>2.21325993537903</v>
+        <v>2.21326017379761</v>
       </c>
       <c r="H838" t="s">
         <v>8</v>
@@ -22235,7 +22235,7 @@
         <v>3.52600002288818</v>
       </c>
       <c r="G841" t="n">
-        <v>2.14630198478699</v>
+        <v>2.14630246162415</v>
       </c>
       <c r="H841" t="s">
         <v>8</v>
@@ -22261,7 +22261,7 @@
         <v>3.51799988746643</v>
       </c>
       <c r="G842" t="n">
-        <v>2.14143228530884</v>
+        <v>2.14143252372742</v>
       </c>
       <c r="H842" t="s">
         <v>8</v>
@@ -22339,7 +22339,7 @@
         <v>3.57800006866455</v>
       </c>
       <c r="G845" t="n">
-        <v>2.17795538902283</v>
+        <v>2.17795515060425</v>
       </c>
       <c r="H845" t="s">
         <v>8</v>
@@ -22365,7 +22365,7 @@
         <v>3.5460000038147</v>
       </c>
       <c r="G846" t="n">
-        <v>2.15847659111023</v>
+        <v>2.15847611427307</v>
       </c>
       <c r="H846" t="s">
         <v>8</v>
@@ -22391,7 +22391,7 @@
         <v>3.5239999294281</v>
       </c>
       <c r="G847" t="n">
-        <v>2.14508461952209</v>
+        <v>2.14508485794067</v>
       </c>
       <c r="H847" t="s">
         <v>8</v>
@@ -22417,7 +22417,7 @@
         <v>3.4779999256134</v>
       </c>
       <c r="G848" t="n">
-        <v>2.11708402633667</v>
+        <v>2.11708426475525</v>
       </c>
       <c r="H848" t="s">
         <v>8</v>
@@ -22443,7 +22443,7 @@
         <v>3.38599991798401</v>
       </c>
       <c r="G849" t="n">
-        <v>2.06108331680298</v>
+        <v>2.06108355522156</v>
       </c>
       <c r="H849" t="s">
         <v>8</v>
@@ -22495,7 +22495,7 @@
         <v>3.34200000762939</v>
       </c>
       <c r="G851" t="n">
-        <v>2.03429985046387</v>
+        <v>2.03430008888245</v>
       </c>
       <c r="H851" t="s">
         <v>8</v>
@@ -22547,7 +22547,7 @@
         <v>3.18400001525879</v>
       </c>
       <c r="G853" t="n">
-        <v>1.93812441825867</v>
+        <v>1.93812453746796</v>
       </c>
       <c r="H853" t="s">
         <v>8</v>
@@ -22573,7 +22573,7 @@
         <v>3.04800009727478</v>
       </c>
       <c r="G854" t="n">
-        <v>1.85534012317657</v>
+        <v>1.85534000396729</v>
       </c>
       <c r="H854" t="s">
         <v>8</v>
@@ -22599,7 +22599,7 @@
         <v>3.11199998855591</v>
       </c>
       <c r="G855" t="n">
-        <v>1.89429748058319</v>
+        <v>1.89429724216461</v>
       </c>
       <c r="H855" t="s">
         <v>8</v>
@@ -22625,7 +22625,7 @@
         <v>3.01600003242493</v>
       </c>
       <c r="G856" t="n">
-        <v>1.83586120605469</v>
+        <v>1.83586144447327</v>
       </c>
       <c r="H856" t="s">
         <v>8</v>
@@ -22651,7 +22651,7 @@
         <v>3.03800010681152</v>
       </c>
       <c r="G857" t="n">
-        <v>1.84925329685211</v>
+        <v>1.84925317764282</v>
       </c>
       <c r="H857" t="s">
         <v>8</v>
@@ -22703,7 +22703,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G859" t="n">
-        <v>1.84802520275116</v>
+        <v>1.84802544116974</v>
       </c>
       <c r="H859" t="s">
         <v>8</v>
@@ -22729,7 +22729,7 @@
         <v>2.8840000629425</v>
       </c>
       <c r="G860" t="n">
-        <v>1.85704004764557</v>
+        <v>1.85704040527344</v>
       </c>
       <c r="H860" t="s">
         <v>8</v>
@@ -22781,7 +22781,7 @@
         <v>2.80399990081787</v>
       </c>
       <c r="G862" t="n">
-        <v>1.80552732944489</v>
+        <v>1.8055272102356</v>
       </c>
       <c r="H862" t="s">
         <v>8</v>
@@ -22807,7 +22807,7 @@
         <v>2.76799988746643</v>
       </c>
       <c r="G863" t="n">
-        <v>1.78234648704529</v>
+        <v>1.78234672546387</v>
       </c>
       <c r="H863" t="s">
         <v>8</v>
@@ -22859,7 +22859,7 @@
         <v>2.68799996376038</v>
       </c>
       <c r="G865" t="n">
-        <v>1.73083353042603</v>
+        <v>1.7308337688446</v>
       </c>
       <c r="H865" t="s">
         <v>8</v>
@@ -22885,7 +22885,7 @@
         <v>2.6340000629425</v>
       </c>
       <c r="G866" t="n">
-        <v>1.69606256484985</v>
+        <v>1.69606244564056</v>
       </c>
       <c r="H866" t="s">
         <v>8</v>
@@ -22911,7 +22911,7 @@
         <v>2.70600008964539</v>
       </c>
       <c r="G867" t="n">
-        <v>1.74242424964905</v>
+        <v>1.74242413043976</v>
       </c>
       <c r="H867" t="s">
         <v>8</v>
@@ -22937,7 +22937,7 @@
         <v>2.71000003814697</v>
       </c>
       <c r="G868" t="n">
-        <v>1.74499952793121</v>
+        <v>1.7449996471405</v>
       </c>
       <c r="H868" t="s">
         <v>8</v>
@@ -22963,7 +22963,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G869" t="n">
-        <v>1.70636522769928</v>
+        <v>1.70636510848999</v>
       </c>
       <c r="H869" t="s">
         <v>8</v>
@@ -22989,7 +22989,7 @@
         <v>2.81399989128113</v>
       </c>
       <c r="G870" t="n">
-        <v>1.81196641921997</v>
+        <v>1.81196618080139</v>
       </c>
       <c r="H870" t="s">
         <v>8</v>
@@ -23015,7 +23015,7 @@
         <v>2.77999997138977</v>
       </c>
       <c r="G871" t="n">
-        <v>1.79007339477539</v>
+        <v>1.79007363319397</v>
       </c>
       <c r="H871" t="s">
         <v>8</v>
@@ -23041,7 +23041,7 @@
         <v>2.74000000953674</v>
       </c>
       <c r="G872" t="n">
-        <v>1.76431703567505</v>
+        <v>1.76431727409363</v>
       </c>
       <c r="H872" t="s">
         <v>8</v>
@@ -23067,7 +23067,7 @@
         <v>2.76999998092651</v>
       </c>
       <c r="G873" t="n">
-        <v>1.78363430500031</v>
+        <v>1.78363442420959</v>
       </c>
       <c r="H873" t="s">
         <v>8</v>
@@ -23093,7 +23093,7 @@
         <v>2.75399994850159</v>
       </c>
       <c r="G874" t="n">
-        <v>1.77333164215088</v>
+        <v>1.77333176136017</v>
       </c>
       <c r="H874" t="s">
         <v>8</v>
@@ -23119,7 +23119,7 @@
         <v>2.77999997138977</v>
       </c>
       <c r="G875" t="n">
-        <v>1.79007339477539</v>
+        <v>1.79007363319397</v>
       </c>
       <c r="H875" t="s">
         <v>8</v>
@@ -23171,7 +23171,7 @@
         <v>2.72199988365173</v>
       </c>
       <c r="G877" t="n">
-        <v>1.75272655487061</v>
+        <v>1.75272631645203</v>
       </c>
       <c r="H877" t="s">
         <v>8</v>
@@ -23197,7 +23197,7 @@
         <v>2.72399997711182</v>
       </c>
       <c r="G878" t="n">
-        <v>1.75401449203491</v>
+        <v>1.7540146112442</v>
       </c>
       <c r="H878" t="s">
         <v>8</v>
@@ -23223,7 +23223,7 @@
         <v>2.68799996376038</v>
       </c>
       <c r="G879" t="n">
-        <v>1.73083353042603</v>
+        <v>1.7308337688446</v>
       </c>
       <c r="H879" t="s">
         <v>8</v>
@@ -23249,7 +23249,7 @@
         <v>2.71399998664856</v>
       </c>
       <c r="G880" t="n">
-        <v>1.74757528305054</v>
+        <v>1.74757540225983</v>
       </c>
       <c r="H880" t="s">
         <v>8</v>
@@ -23301,7 +23301,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G882" t="n">
-        <v>1.84158623218536</v>
+        <v>1.84158635139465</v>
       </c>
       <c r="H882" t="s">
         <v>8</v>
@@ -23327,7 +23327,7 @@
         <v>2.9300000667572</v>
       </c>
       <c r="G883" t="n">
-        <v>1.88666033744812</v>
+        <v>1.88666021823883</v>
       </c>
       <c r="H883" t="s">
         <v>8</v>
@@ -23353,7 +23353,7 @@
         <v>2.86800003051758</v>
       </c>
       <c r="G884" t="n">
-        <v>1.84673762321472</v>
+        <v>1.8467378616333</v>
       </c>
       <c r="H884" t="s">
         <v>8</v>
@@ -23379,7 +23379,7 @@
         <v>2.82599997520447</v>
       </c>
       <c r="G885" t="n">
-        <v>1.81969332695007</v>
+        <v>1.81969356536865</v>
       </c>
       <c r="H885" t="s">
         <v>8</v>
@@ -23431,7 +23431,7 @@
         <v>2.89199995994568</v>
       </c>
       <c r="G887" t="n">
-        <v>1.86219143867493</v>
+        <v>1.86219131946564</v>
       </c>
       <c r="H887" t="s">
         <v>8</v>
@@ -23457,7 +23457,7 @@
         <v>2.98799991607666</v>
       </c>
       <c r="G888" t="n">
-        <v>1.92400681972504</v>
+        <v>1.92400705814362</v>
       </c>
       <c r="H888" t="s">
         <v>8</v>
@@ -23483,7 +23483,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G889" t="n">
-        <v>1.94461214542389</v>
+        <v>1.94461226463318</v>
       </c>
       <c r="H889" t="s">
         <v>8</v>
@@ -23509,7 +23509,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G890" t="n">
-        <v>1.99612510204315</v>
+        <v>1.99612498283386</v>
       </c>
       <c r="H890" t="s">
         <v>8</v>
@@ -23535,7 +23535,7 @@
         <v>3.21199989318848</v>
       </c>
       <c r="G891" t="n">
-        <v>2.0682430267334</v>
+        <v>2.06824326515198</v>
       </c>
       <c r="H891" t="s">
         <v>8</v>
@@ -23561,7 +23561,7 @@
         <v>3.25</v>
       </c>
       <c r="G892" t="n">
-        <v>2.09271192550659</v>
+        <v>2.09271144866943</v>
       </c>
       <c r="H892" t="s">
         <v>8</v>
@@ -23587,7 +23587,7 @@
         <v>3.25799989700317</v>
       </c>
       <c r="G893" t="n">
-        <v>2.09786295890808</v>
+        <v>2.09786319732666</v>
       </c>
       <c r="H893" t="s">
         <v>8</v>
@@ -23613,7 +23613,7 @@
         <v>3.26600003242493</v>
       </c>
       <c r="G894" t="n">
-        <v>2.10301423072815</v>
+        <v>2.10301399230957</v>
       </c>
       <c r="H894" t="s">
         <v>8</v>
@@ -23691,7 +23691,7 @@
         <v>3.24399995803833</v>
       </c>
       <c r="G897" t="n">
-        <v>2.08884859085083</v>
+        <v>2.08884835243225</v>
       </c>
       <c r="H897" t="s">
         <v>8</v>
@@ -23717,7 +23717,7 @@
         <v>3.33800005912781</v>
       </c>
       <c r="G898" t="n">
-        <v>2.14937591552734</v>
+        <v>2.14937615394592</v>
       </c>
       <c r="H898" t="s">
         <v>8</v>
@@ -23769,7 +23769,7 @@
         <v>3.32999992370605</v>
       </c>
       <c r="G900" t="n">
-        <v>2.14422464370728</v>
+        <v>2.1442244052887</v>
       </c>
       <c r="H900" t="s">
         <v>8</v>
@@ -23821,7 +23821,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G902" t="n">
-        <v>2.11202883720398</v>
+        <v>2.11202907562256</v>
       </c>
       <c r="H902" t="s">
         <v>8</v>
@@ -23847,7 +23847,7 @@
         <v>3.2039999961853</v>
       </c>
       <c r="G903" t="n">
-        <v>2.06309175491333</v>
+        <v>2.06309199333191</v>
       </c>
       <c r="H903" t="s">
         <v>8</v>
@@ -23925,7 +23925,7 @@
         <v>3.23799991607666</v>
       </c>
       <c r="G906" t="n">
-        <v>2.08498454093933</v>
+        <v>2.08498477935791</v>
       </c>
       <c r="H906" t="s">
         <v>8</v>
@@ -24003,7 +24003,7 @@
         <v>3.4300000667572</v>
       </c>
       <c r="G909" t="n">
-        <v>2.20861577987671</v>
+        <v>2.20861601829529</v>
       </c>
       <c r="H909" t="s">
         <v>8</v>
@@ -24081,7 +24081,7 @@
         <v>3.32599997520447</v>
       </c>
       <c r="G912" t="n">
-        <v>2.14164924621582</v>
+        <v>2.14164900779724</v>
       </c>
       <c r="H912" t="s">
         <v>8</v>
@@ -24185,7 +24185,7 @@
         <v>3.13599991798401</v>
       </c>
       <c r="G916" t="n">
-        <v>2.01930594444275</v>
+        <v>2.01930570602417</v>
       </c>
       <c r="H916" t="s">
         <v>8</v>
@@ -24211,7 +24211,7 @@
         <v>3.20799994468689</v>
       </c>
       <c r="G917" t="n">
-        <v>2.06566762924194</v>
+        <v>2.06566739082336</v>
       </c>
       <c r="H917" t="s">
         <v>8</v>
@@ -24237,7 +24237,7 @@
         <v>3.05999994277954</v>
       </c>
       <c r="G918" t="n">
-        <v>1.97036838531494</v>
+        <v>1.97036862373352</v>
       </c>
       <c r="H918" t="s">
         <v>8</v>
@@ -24263,7 +24263,7 @@
         <v>3.03999996185303</v>
       </c>
       <c r="G919" t="n">
-        <v>1.95749044418335</v>
+        <v>1.95749032497406</v>
       </c>
       <c r="H919" t="s">
         <v>8</v>
@@ -24289,7 +24289,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G920" t="n">
-        <v>1.97680771350861</v>
+        <v>1.9768078327179</v>
       </c>
       <c r="H920" t="s">
         <v>8</v>
@@ -24367,7 +24367,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G923" t="n">
-        <v>2.02188158035278</v>
+        <v>2.0218813419342</v>
       </c>
       <c r="H923" t="s">
         <v>8</v>
@@ -24393,7 +24393,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G924" t="n">
-        <v>2.03475975990295</v>
+        <v>2.03475999832153</v>
       </c>
       <c r="H924" t="s">
         <v>8</v>
@@ -24471,7 +24471,7 @@
         <v>3.18199992179871</v>
       </c>
       <c r="G927" t="n">
-        <v>2.04892563819885</v>
+        <v>2.04892587661743</v>
       </c>
       <c r="H927" t="s">
         <v>8</v>
@@ -24497,7 +24497,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G928" t="n">
-        <v>2.03475975990295</v>
+        <v>2.03475999832153</v>
       </c>
       <c r="H928" t="s">
         <v>8</v>
@@ -24523,7 +24523,7 @@
         <v>3.17199993133545</v>
       </c>
       <c r="G929" t="n">
-        <v>2.04248666763306</v>
+        <v>2.04248642921448</v>
       </c>
       <c r="H929" t="s">
         <v>8</v>
@@ -24549,7 +24549,7 @@
         <v>3.15199995040894</v>
       </c>
       <c r="G930" t="n">
-        <v>2.02960848808289</v>
+        <v>2.02960872650146</v>
       </c>
       <c r="H930" t="s">
         <v>8</v>
@@ -24575,7 +24575,7 @@
         <v>3.25600004196167</v>
       </c>
       <c r="G931" t="n">
-        <v>2.09657502174377</v>
+        <v>2.09657549858093</v>
       </c>
       <c r="H931" t="s">
         <v>8</v>
@@ -24601,7 +24601,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G932" t="n">
-        <v>2.11202883720398</v>
+        <v>2.11202907562256</v>
       </c>
       <c r="H932" t="s">
         <v>8</v>
@@ -24627,7 +24627,7 @@
         <v>3.25399994850159</v>
       </c>
       <c r="G933" t="n">
-        <v>2.09528756141663</v>
+        <v>2.09528732299805</v>
       </c>
       <c r="H933" t="s">
         <v>8</v>
@@ -24653,7 +24653,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G934" t="n">
-        <v>2.07983350753784</v>
+        <v>2.07983374595642</v>
       </c>
       <c r="H934" t="s">
         <v>8</v>
@@ -24757,7 +24757,7 @@
         <v>3.43400001525879</v>
       </c>
       <c r="G938" t="n">
-        <v>2.21119165420532</v>
+        <v>2.21119141578674</v>
       </c>
       <c r="H938" t="s">
         <v>8</v>
@@ -24783,7 +24783,7 @@
         <v>3.41400003433228</v>
       </c>
       <c r="G939" t="n">
-        <v>2.19831323623657</v>
+        <v>2.19831347465515</v>
       </c>
       <c r="H939" t="s">
         <v>8</v>
@@ -24809,7 +24809,7 @@
         <v>3.43799996376038</v>
       </c>
       <c r="G940" t="n">
-        <v>2.21376705169678</v>
+        <v>2.21376729011536</v>
       </c>
       <c r="H940" t="s">
         <v>8</v>
@@ -24835,7 +24835,7 @@
         <v>3.51200008392334</v>
       </c>
       <c r="G941" t="n">
-        <v>2.2614164352417</v>
+        <v>2.26141667366028</v>
       </c>
       <c r="H941" t="s">
         <v>8</v>
@@ -24861,7 +24861,7 @@
         <v>3.62800002098083</v>
       </c>
       <c r="G942" t="n">
-        <v>2.33611059188843</v>
+        <v>2.33611035346985</v>
       </c>
       <c r="H942" t="s">
         <v>8</v>
@@ -24913,7 +24913,7 @@
         <v>3.50399994850159</v>
       </c>
       <c r="G944" t="n">
-        <v>2.25626516342163</v>
+        <v>2.25626540184021</v>
       </c>
       <c r="H944" t="s">
         <v>8</v>
@@ -24991,7 +24991,7 @@
         <v>3.5460000038147</v>
       </c>
       <c r="G947" t="n">
-        <v>2.28330945968628</v>
+        <v>2.2833092212677</v>
       </c>
       <c r="H947" t="s">
         <v>8</v>
@@ -25017,7 +25017,7 @@
         <v>3.45799994468689</v>
       </c>
       <c r="G948" t="n">
-        <v>2.22664523124695</v>
+        <v>2.22664499282837</v>
       </c>
       <c r="H948" t="s">
         <v>8</v>
@@ -25043,7 +25043,7 @@
         <v>3.44400000572205</v>
       </c>
       <c r="G949" t="n">
-        <v>2.21763062477112</v>
+        <v>2.21763038635254</v>
       </c>
       <c r="H949" t="s">
         <v>8</v>
@@ -25173,7 +25173,7 @@
         <v>3.42400002479553</v>
       </c>
       <c r="G954" t="n">
-        <v>2.20475220680237</v>
+        <v>2.20475244522095</v>
       </c>
       <c r="H954" t="s">
         <v>8</v>
@@ -25277,7 +25277,7 @@
         <v>3.38199996948242</v>
       </c>
       <c r="G958" t="n">
-        <v>2.1777081489563</v>
+        <v>2.17770791053772</v>
       </c>
       <c r="H958" t="s">
         <v>8</v>
@@ -25303,7 +25303,7 @@
         <v>3.3840000629425</v>
       </c>
       <c r="G959" t="n">
-        <v>2.17899608612061</v>
+        <v>2.17899632453918</v>
       </c>
       <c r="H959" t="s">
         <v>8</v>
@@ -25329,7 +25329,7 @@
         <v>3.43799996376038</v>
       </c>
       <c r="G960" t="n">
-        <v>2.21376705169678</v>
+        <v>2.21376729011536</v>
       </c>
       <c r="H960" t="s">
         <v>8</v>
@@ -25407,7 +25407,7 @@
         <v>3.58400011062622</v>
       </c>
       <c r="G963" t="n">
-        <v>2.30777835845947</v>
+        <v>2.30777812004089</v>
       </c>
       <c r="H963" t="s">
         <v>8</v>
@@ -25459,7 +25459,7 @@
         <v>3.7720000743866</v>
       </c>
       <c r="G965" t="n">
-        <v>2.42883372306824</v>
+        <v>2.42883348464966</v>
       </c>
       <c r="H965" t="s">
         <v>8</v>
@@ -25485,7 +25485,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G966" t="n">
-        <v>2.48549771308899</v>
+        <v>2.48549747467041</v>
       </c>
       <c r="H966" t="s">
         <v>8</v>
@@ -25537,7 +25537,7 @@
         <v>3.90400004386902</v>
       </c>
       <c r="G968" t="n">
-        <v>2.51383018493652</v>
+        <v>2.51382946968079</v>
       </c>
       <c r="H968" t="s">
         <v>8</v>
@@ -25563,7 +25563,7 @@
         <v>3.96199989318848</v>
       </c>
       <c r="G969" t="n">
-        <v>2.55117630958557</v>
+        <v>2.55117654800415</v>
       </c>
       <c r="H969" t="s">
         <v>8</v>
@@ -25589,7 +25589,7 @@
         <v>3.93400001525879</v>
       </c>
       <c r="G970" t="n">
-        <v>2.53314709663391</v>
+        <v>2.53314685821533</v>
       </c>
       <c r="H970" t="s">
         <v>8</v>
@@ -25641,7 +25641,7 @@
         <v>3.97000002861023</v>
       </c>
       <c r="G972" t="n">
-        <v>2.55632781982422</v>
+        <v>2.5563280582428</v>
       </c>
       <c r="H972" t="s">
         <v>8</v>
@@ -25693,7 +25693,7 @@
         <v>4.01800012588501</v>
       </c>
       <c r="G974" t="n">
-        <v>2.58723568916321</v>
+        <v>2.58723545074463</v>
       </c>
       <c r="H974" t="s">
         <v>8</v>
@@ -25719,7 +25719,7 @@
         <v>3.99799990653992</v>
       </c>
       <c r="G975" t="n">
-        <v>2.57435727119446</v>
+        <v>2.57435750961304</v>
       </c>
       <c r="H975" t="s">
         <v>8</v>
@@ -25771,7 +25771,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G977" t="n">
-        <v>2.51125407218933</v>
+        <v>2.51125431060791</v>
       </c>
       <c r="H977" t="s">
         <v>8</v>
@@ -25797,7 +25797,7 @@
         <v>3.92400002479553</v>
       </c>
       <c r="G978" t="n">
-        <v>2.52670788764954</v>
+        <v>2.52670812606812</v>
       </c>
       <c r="H978" t="s">
         <v>8</v>
@@ -25875,7 +25875,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G981" t="n">
-        <v>2.62715816497803</v>
+        <v>2.62715792655945</v>
       </c>
       <c r="H981" t="s">
         <v>8</v>
@@ -25927,7 +25927,7 @@
         <v>4.25</v>
       </c>
       <c r="G983" t="n">
-        <v>2.73662304878235</v>
+        <v>2.73662328720093</v>
       </c>
       <c r="H983" t="s">
         <v>8</v>
@@ -25953,7 +25953,7 @@
         <v>4.34999990463257</v>
       </c>
       <c r="G984" t="n">
-        <v>2.8010139465332</v>
+        <v>2.80101418495178</v>
       </c>
       <c r="H984" t="s">
         <v>8</v>
@@ -26031,7 +26031,7 @@
         <v>4.44199991226196</v>
       </c>
       <c r="G987" t="n">
-        <v>2.86025381088257</v>
+        <v>2.86025404930115</v>
       </c>
       <c r="H987" t="s">
         <v>8</v>
@@ -26057,7 +26057,7 @@
         <v>4.52400016784668</v>
       </c>
       <c r="G988" t="n">
-        <v>2.91305470466614</v>
+        <v>2.9130551815033</v>
       </c>
       <c r="H988" t="s">
         <v>8</v>
@@ -26135,7 +26135,7 @@
         <v>4.53599977493286</v>
       </c>
       <c r="G991" t="n">
-        <v>2.92078185081482</v>
+        <v>2.92078161239624</v>
       </c>
       <c r="H991" t="s">
         <v>8</v>
@@ -26187,7 +26187,7 @@
         <v>4.65999984741211</v>
       </c>
       <c r="G993" t="n">
-        <v>3.00062656402588</v>
+        <v>3.00062680244446</v>
       </c>
       <c r="H993" t="s">
         <v>8</v>
@@ -26369,7 +26369,7 @@
         <v>4.69600009918213</v>
       </c>
       <c r="G1000" t="n">
-        <v>3.02380800247192</v>
+        <v>3.02380776405334</v>
       </c>
       <c r="H1000" t="s">
         <v>8</v>
@@ -26395,7 +26395,7 @@
         <v>4.63000011444092</v>
       </c>
       <c r="G1001" t="n">
-        <v>2.98130965232849</v>
+        <v>2.98130941390991</v>
       </c>
       <c r="H1001" t="s">
         <v>8</v>
@@ -26447,7 +26447,7 @@
         <v>4.6560001373291</v>
       </c>
       <c r="G1003" t="n">
-        <v>2.99805116653442</v>
+        <v>2.998051404953</v>
       </c>
       <c r="H1003" t="s">
         <v>8</v>
@@ -26525,7 +26525,7 @@
         <v>4.6560001373291</v>
       </c>
       <c r="G1006" t="n">
-        <v>2.99805116653442</v>
+        <v>2.998051404953</v>
       </c>
       <c r="H1006" t="s">
         <v>8</v>
@@ -26551,7 +26551,7 @@
         <v>4.67600011825562</v>
       </c>
       <c r="G1007" t="n">
-        <v>3.01092934608459</v>
+        <v>3.01092958450317</v>
       </c>
       <c r="H1007" t="s">
         <v>8</v>
@@ -26577,7 +26577,7 @@
         <v>4.67600011825562</v>
       </c>
       <c r="G1008" t="n">
-        <v>3.01092934608459</v>
+        <v>3.01092958450317</v>
       </c>
       <c r="H1008" t="s">
         <v>8</v>
@@ -26603,7 +26603,7 @@
         <v>4.71000003814697</v>
       </c>
       <c r="G1009" t="n">
-        <v>3.03282260894775</v>
+        <v>3.03282237052917</v>
       </c>
       <c r="H1009" t="s">
         <v>8</v>
@@ -26655,7 +26655,7 @@
         <v>4.63399982452393</v>
       </c>
       <c r="G1011" t="n">
-        <v>2.98388481140137</v>
+        <v>2.98388528823853</v>
       </c>
       <c r="H1011" t="s">
         <v>8</v>
@@ -26681,7 +26681,7 @@
         <v>4.61399984359741</v>
       </c>
       <c r="G1012" t="n">
-        <v>2.97100639343262</v>
+        <v>2.9710066318512</v>
       </c>
       <c r="H1012" t="s">
         <v>8</v>
@@ -26733,7 +26733,7 @@
         <v>4.65000009536743</v>
       </c>
       <c r="G1014" t="n">
-        <v>2.99418783187866</v>
+        <v>2.99418759346008</v>
       </c>
       <c r="H1014" t="s">
         <v>8</v>
@@ -26837,7 +26837,7 @@
         <v>4.42199993133545</v>
       </c>
       <c r="G1018" t="n">
-        <v>2.84737586975098</v>
+        <v>2.8473756313324</v>
       </c>
       <c r="H1018" t="s">
         <v>8</v>
@@ -26889,7 +26889,7 @@
         <v>4.53999996185303</v>
       </c>
       <c r="G1020" t="n">
-        <v>2.92335724830627</v>
+        <v>2.92335748672485</v>
       </c>
       <c r="H1020" t="s">
         <v>8</v>
@@ -26915,7 +26915,7 @@
         <v>4.62400007247925</v>
       </c>
       <c r="G1021" t="n">
-        <v>2.97744584083557</v>
+        <v>2.97744607925415</v>
       </c>
       <c r="H1021" t="s">
         <v>8</v>
@@ -26993,7 +26993,7 @@
         <v>4.57399988174438</v>
       </c>
       <c r="G1024" t="n">
-        <v>2.94525027275085</v>
+        <v>2.94525003433228</v>
       </c>
       <c r="H1024" t="s">
         <v>8</v>
@@ -27149,7 +27149,7 @@
         <v>4.63399982452393</v>
       </c>
       <c r="G1030" t="n">
-        <v>2.98388481140137</v>
+        <v>2.98388528823853</v>
       </c>
       <c r="H1030" t="s">
         <v>8</v>
@@ -27175,7 +27175,7 @@
         <v>4.57399988174438</v>
       </c>
       <c r="G1031" t="n">
-        <v>2.94525027275085</v>
+        <v>2.94525003433228</v>
       </c>
       <c r="H1031" t="s">
         <v>8</v>
@@ -27253,7 +27253,7 @@
         <v>4.5479998588562</v>
       </c>
       <c r="G1034" t="n">
-        <v>2.92850828170776</v>
+        <v>2.92850875854492</v>
       </c>
       <c r="H1034" t="s">
         <v>8</v>
@@ -27305,7 +27305,7 @@
         <v>4.57000017166138</v>
       </c>
       <c r="G1036" t="n">
-        <v>2.9426748752594</v>
+        <v>2.94267511367798</v>
       </c>
       <c r="H1036" t="s">
         <v>8</v>
@@ -27357,7 +27357,7 @@
         <v>4.37799978256226</v>
       </c>
       <c r="G1038" t="n">
-        <v>2.81904363632202</v>
+        <v>2.8190438747406</v>
       </c>
       <c r="H1038" t="s">
         <v>8</v>
@@ -27383,7 +27383,7 @@
         <v>4.44199991226196</v>
       </c>
       <c r="G1039" t="n">
-        <v>2.86025381088257</v>
+        <v>2.86025404930115</v>
       </c>
       <c r="H1039" t="s">
         <v>8</v>
@@ -27461,7 +27461,7 @@
         <v>4.51399993896484</v>
       </c>
       <c r="G1042" t="n">
-        <v>2.90661597251892</v>
+        <v>2.90661573410034</v>
       </c>
       <c r="H1042" t="s">
         <v>8</v>
@@ -27487,7 +27487,7 @@
         <v>4.54199981689453</v>
       </c>
       <c r="G1043" t="n">
-        <v>2.924644947052</v>
+        <v>2.92464470863342</v>
       </c>
       <c r="H1043" t="s">
         <v>8</v>
@@ -27513,7 +27513,7 @@
         <v>4.57200002670288</v>
       </c>
       <c r="G1044" t="n">
-        <v>2.94396233558655</v>
+        <v>2.94396281242371</v>
       </c>
       <c r="H1044" t="s">
         <v>8</v>
@@ -27539,7 +27539,7 @@
         <v>4.51000022888184</v>
       </c>
       <c r="G1045" t="n">
-        <v>2.90404033660889</v>
+        <v>2.90404009819031</v>
       </c>
       <c r="H1045" t="s">
         <v>8</v>
@@ -27565,7 +27565,7 @@
         <v>4.47200012207031</v>
       </c>
       <c r="G1046" t="n">
-        <v>2.87957143783569</v>
+        <v>2.87957167625427</v>
       </c>
       <c r="H1046" t="s">
         <v>8</v>
@@ -27617,7 +27617,7 @@
         <v>4.48600006103516</v>
       </c>
       <c r="G1048" t="n">
-        <v>2.8885862827301</v>
+        <v>2.88858604431152</v>
       </c>
       <c r="H1048" t="s">
         <v>8</v>
@@ -27773,7 +27773,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G1054" t="n">
-        <v>2.73018360137939</v>
+        <v>2.73018383979797</v>
       </c>
       <c r="H1054" t="s">
         <v>8</v>
@@ -27825,7 +27825,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G1056" t="n">
-        <v>2.65935397148132</v>
+        <v>2.65935373306274</v>
       </c>
       <c r="H1056" t="s">
         <v>8</v>
@@ -27877,7 +27877,7 @@
         <v>3.7279999256134</v>
       </c>
       <c r="G1058" t="n">
-        <v>2.40050148963928</v>
+        <v>2.4005012512207</v>
       </c>
       <c r="H1058" t="s">
         <v>8</v>
@@ -27903,7 +27903,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G1059" t="n">
-        <v>2.36959385871887</v>
+        <v>2.36959362030029</v>
       </c>
       <c r="H1059" t="s">
         <v>8</v>
@@ -27981,7 +27981,7 @@
         <v>3.30599999427795</v>
       </c>
       <c r="G1062" t="n">
-        <v>2.12877082824707</v>
+        <v>2.12877058982849</v>
       </c>
       <c r="H1062" t="s">
         <v>8</v>
@@ -28007,7 +28007,7 @@
         <v>2.98600006103516</v>
       </c>
       <c r="G1063" t="n">
-        <v>1.92271947860718</v>
+        <v>1.92271935939789</v>
       </c>
       <c r="H1063" t="s">
         <v>8</v>
@@ -28033,7 +28033,7 @@
         <v>2.82200002670288</v>
       </c>
       <c r="G1064" t="n">
-        <v>1.81711769104004</v>
+        <v>1.81711781024933</v>
       </c>
       <c r="H1064" t="s">
         <v>8</v>
@@ -28059,7 +28059,7 @@
         <v>2.87199997901917</v>
       </c>
       <c r="G1065" t="n">
-        <v>1.84931337833405</v>
+        <v>1.84931349754333</v>
       </c>
       <c r="H1065" t="s">
         <v>8</v>
@@ -28085,7 +28085,7 @@
         <v>2.43799996376038</v>
       </c>
       <c r="G1066" t="n">
-        <v>1.56985557079315</v>
+        <v>1.56985569000244</v>
       </c>
       <c r="H1066" t="s">
         <v>8</v>
@@ -28111,7 +28111,7 @@
         <v>2.57399988174438</v>
       </c>
       <c r="G1067" t="n">
-        <v>1.65742778778076</v>
+        <v>1.65742766857147</v>
       </c>
       <c r="H1067" t="s">
         <v>8</v>
@@ -28267,7 +28267,7 @@
         <v>2.31599998474121</v>
       </c>
       <c r="G1073" t="n">
-        <v>1.49129843711853</v>
+        <v>1.49129855632782</v>
       </c>
       <c r="H1073" t="s">
         <v>8</v>
@@ -28293,7 +28293,7 @@
         <v>2.42199993133545</v>
       </c>
       <c r="G1074" t="n">
-        <v>1.55955338478088</v>
+        <v>1.5595531463623</v>
       </c>
       <c r="H1074" t="s">
         <v>8</v>
@@ -28319,7 +28319,7 @@
         <v>2.41799998283386</v>
       </c>
       <c r="G1075" t="n">
-        <v>1.55697751045227</v>
+        <v>1.55697762966156</v>
       </c>
       <c r="H1075" t="s">
         <v>8</v>
@@ -28345,7 +28345,7 @@
         <v>2.71399998664856</v>
       </c>
       <c r="G1076" t="n">
-        <v>1.74757528305054</v>
+        <v>1.74757540225983</v>
       </c>
       <c r="H1076" t="s">
         <v>8</v>
@@ -28371,7 +28371,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G1077" t="n">
-        <v>1.60333907604218</v>
+        <v>1.60333931446075</v>
       </c>
       <c r="H1077" t="s">
         <v>8</v>
@@ -28423,7 +28423,7 @@
         <v>2.44799995422363</v>
       </c>
       <c r="G1079" t="n">
-        <v>1.57629477977753</v>
+        <v>1.57629489898682</v>
       </c>
       <c r="H1079" t="s">
         <v>8</v>
@@ -28449,7 +28449,7 @@
         <v>2.48600006103516</v>
       </c>
       <c r="G1080" t="n">
-        <v>1.60076367855072</v>
+        <v>1.60076344013214</v>
       </c>
       <c r="H1080" t="s">
         <v>8</v>
@@ -28475,7 +28475,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G1081" t="n">
-        <v>1.6290956735611</v>
+        <v>1.62909579277039</v>
       </c>
       <c r="H1081" t="s">
         <v>8</v>
@@ -28501,7 +28501,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G1082" t="n">
-        <v>1.60333907604218</v>
+        <v>1.60333931446075</v>
       </c>
       <c r="H1082" t="s">
         <v>8</v>
@@ -28527,7 +28527,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G1083" t="n">
-        <v>1.66129112243652</v>
+        <v>1.66129100322723</v>
       </c>
       <c r="H1083" t="s">
         <v>8</v>
@@ -28553,7 +28553,7 @@
         <v>2.81399989128113</v>
       </c>
       <c r="G1084" t="n">
-        <v>1.81196641921997</v>
+        <v>1.81196618080139</v>
       </c>
       <c r="H1084" t="s">
         <v>8</v>
@@ -28579,7 +28579,7 @@
         <v>2.91599988937378</v>
       </c>
       <c r="G1085" t="n">
-        <v>1.87764537334442</v>
+        <v>1.87764549255371</v>
       </c>
       <c r="H1085" t="s">
         <v>8</v>
@@ -28605,7 +28605,7 @@
         <v>2.97399997711182</v>
       </c>
       <c r="G1086" t="n">
-        <v>1.91499221324921</v>
+        <v>1.91499209403992</v>
       </c>
       <c r="H1086" t="s">
         <v>8</v>
@@ -28631,7 +28631,7 @@
         <v>2.96199989318848</v>
       </c>
       <c r="G1087" t="n">
-        <v>1.90726542472839</v>
+        <v>1.9072653055191</v>
       </c>
       <c r="H1087" t="s">
         <v>8</v>
@@ -28657,7 +28657,7 @@
         <v>2.87599992752075</v>
       </c>
       <c r="G1088" t="n">
-        <v>1.85188865661621</v>
+        <v>1.8518887758255</v>
       </c>
       <c r="H1088" t="s">
         <v>8</v>
@@ -28709,7 +28709,7 @@
         <v>2.83599996566772</v>
       </c>
       <c r="G1090" t="n">
-        <v>1.82613229751587</v>
+        <v>1.82613253593445</v>
       </c>
       <c r="H1090" t="s">
         <v>8</v>
@@ -28761,7 +28761,7 @@
         <v>2.68199992179871</v>
       </c>
       <c r="G1092" t="n">
-        <v>1.72696995735168</v>
+        <v>1.7269698381424</v>
       </c>
       <c r="H1092" t="s">
         <v>8</v>
@@ -28787,7 +28787,7 @@
         <v>2.69400000572205</v>
       </c>
       <c r="G1093" t="n">
-        <v>1.73469686508179</v>
+        <v>1.73469698429108</v>
       </c>
       <c r="H1093" t="s">
         <v>8</v>
@@ -28813,7 +28813,7 @@
         <v>2.7739999294281</v>
       </c>
       <c r="G1094" t="n">
-        <v>1.78621006011963</v>
+        <v>1.78620994091034</v>
       </c>
       <c r="H1094" t="s">
         <v>8</v>
@@ -28839,7 +28839,7 @@
         <v>2.74200010299683</v>
       </c>
       <c r="G1095" t="n">
-        <v>1.76560485363007</v>
+        <v>1.76560497283936</v>
       </c>
       <c r="H1095" t="s">
         <v>8</v>
@@ -28969,7 +28969,7 @@
         <v>3.21000003814697</v>
       </c>
       <c r="G1100" t="n">
-        <v>2.06695508956909</v>
+        <v>2.06695532798767</v>
       </c>
       <c r="H1100" t="s">
         <v>8</v>
@@ -29021,7 +29021,7 @@
         <v>3.07800006866455</v>
       </c>
       <c r="G1102" t="n">
-        <v>1.98195898532867</v>
+        <v>1.98195910453796</v>
       </c>
       <c r="H1102" t="s">
         <v>8</v>
@@ -29073,7 +29073,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G1104" t="n">
-        <v>2.18929839134216</v>
+        <v>2.18929886817932</v>
       </c>
       <c r="H1104" t="s">
         <v>8</v>
@@ -29125,7 +29125,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G1106" t="n">
-        <v>2.17642045021057</v>
+        <v>2.17642021179199</v>
       </c>
       <c r="H1106" t="s">
         <v>8</v>
@@ -29151,7 +29151,7 @@
         <v>3.33800005912781</v>
       </c>
       <c r="G1107" t="n">
-        <v>2.14937591552734</v>
+        <v>2.14937615394592</v>
       </c>
       <c r="H1107" t="s">
         <v>8</v>
@@ -29177,7 +29177,7 @@
         <v>3.24399995803833</v>
       </c>
       <c r="G1108" t="n">
-        <v>2.08884859085083</v>
+        <v>2.08884835243225</v>
       </c>
       <c r="H1108" t="s">
         <v>8</v>
@@ -29229,7 +29229,7 @@
         <v>3.36199998855591</v>
       </c>
       <c r="G1110" t="n">
-        <v>2.30693340301514</v>
+        <v>2.30693364143372</v>
       </c>
       <c r="H1110" t="s">
         <v>8</v>
@@ -29255,7 +29255,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G1111" t="n">
-        <v>2.33300852775574</v>
+        <v>2.33300876617432</v>
       </c>
       <c r="H1111" t="s">
         <v>8</v>
@@ -29281,7 +29281,7 @@
         <v>3.37199997901917</v>
       </c>
       <c r="G1112" t="n">
-        <v>2.31379556655884</v>
+        <v>2.31379532814026</v>
       </c>
       <c r="H1112" t="s">
         <v>8</v>
@@ -29333,7 +29333,7 @@
         <v>3.32200002670288</v>
       </c>
       <c r="G1114" t="n">
-        <v>2.27948641777039</v>
+        <v>2.27948617935181</v>
       </c>
       <c r="H1114" t="s">
         <v>8</v>
@@ -29515,7 +29515,7 @@
         <v>3.89199995994568</v>
       </c>
       <c r="G1121" t="n">
-        <v>2.67060828208923</v>
+        <v>2.67060852050781</v>
       </c>
       <c r="H1121" t="s">
         <v>8</v>
@@ -29541,7 +29541,7 @@
         <v>3.88199996948242</v>
       </c>
       <c r="G1122" t="n">
-        <v>2.66374659538269</v>
+        <v>2.66374635696411</v>
       </c>
       <c r="H1122" t="s">
         <v>8</v>
@@ -29645,7 +29645,7 @@
         <v>4.25</v>
       </c>
       <c r="G1126" t="n">
-        <v>2.91626071929932</v>
+        <v>2.91626024246216</v>
       </c>
       <c r="H1126" t="s">
         <v>8</v>
@@ -29671,7 +29671,7 @@
         <v>4.25</v>
       </c>
       <c r="G1127" t="n">
-        <v>2.91626071929932</v>
+        <v>2.91626024246216</v>
       </c>
       <c r="H1127" t="s">
         <v>8</v>
@@ -29697,7 +29697,7 @@
         <v>3.97199988365173</v>
       </c>
       <c r="G1128" t="n">
-        <v>2.72550296783447</v>
+        <v>2.72550272941589</v>
       </c>
       <c r="H1128" t="s">
         <v>8</v>
@@ -29749,7 +29749,7 @@
         <v>3.98200011253357</v>
       </c>
       <c r="G1130" t="n">
-        <v>2.73236489295959</v>
+        <v>2.73236465454102</v>
       </c>
       <c r="H1130" t="s">
         <v>8</v>
@@ -29853,7 +29853,7 @@
         <v>3.90599989891052</v>
       </c>
       <c r="G1134" t="n">
-        <v>2.68021488189697</v>
+        <v>2.68021512031555</v>
       </c>
       <c r="H1134" t="s">
         <v>8</v>
@@ -30061,7 +30061,7 @@
         <v>3.87400007247925</v>
       </c>
       <c r="G1142" t="n">
-        <v>2.65825724601746</v>
+        <v>2.65825700759888</v>
       </c>
       <c r="H1142" t="s">
         <v>8</v>
@@ -30113,7 +30113,7 @@
         <v>4.05399990081787</v>
       </c>
       <c r="G1144" t="n">
-        <v>2.78176927566528</v>
+        <v>2.78176951408386</v>
       </c>
       <c r="H1144" t="s">
         <v>8</v>
@@ -30191,7 +30191,7 @@
         <v>4.08599996566772</v>
       </c>
       <c r="G1147" t="n">
-        <v>2.80372714996338</v>
+        <v>2.8037269115448</v>
       </c>
       <c r="H1147" t="s">
         <v>8</v>
@@ -30217,7 +30217,7 @@
         <v>3.95199990272522</v>
       </c>
       <c r="G1148" t="n">
-        <v>2.71177911758423</v>
+        <v>2.71177935600281</v>
       </c>
       <c r="H1148" t="s">
         <v>8</v>
@@ -30243,7 +30243,7 @@
         <v>3.96600008010864</v>
       </c>
       <c r="G1149" t="n">
-        <v>2.72138547897339</v>
+        <v>2.72138571739197</v>
       </c>
       <c r="H1149" t="s">
         <v>8</v>
@@ -30295,7 +30295,7 @@
         <v>4.03599977493286</v>
       </c>
       <c r="G1151" t="n">
-        <v>2.76941823959351</v>
+        <v>2.76941800117493</v>
       </c>
       <c r="H1151" t="s">
         <v>8</v>
@@ -30399,7 +30399,7 @@
         <v>4</v>
       </c>
       <c r="G1155" t="n">
-        <v>2.74471569061279</v>
+        <v>2.74471592903137</v>
       </c>
       <c r="H1155" t="s">
         <v>8</v>
@@ -30477,7 +30477,7 @@
         <v>4.19000005722046</v>
       </c>
       <c r="G1158" t="n">
-        <v>2.87508940696716</v>
+        <v>2.87508964538574</v>
       </c>
       <c r="H1158" t="s">
         <v>8</v>
@@ -30503,7 +30503,7 @@
         <v>4.08400011062622</v>
       </c>
       <c r="G1159" t="n">
-        <v>2.80235505104065</v>
+        <v>2.80235481262207</v>
       </c>
       <c r="H1159" t="s">
         <v>8</v>
@@ -30685,7 +30685,7 @@
         <v>3.86199998855591</v>
       </c>
       <c r="G1166" t="n">
-        <v>2.6500232219696</v>
+        <v>2.65002298355103</v>
       </c>
       <c r="H1166" t="s">
         <v>8</v>
@@ -30711,7 +30711,7 @@
         <v>3.91799998283386</v>
       </c>
       <c r="G1167" t="n">
-        <v>2.6884491443634</v>
+        <v>2.68844938278198</v>
       </c>
       <c r="H1167" t="s">
         <v>8</v>
@@ -30763,7 +30763,7 @@
         <v>3.90599989891052</v>
       </c>
       <c r="G1169" t="n">
-        <v>2.68021488189697</v>
+        <v>2.68021512031555</v>
       </c>
       <c r="H1169" t="s">
         <v>8</v>
@@ -30789,7 +30789,7 @@
         <v>3.9539999961853</v>
       </c>
       <c r="G1170" t="n">
-        <v>2.71315145492554</v>
+        <v>2.71315169334412</v>
       </c>
       <c r="H1170" t="s">
         <v>8</v>
@@ -30841,7 +30841,7 @@
         <v>3.94199991226196</v>
       </c>
       <c r="G1172" t="n">
-        <v>2.70491743087769</v>
+        <v>2.70491719245911</v>
       </c>
       <c r="H1172" t="s">
         <v>8</v>
@@ -30997,7 +30997,7 @@
         <v>3.74600005149841</v>
       </c>
       <c r="G1178" t="n">
-        <v>2.57042622566223</v>
+        <v>2.57042598724365</v>
       </c>
       <c r="H1178" t="s">
         <v>8</v>
@@ -31101,7 +31101,7 @@
         <v>3.78800010681152</v>
       </c>
       <c r="G1182" t="n">
-        <v>2.59924602508545</v>
+        <v>2.59924578666687</v>
       </c>
       <c r="H1182" t="s">
         <v>8</v>
@@ -31257,7 +31257,7 @@
         <v>3.7039999961853</v>
       </c>
       <c r="G1188" t="n">
-        <v>2.54160690307617</v>
+        <v>2.54160666465759</v>
       </c>
       <c r="H1188" t="s">
         <v>8</v>
@@ -31283,7 +31283,7 @@
         <v>3.65400004386902</v>
       </c>
       <c r="G1189" t="n">
-        <v>2.50729775428772</v>
+        <v>2.5072979927063</v>
       </c>
       <c r="H1189" t="s">
         <v>8</v>
@@ -31309,7 +31309,7 @@
         <v>3.78399991989136</v>
       </c>
       <c r="G1190" t="n">
-        <v>2.59650111198425</v>
+        <v>2.59650087356567</v>
       </c>
       <c r="H1190" t="s">
         <v>8</v>
@@ -31361,7 +31361,7 @@
         <v>3.7279999256134</v>
       </c>
       <c r="G1192" t="n">
-        <v>2.55807518959045</v>
+        <v>2.55807495117188</v>
       </c>
       <c r="H1192" t="s">
         <v>8</v>
@@ -31413,7 +31413,7 @@
         <v>3.71799993515015</v>
       </c>
       <c r="G1194" t="n">
-        <v>2.55121326446533</v>
+        <v>2.55121302604675</v>
       </c>
       <c r="H1194" t="s">
         <v>8</v>
@@ -31465,7 +31465,7 @@
         <v>3.67600011825562</v>
       </c>
       <c r="G1196" t="n">
-        <v>2.52239370346069</v>
+        <v>2.52239394187927</v>
       </c>
       <c r="H1196" t="s">
         <v>8</v>
@@ -31491,7 +31491,7 @@
         <v>3.66599988937378</v>
       </c>
       <c r="G1197" t="n">
-        <v>2.51553201675415</v>
+        <v>2.51553177833557</v>
       </c>
       <c r="H1197" t="s">
         <v>8</v>
@@ -31543,7 +31543,7 @@
         <v>3.66400003433228</v>
       </c>
       <c r="G1199" t="n">
-        <v>2.51415991783142</v>
+        <v>2.51415944099426</v>
       </c>
       <c r="H1199" t="s">
         <v>8</v>
@@ -31569,7 +31569,7 @@
         <v>3.53600001335144</v>
       </c>
       <c r="G1200" t="n">
-        <v>2.42632842063904</v>
+        <v>2.4263288974762</v>
       </c>
       <c r="H1200" t="s">
         <v>8</v>
@@ -31595,7 +31595,7 @@
         <v>3.48600006103516</v>
       </c>
       <c r="G1201" t="n">
-        <v>2.39201974868774</v>
+        <v>2.39201998710632</v>
       </c>
       <c r="H1201" t="s">
         <v>8</v>
@@ -31673,7 +31673,7 @@
         <v>3.4300000667572</v>
       </c>
       <c r="G1204" t="n">
-        <v>2.35359358787537</v>
+        <v>2.35359406471252</v>
       </c>
       <c r="H1204" t="s">
         <v>8</v>
@@ -31751,7 +31751,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G1207" t="n">
-        <v>2.29869937896729</v>
+        <v>2.29869914054871</v>
       </c>
       <c r="H1207" t="s">
         <v>8</v>
@@ -31803,7 +31803,7 @@
         <v>3.28999996185303</v>
       </c>
       <c r="G1209" t="n">
-        <v>2.25752830505371</v>
+        <v>2.25752854347229</v>
       </c>
       <c r="H1209" t="s">
         <v>8</v>
@@ -31959,7 +31959,7 @@
         <v>3.53200006484985</v>
       </c>
       <c r="G1215" t="n">
-        <v>2.423583984375</v>
+        <v>2.42358422279358</v>
       </c>
       <c r="H1215" t="s">
         <v>8</v>
@@ -31985,7 +31985,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G1216" t="n">
-        <v>2.33300852775574</v>
+        <v>2.33300876617432</v>
       </c>
       <c r="H1216" t="s">
         <v>8</v>
@@ -32011,7 +32011,7 @@
         <v>3.44199991226196</v>
       </c>
       <c r="G1217" t="n">
-        <v>2.36182808876038</v>
+        <v>2.3618278503418</v>
       </c>
       <c r="H1217" t="s">
         <v>8</v>
@@ -32089,7 +32089,7 @@
         <v>3.55800008773804</v>
       </c>
       <c r="G1220" t="n">
-        <v>2.44142460823059</v>
+        <v>2.44142484664917</v>
       </c>
       <c r="H1220" t="s">
         <v>8</v>
@@ -32115,7 +32115,7 @@
         <v>3.59599995613098</v>
       </c>
       <c r="G1221" t="n">
-        <v>2.46749949455261</v>
+        <v>2.46749925613403</v>
       </c>
       <c r="H1221" t="s">
         <v>8</v>
@@ -32141,7 +32141,7 @@
         <v>3.67600011825562</v>
       </c>
       <c r="G1222" t="n">
-        <v>2.52239370346069</v>
+        <v>2.52239394187927</v>
       </c>
       <c r="H1222" t="s">
         <v>8</v>
@@ -32167,7 +32167,7 @@
         <v>3.56800007820129</v>
       </c>
       <c r="G1223" t="n">
-        <v>2.44828629493713</v>
+        <v>2.44828653335571</v>
       </c>
       <c r="H1223" t="s">
         <v>8</v>
@@ -32193,7 +32193,7 @@
         <v>3.52800011634827</v>
       </c>
       <c r="G1224" t="n">
-        <v>2.42083930969238</v>
+        <v>2.42083978652954</v>
       </c>
       <c r="H1224" t="s">
         <v>8</v>
@@ -32219,7 +32219,7 @@
         <v>3.42600011825562</v>
       </c>
       <c r="G1225" t="n">
-        <v>2.35084915161133</v>
+        <v>2.35084939002991</v>
       </c>
       <c r="H1225" t="s">
         <v>8</v>
@@ -32297,7 +32297,7 @@
         <v>3.13599991798401</v>
       </c>
       <c r="G1228" t="n">
-        <v>2.15185713768005</v>
+        <v>2.15185689926147</v>
       </c>
       <c r="H1228" t="s">
         <v>8</v>
@@ -32349,7 +32349,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G1230" t="n">
-        <v>2.29869937896729</v>
+        <v>2.29869914054871</v>
       </c>
       <c r="H1230" t="s">
         <v>8</v>
@@ -32375,7 +32375,7 @@
         <v>3.40599989891052</v>
       </c>
       <c r="G1231" t="n">
-        <v>2.33712553977966</v>
+        <v>2.33712530136108</v>
       </c>
       <c r="H1231" t="s">
         <v>8</v>
@@ -32401,7 +32401,7 @@
         <v>3.49600005149841</v>
       </c>
       <c r="G1232" t="n">
-        <v>2.39888167381287</v>
+        <v>2.39888143539429</v>
       </c>
       <c r="H1232" t="s">
         <v>8</v>
@@ -32427,7 +32427,7 @@
         <v>3.57599997520447</v>
       </c>
       <c r="G1233" t="n">
-        <v>2.45377588272095</v>
+        <v>2.45377564430237</v>
       </c>
       <c r="H1233" t="s">
         <v>8</v>
@@ -32479,7 +32479,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G1235" t="n">
-        <v>2.42907333374023</v>
+        <v>2.42907357215881</v>
       </c>
       <c r="H1235" t="s">
         <v>8</v>
@@ -32531,7 +32531,7 @@
         <v>3.52800011634827</v>
       </c>
       <c r="G1237" t="n">
-        <v>2.42083930969238</v>
+        <v>2.42083978652954</v>
       </c>
       <c r="H1237" t="s">
         <v>8</v>
@@ -32609,7 +32609,7 @@
         <v>3.67199993133545</v>
       </c>
       <c r="G1240" t="n">
-        <v>2.51964926719666</v>
+        <v>2.5196487903595</v>
       </c>
       <c r="H1240" t="s">
         <v>8</v>
@@ -32661,7 +32661,7 @@
         <v>3.71600008010864</v>
       </c>
       <c r="G1242" t="n">
-        <v>2.54984092712402</v>
+        <v>2.54984068870544</v>
       </c>
       <c r="H1242" t="s">
         <v>8</v>
@@ -32739,7 +32739,7 @@
         <v>3.78800010681152</v>
       </c>
       <c r="G1245" t="n">
-        <v>2.59924602508545</v>
+        <v>2.59924578666687</v>
       </c>
       <c r="H1245" t="s">
         <v>8</v>
@@ -32791,7 +32791,7 @@
         <v>3.7739999294281</v>
       </c>
       <c r="G1247" t="n">
-        <v>2.58963942527771</v>
+        <v>2.58963918685913</v>
       </c>
       <c r="H1247" t="s">
         <v>8</v>
@@ -32817,7 +32817,7 @@
         <v>3.7279999256134</v>
       </c>
       <c r="G1248" t="n">
-        <v>2.55807518959045</v>
+        <v>2.55807495117188</v>
       </c>
       <c r="H1248" t="s">
         <v>8</v>
@@ -32869,7 +32869,7 @@
         <v>3.67199993133545</v>
       </c>
       <c r="G1250" t="n">
-        <v>2.51964926719666</v>
+        <v>2.5196487903595</v>
       </c>
       <c r="H1250" t="s">
         <v>8</v>
@@ -32947,7 +32947,7 @@
         <v>3.61400008201599</v>
       </c>
       <c r="G1253" t="n">
-        <v>2.47985053062439</v>
+        <v>2.47985076904297</v>
       </c>
       <c r="H1253" t="s">
         <v>8</v>
@@ -32999,7 +32999,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G1255" t="n">
-        <v>2.45652031898499</v>
+        <v>2.45652055740356</v>
       </c>
       <c r="H1255" t="s">
         <v>8</v>
@@ -33051,7 +33051,7 @@
         <v>3.58599996566772</v>
       </c>
       <c r="G1257" t="n">
-        <v>2.46063756942749</v>
+        <v>2.46063780784607</v>
       </c>
       <c r="H1257" t="s">
         <v>8</v>
@@ -33129,7 +33129,7 @@
         <v>3.59800004959106</v>
       </c>
       <c r="G1260" t="n">
-        <v>2.46887183189392</v>
+        <v>2.46887159347534</v>
       </c>
       <c r="H1260" t="s">
         <v>8</v>
@@ -33155,7 +33155,7 @@
         <v>3.59800004959106</v>
       </c>
       <c r="G1261" t="n">
-        <v>2.46887183189392</v>
+        <v>2.46887159347534</v>
       </c>
       <c r="H1261" t="s">
         <v>8</v>
@@ -33181,7 +33181,7 @@
         <v>3.68199992179871</v>
       </c>
       <c r="G1262" t="n">
-        <v>2.5265109539032</v>
+        <v>2.52651047706604</v>
       </c>
       <c r="H1262" t="s">
         <v>8</v>
@@ -33233,7 +33233,7 @@
         <v>3.90599989891052</v>
       </c>
       <c r="G1264" t="n">
-        <v>2.68021488189697</v>
+        <v>2.68021512031555</v>
       </c>
       <c r="H1264" t="s">
         <v>8</v>
@@ -33259,7 +33259,7 @@
         <v>3.8659999370575</v>
       </c>
       <c r="G1265" t="n">
-        <v>2.65276741981506</v>
+        <v>2.65276765823364</v>
       </c>
       <c r="H1265" t="s">
         <v>8</v>
@@ -33389,7 +33389,7 @@
         <v>3.88199996948242</v>
       </c>
       <c r="G1270" t="n">
-        <v>2.66374659538269</v>
+        <v>2.66374635696411</v>
       </c>
       <c r="H1270" t="s">
         <v>8</v>
@@ -33467,7 +33467,7 @@
         <v>4.03399991989136</v>
       </c>
       <c r="G1273" t="n">
-        <v>2.76804566383362</v>
+        <v>2.7680459022522</v>
       </c>
       <c r="H1273" t="s">
         <v>8</v>
@@ -33519,7 +33519,7 @@
         <v>4.11399984359741</v>
       </c>
       <c r="G1275" t="n">
-        <v>2.82294011116028</v>
+        <v>2.8229398727417</v>
       </c>
       <c r="H1275" t="s">
         <v>8</v>
@@ -33545,7 +33545,7 @@
         <v>4.15999984741211</v>
       </c>
       <c r="G1276" t="n">
-        <v>2.85450434684753</v>
+        <v>2.85450410842896</v>
       </c>
       <c r="H1276" t="s">
         <v>8</v>
@@ -33571,7 +33571,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G1277" t="n">
-        <v>2.89567518234253</v>
+        <v>2.89567494392395</v>
       </c>
       <c r="H1277" t="s">
         <v>8</v>
@@ -33597,7 +33597,7 @@
         <v>4.14200019836426</v>
       </c>
       <c r="G1278" t="n">
-        <v>2.84215307235718</v>
+        <v>2.84215331077576</v>
       </c>
       <c r="H1278" t="s">
         <v>8</v>
@@ -33623,7 +33623,7 @@
         <v>4.09200000762939</v>
       </c>
       <c r="G1279" t="n">
-        <v>2.80784440040588</v>
+        <v>2.8078441619873</v>
       </c>
       <c r="H1279" t="s">
         <v>8</v>
@@ -33701,7 +33701,7 @@
         <v>4.08599996566772</v>
       </c>
       <c r="G1282" t="n">
-        <v>2.80372714996338</v>
+        <v>2.8037269115448</v>
       </c>
       <c r="H1282" t="s">
         <v>8</v>
@@ -33831,7 +33831,7 @@
         <v>3.93400001525879</v>
       </c>
       <c r="G1287" t="n">
-        <v>2.69942784309387</v>
+        <v>2.69942808151245</v>
       </c>
       <c r="H1287" t="s">
         <v>8</v>
@@ -33935,7 +33935,7 @@
         <v>3.94799995422363</v>
       </c>
       <c r="G1291" t="n">
-        <v>2.70903444290161</v>
+        <v>2.70903468132019</v>
       </c>
       <c r="H1291" t="s">
         <v>8</v>
@@ -33961,7 +33961,7 @@
         <v>4</v>
       </c>
       <c r="G1292" t="n">
-        <v>2.74471569061279</v>
+        <v>2.74471592903137</v>
       </c>
       <c r="H1292" t="s">
         <v>8</v>
@@ -33987,7 +33987,7 @@
         <v>4.12400007247925</v>
       </c>
       <c r="G1293" t="n">
-        <v>2.8298020362854</v>
+        <v>2.82980179786682</v>
       </c>
       <c r="H1293" t="s">
         <v>8</v>
@@ -34013,7 +34013,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G1294" t="n">
-        <v>2.90939831733704</v>
+        <v>2.90939855575562</v>
       </c>
       <c r="H1294" t="s">
         <v>8</v>
@@ -34039,7 +34039,7 @@
         <v>4.19600009918213</v>
       </c>
       <c r="G1295" t="n">
-        <v>2.87920689582825</v>
+        <v>2.87920641899109</v>
       </c>
       <c r="H1295" t="s">
         <v>8</v>
@@ -34065,7 +34065,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G1296" t="n">
-        <v>2.95056962966919</v>
+        <v>2.95056986808777</v>
       </c>
       <c r="H1296" t="s">
         <v>8</v>
@@ -34117,7 +34117,7 @@
         <v>4.2039999961853</v>
       </c>
       <c r="G1298" t="n">
-        <v>2.88469624519348</v>
+        <v>2.8846960067749</v>
       </c>
       <c r="H1298" t="s">
         <v>8</v>
@@ -34143,7 +34143,7 @@
         <v>4.2039999961853</v>
       </c>
       <c r="G1299" t="n">
-        <v>2.88469624519348</v>
+        <v>2.8846960067749</v>
       </c>
       <c r="H1299" t="s">
         <v>8</v>
@@ -34169,7 +34169,7 @@
         <v>4.25</v>
       </c>
       <c r="G1300" t="n">
-        <v>2.91626071929932</v>
+        <v>2.91626024246216</v>
       </c>
       <c r="H1300" t="s">
         <v>8</v>
@@ -34195,7 +34195,7 @@
         <v>4.24399995803833</v>
       </c>
       <c r="G1301" t="n">
-        <v>2.91214323043823</v>
+        <v>2.91214346885681</v>
       </c>
       <c r="H1301" t="s">
         <v>8</v>
@@ -34221,7 +34221,7 @@
         <v>4.17399978637695</v>
       </c>
       <c r="G1302" t="n">
-        <v>2.86411094665527</v>
+        <v>2.86411070823669</v>
       </c>
       <c r="H1302" t="s">
         <v>8</v>
@@ -34247,7 +34247,7 @@
         <v>4.06199979782104</v>
       </c>
       <c r="G1303" t="n">
-        <v>2.7872588634491</v>
+        <v>2.78725862503052</v>
       </c>
       <c r="H1303" t="s">
         <v>8</v>
@@ -34299,7 +34299,7 @@
         <v>3.98600006103516</v>
       </c>
       <c r="G1305" t="n">
-        <v>2.73510909080505</v>
+        <v>2.73510932922363</v>
       </c>
       <c r="H1305" t="s">
         <v>8</v>
@@ -34325,7 +34325,7 @@
         <v>4.05999994277954</v>
       </c>
       <c r="G1306" t="n">
-        <v>2.78588676452637</v>
+        <v>2.78588652610779</v>
       </c>
       <c r="H1306" t="s">
         <v>8</v>
@@ -34351,7 +34351,7 @@
         <v>3.97199988365173</v>
       </c>
       <c r="G1307" t="n">
-        <v>2.72550296783447</v>
+        <v>2.72550272941589</v>
       </c>
       <c r="H1307" t="s">
         <v>8</v>
@@ -34403,7 +34403,7 @@
         <v>3.98600006103516</v>
       </c>
       <c r="G1309" t="n">
-        <v>2.73510909080505</v>
+        <v>2.73510932922363</v>
       </c>
       <c r="H1309" t="s">
         <v>8</v>
@@ -34429,7 +34429,7 @@
         <v>3.9779999256134</v>
       </c>
       <c r="G1310" t="n">
-        <v>2.72961974143982</v>
+        <v>2.7296199798584</v>
       </c>
       <c r="H1310" t="s">
         <v>8</v>
@@ -34455,7 +34455,7 @@
         <v>4.18200016021729</v>
       </c>
       <c r="G1311" t="n">
-        <v>2.86960053443909</v>
+        <v>2.86960029602051</v>
       </c>
       <c r="H1311" t="s">
         <v>8</v>
@@ -34507,7 +34507,7 @@
         <v>4.16400003433228</v>
       </c>
       <c r="G1313" t="n">
-        <v>2.85724902153015</v>
+        <v>2.85724925994873</v>
       </c>
       <c r="H1313" t="s">
         <v>8</v>
@@ -34559,7 +34559,7 @@
         <v>4.12400007247925</v>
       </c>
       <c r="G1315" t="n">
-        <v>2.8298020362854</v>
+        <v>2.82980179786682</v>
       </c>
       <c r="H1315" t="s">
         <v>8</v>
@@ -34585,7 +34585,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G1316" t="n">
-        <v>2.8682279586792</v>
+        <v>2.86822819709778</v>
       </c>
       <c r="H1316" t="s">
         <v>8</v>
@@ -34611,7 +34611,7 @@
         <v>4.23199987411499</v>
       </c>
       <c r="G1317" t="n">
-        <v>2.9039089679718</v>
+        <v>2.90390920639038</v>
       </c>
       <c r="H1317" t="s">
         <v>8</v>
@@ -34637,7 +34637,7 @@
         <v>4.39400005340576</v>
       </c>
       <c r="G1318" t="n">
-        <v>3.01507019996643</v>
+        <v>3.01507043838501</v>
       </c>
       <c r="H1318" t="s">
         <v>8</v>
@@ -34663,7 +34663,7 @@
         <v>4.33799982070923</v>
       </c>
       <c r="G1319" t="n">
-        <v>2.97664403915405</v>
+        <v>2.97664427757263</v>
       </c>
       <c r="H1319" t="s">
         <v>8</v>
@@ -34689,7 +34689,7 @@
         <v>4.35599994659424</v>
       </c>
       <c r="G1320" t="n">
-        <v>2.98899531364441</v>
+        <v>2.98899555206299</v>
       </c>
       <c r="H1320" t="s">
         <v>8</v>
@@ -34715,7 +34715,7 @@
         <v>4.51000022888184</v>
       </c>
       <c r="G1321" t="n">
-        <v>3.0946671962738</v>
+        <v>3.09466695785522</v>
       </c>
       <c r="H1321" t="s">
         <v>8</v>
@@ -34741,7 +34741,7 @@
         <v>4.51800012588501</v>
       </c>
       <c r="G1322" t="n">
-        <v>3.10015654563904</v>
+        <v>3.10015630722046</v>
       </c>
       <c r="H1322" t="s">
         <v>8</v>
@@ -34793,7 +34793,7 @@
         <v>4.48199987411499</v>
       </c>
       <c r="G1324" t="n">
-        <v>3.07545399665833</v>
+        <v>3.07545375823975</v>
       </c>
       <c r="H1324" t="s">
         <v>8</v>
@@ -34819,7 +34819,7 @@
         <v>4.41400003433228</v>
       </c>
       <c r="G1325" t="n">
-        <v>3.0287938117981</v>
+        <v>3.02879405021667</v>
       </c>
       <c r="H1325" t="s">
         <v>8</v>
@@ -34897,7 +34897,7 @@
         <v>4.45599985122681</v>
       </c>
       <c r="G1328" t="n">
-        <v>3.05761337280273</v>
+        <v>3.05761361122131</v>
       </c>
       <c r="H1328" t="s">
         <v>8</v>
@@ -34975,7 +34975,7 @@
         <v>4.45800018310547</v>
       </c>
       <c r="G1331" t="n">
-        <v>3.0589861869812</v>
+        <v>3.05898594856262</v>
       </c>
       <c r="H1331" t="s">
         <v>8</v>
@@ -35001,7 +35001,7 @@
         <v>4.42999982833862</v>
       </c>
       <c r="G1332" t="n">
-        <v>3.03977227210999</v>
+        <v>3.03977251052856</v>
       </c>
       <c r="H1332" t="s">
         <v>8</v>
@@ -35053,7 +35053,7 @@
         <v>4.49700021743774</v>
       </c>
       <c r="G1334" t="n">
-        <v>3.0857470035553</v>
+        <v>3.08574676513672</v>
       </c>
       <c r="H1334" t="s">
         <v>8</v>
@@ -35079,7 +35079,7 @@
         <v>4.47499990463257</v>
       </c>
       <c r="G1335" t="n">
-        <v>3.07065033912659</v>
+        <v>3.07065057754517</v>
       </c>
       <c r="H1335" t="s">
         <v>8</v>
@@ -35131,7 +35131,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G1337" t="n">
-        <v>3.06035804748535</v>
+        <v>3.06035828590393</v>
       </c>
       <c r="H1337" t="s">
         <v>8</v>
@@ -35157,7 +35157,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G1338" t="n">
-        <v>3.01918721199036</v>
+        <v>3.01918745040894</v>
       </c>
       <c r="H1338" t="s">
         <v>8</v>
@@ -35287,7 +35287,7 @@
         <v>4.43599987030029</v>
       </c>
       <c r="G1343" t="n">
-        <v>3.04388976097107</v>
+        <v>3.04388952255249</v>
       </c>
       <c r="H1343" t="s">
         <v>8</v>
@@ -35313,7 +35313,7 @@
         <v>4.44099998474121</v>
       </c>
       <c r="G1344" t="n">
-        <v>3.04732036590576</v>
+        <v>3.04732060432434</v>
       </c>
       <c r="H1344" t="s">
         <v>8</v>
@@ -35339,7 +35339,7 @@
         <v>4.31099987030029</v>
       </c>
       <c r="G1345" t="n">
-        <v>2.95811724662781</v>
+        <v>2.95811748504639</v>
       </c>
       <c r="H1345" t="s">
         <v>8</v>
@@ -35365,7 +35365,7 @@
         <v>4.24399995803833</v>
       </c>
       <c r="G1346" t="n">
-        <v>2.91214323043823</v>
+        <v>2.91214346885681</v>
       </c>
       <c r="H1346" t="s">
         <v>8</v>
@@ -35391,7 +35391,7 @@
         <v>4.24200010299683</v>
       </c>
       <c r="G1347" t="n">
-        <v>2.91077136993408</v>
+        <v>2.91077089309692</v>
       </c>
       <c r="H1347" t="s">
         <v>8</v>
@@ -35417,7 +35417,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G1348" t="n">
-        <v>2.88195109367371</v>
+        <v>2.88195133209229</v>
       </c>
       <c r="H1348" t="s">
         <v>8</v>
@@ -35443,7 +35443,7 @@
         <v>4.2810001373291</v>
       </c>
       <c r="G1349" t="n">
-        <v>2.9375319480896</v>
+        <v>2.93753218650818</v>
       </c>
       <c r="H1349" t="s">
         <v>8</v>
@@ -35469,7 +35469,7 @@
         <v>4.24300003051758</v>
       </c>
       <c r="G1350" t="n">
-        <v>2.91145753860474</v>
+        <v>2.91145730018616</v>
       </c>
       <c r="H1350" t="s">
         <v>8</v>
@@ -35495,7 +35495,7 @@
         <v>4.23199987411499</v>
       </c>
       <c r="G1351" t="n">
-        <v>2.9039089679718</v>
+        <v>2.90390920639038</v>
       </c>
       <c r="H1351" t="s">
         <v>8</v>
@@ -35521,7 +35521,7 @@
         <v>4.24200010299683</v>
       </c>
       <c r="G1352" t="n">
-        <v>2.91077136993408</v>
+        <v>2.91077089309692</v>
       </c>
       <c r="H1352" t="s">
         <v>8</v>
@@ -35573,7 +35573,7 @@
         <v>4.31099987030029</v>
       </c>
       <c r="G1354" t="n">
-        <v>2.95811724662781</v>
+        <v>2.95811748504639</v>
       </c>
       <c r="H1354" t="s">
         <v>8</v>
@@ -35599,7 +35599,7 @@
         <v>4.19099998474121</v>
       </c>
       <c r="G1355" t="n">
-        <v>2.8757758140564</v>
+        <v>2.87577629089355</v>
       </c>
       <c r="H1355" t="s">
         <v>8</v>
@@ -35625,7 +35625,7 @@
         <v>4.26800012588501</v>
       </c>
       <c r="G1356" t="n">
-        <v>2.92861175537109</v>
+        <v>2.92861151695251</v>
       </c>
       <c r="H1356" t="s">
         <v>8</v>
@@ -35651,7 +35651,7 @@
         <v>4.24499988555908</v>
       </c>
       <c r="G1357" t="n">
-        <v>2.91282916069031</v>
+        <v>2.91282939910889</v>
       </c>
       <c r="H1357" t="s">
         <v>8</v>
@@ -35703,7 +35703,7 @@
         <v>4.41900014877319</v>
       </c>
       <c r="G1359" t="n">
-        <v>3.03222489356995</v>
+        <v>3.03222465515137</v>
       </c>
       <c r="H1359" t="s">
         <v>8</v>
@@ -35807,7 +35807,7 @@
         <v>4.49300003051758</v>
       </c>
       <c r="G1363" t="n">
-        <v>3.08300185203552</v>
+        <v>3.0830020904541</v>
       </c>
       <c r="H1363" t="s">
         <v>8</v>
@@ -35859,7 +35859,7 @@
         <v>4.61999988555908</v>
       </c>
       <c r="G1365" t="n">
-        <v>3.17014670372009</v>
+        <v>3.17014646530151</v>
       </c>
       <c r="H1365" t="s">
         <v>8</v>
@@ -35885,7 +35885,7 @@
         <v>4.49399995803833</v>
       </c>
       <c r="G1366" t="n">
-        <v>3.08368825912476</v>
+        <v>3.08368849754333</v>
       </c>
       <c r="H1366" t="s">
         <v>8</v>
@@ -35911,7 +35911,7 @@
         <v>4.50600004196167</v>
       </c>
       <c r="G1367" t="n">
-        <v>3.09192204475403</v>
+        <v>3.09192228317261</v>
       </c>
       <c r="H1367" t="s">
         <v>8</v>
@@ -35989,7 +35989,7 @@
         <v>4.27099990844727</v>
       </c>
       <c r="G1370" t="n">
-        <v>3.08177089691162</v>
+        <v>3.0817711353302</v>
       </c>
       <c r="H1370" t="s">
         <v>8</v>
@@ -36015,7 +36015,7 @@
         <v>4.2960000038147</v>
       </c>
       <c r="G1371" t="n">
-        <v>3.09981036186218</v>
+        <v>3.0998101234436</v>
       </c>
       <c r="H1371" t="s">
         <v>8</v>
@@ -36041,7 +36041,7 @@
         <v>4.28999996185303</v>
       </c>
       <c r="G1372" t="n">
-        <v>3.09548091888428</v>
+        <v>3.0954806804657</v>
       </c>
       <c r="H1372" t="s">
         <v>8</v>
@@ -36119,7 +36119,7 @@
         <v>4.39300012588501</v>
       </c>
       <c r="G1375" t="n">
-        <v>3.16980147361755</v>
+        <v>3.16980123519897</v>
       </c>
       <c r="H1375" t="s">
         <v>8</v>
@@ -36197,7 +36197,7 @@
         <v>4.39300012588501</v>
       </c>
       <c r="G1378" t="n">
-        <v>3.16980147361755</v>
+        <v>3.16980123519897</v>
       </c>
       <c r="H1378" t="s">
         <v>8</v>
@@ -36327,7 +36327,7 @@
         <v>4.53299999237061</v>
       </c>
       <c r="G1383" t="n">
-        <v>3.27081894874573</v>
+        <v>3.27081918716431</v>
       </c>
       <c r="H1383" t="s">
         <v>8</v>
@@ -36353,7 +36353,7 @@
         <v>4.51800012588501</v>
       </c>
       <c r="G1384" t="n">
-        <v>3.25999593734741</v>
+        <v>3.25999569892883</v>
       </c>
       <c r="H1384" t="s">
         <v>8</v>
@@ -36379,7 +36379,7 @@
         <v>4.42999982833862</v>
       </c>
       <c r="G1385" t="n">
-        <v>3.19649839401245</v>
+        <v>3.19649863243103</v>
       </c>
       <c r="H1385" t="s">
         <v>8</v>
@@ -36405,7 +36405,7 @@
         <v>4.47399997711182</v>
       </c>
       <c r="G1386" t="n">
-        <v>3.22824692726135</v>
+        <v>3.22824716567993</v>
       </c>
       <c r="H1386" t="s">
         <v>8</v>
@@ -36431,7 +36431,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G1387" t="n">
-        <v>3.20371437072754</v>
+        <v>3.20371413230896</v>
       </c>
       <c r="H1387" t="s">
         <v>8</v>
@@ -36509,7 +36509,7 @@
         <v>4.29899978637695</v>
       </c>
       <c r="G1390" t="n">
-        <v>3.10197448730469</v>
+        <v>3.10197472572327</v>
       </c>
       <c r="H1390" t="s">
         <v>8</v>
@@ -36561,7 +36561,7 @@
         <v>4.30999994277954</v>
       </c>
       <c r="G1392" t="n">
-        <v>3.10991191864014</v>
+        <v>3.10991168022156</v>
       </c>
       <c r="H1392" t="s">
         <v>8</v>
@@ -36743,7 +36743,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G1399" t="n">
-        <v>3.04497170448303</v>
+        <v>3.04497146606445</v>
       </c>
       <c r="H1399" t="s">
         <v>8</v>
@@ -36769,7 +36769,7 @@
         <v>4.19299983978271</v>
       </c>
       <c r="G1400" t="n">
-        <v>3.02548933029175</v>
+        <v>3.02548956871033</v>
       </c>
       <c r="H1400" t="s">
         <v>8</v>
@@ -36795,7 +36795,7 @@
         <v>4.1710000038147</v>
       </c>
       <c r="G1401" t="n">
-        <v>3.00961518287659</v>
+        <v>3.00961542129517</v>
       </c>
       <c r="H1401" t="s">
         <v>8</v>
@@ -36821,7 +36821,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G1402" t="n">
-        <v>2.96560049057007</v>
+        <v>2.96560025215149</v>
       </c>
       <c r="H1402" t="s">
         <v>8</v>
@@ -36847,7 +36847,7 @@
         <v>4.18300008773804</v>
       </c>
       <c r="G1403" t="n">
-        <v>3.0182740688324</v>
+        <v>3.01827430725098</v>
       </c>
       <c r="H1403" t="s">
         <v>8</v>
@@ -36873,7 +36873,7 @@
         <v>4.23099994659424</v>
       </c>
       <c r="G1404" t="n">
-        <v>3.05290865898132</v>
+        <v>3.0529088973999</v>
       </c>
       <c r="H1404" t="s">
         <v>8</v>
@@ -37159,7 +37159,7 @@
         <v>4.11299991607666</v>
       </c>
       <c r="G1415" t="n">
-        <v>2.96776509284973</v>
+        <v>2.96776485443115</v>
       </c>
       <c r="H1415" t="s">
         <v>8</v>
@@ -37185,7 +37185,7 @@
         <v>4.13399982452393</v>
       </c>
       <c r="G1416" t="n">
-        <v>2.98291778564453</v>
+        <v>2.98291802406311</v>
       </c>
       <c r="H1416" t="s">
         <v>8</v>
@@ -37211,7 +37211,7 @@
         <v>4.15700006484985</v>
       </c>
       <c r="G1417" t="n">
-        <v>2.99951386451721</v>
+        <v>2.99951362609863</v>
       </c>
       <c r="H1417" t="s">
         <v>8</v>
@@ -37237,7 +37237,7 @@
         <v>4.15799999237061</v>
       </c>
       <c r="G1418" t="n">
-        <v>3.00023508071899</v>
+        <v>3.00023531913757</v>
       </c>
       <c r="H1418" t="s">
         <v>8</v>
@@ -37315,7 +37315,7 @@
         <v>4.18300008773804</v>
       </c>
       <c r="G1421" t="n">
-        <v>3.0182740688324</v>
+        <v>3.01827430725098</v>
       </c>
       <c r="H1421" t="s">
         <v>8</v>
@@ -37367,7 +37367,7 @@
         <v>4.2519998550415</v>
       </c>
       <c r="G1423" t="n">
-        <v>3.0680615901947</v>
+        <v>3.06806135177612</v>
       </c>
       <c r="H1423" t="s">
         <v>8</v>
@@ -37393,7 +37393,7 @@
         <v>4.28999996185303</v>
       </c>
       <c r="G1424" t="n">
-        <v>3.09548091888428</v>
+        <v>3.0954806804657</v>
       </c>
       <c r="H1424" t="s">
         <v>8</v>
@@ -37419,7 +37419,7 @@
         <v>4.29899978637695</v>
       </c>
       <c r="G1425" t="n">
-        <v>3.10197448730469</v>
+        <v>3.10197472572327</v>
       </c>
       <c r="H1425" t="s">
         <v>8</v>
@@ -37471,7 +37471,7 @@
         <v>4.2960000038147</v>
       </c>
       <c r="G1427" t="n">
-        <v>3.09981036186218</v>
+        <v>3.0998101234436</v>
       </c>
       <c r="H1427" t="s">
         <v>8</v>
@@ -37523,7 +37523,7 @@
         <v>4.28999996185303</v>
       </c>
       <c r="G1429" t="n">
-        <v>3.09548091888428</v>
+        <v>3.0954806804657</v>
       </c>
       <c r="H1429" t="s">
         <v>8</v>
@@ -37549,7 +37549,7 @@
         <v>4.30999994277954</v>
       </c>
       <c r="G1430" t="n">
-        <v>3.10991191864014</v>
+        <v>3.10991168022156</v>
       </c>
       <c r="H1430" t="s">
         <v>8</v>
@@ -37601,7 +37601,7 @@
         <v>4.28900003433228</v>
       </c>
       <c r="G1432" t="n">
-        <v>3.09475922584534</v>
+        <v>3.09475946426392</v>
       </c>
       <c r="H1432" t="s">
         <v>8</v>
@@ -37653,7 +37653,7 @@
         <v>4.29199981689453</v>
       </c>
       <c r="G1434" t="n">
-        <v>3.096923828125</v>
+        <v>3.09692358970642</v>
       </c>
       <c r="H1434" t="s">
         <v>8</v>
@@ -37731,7 +37731,7 @@
         <v>4.31099987030029</v>
       </c>
       <c r="G1437" t="n">
-        <v>3.1106333732605</v>
+        <v>3.11063361167908</v>
       </c>
       <c r="H1437" t="s">
         <v>8</v>
@@ -37757,7 +37757,7 @@
         <v>4.33500003814697</v>
       </c>
       <c r="G1438" t="n">
-        <v>3.12795090675354</v>
+        <v>3.12795066833496</v>
       </c>
       <c r="H1438" t="s">
         <v>8</v>
@@ -37835,7 +37835,7 @@
         <v>4.39200019836426</v>
       </c>
       <c r="G1441" t="n">
-        <v>3.16907954216003</v>
+        <v>3.16907978057861</v>
       </c>
       <c r="H1441" t="s">
         <v>8</v>
@@ -37861,7 +37861,7 @@
         <v>4.39200019836426</v>
       </c>
       <c r="G1442" t="n">
-        <v>3.16907954216003</v>
+        <v>3.16907978057861</v>
       </c>
       <c r="H1442" t="s">
         <v>8</v>
@@ -37913,7 +37913,7 @@
         <v>4.36499977111816</v>
       </c>
       <c r="G1444" t="n">
-        <v>3.14959764480591</v>
+        <v>3.14959740638733</v>
       </c>
       <c r="H1444" t="s">
         <v>8</v>
@@ -37939,7 +37939,7 @@
         <v>4.37400007247925</v>
       </c>
       <c r="G1445" t="n">
-        <v>3.1560914516449</v>
+        <v>3.15609169006348</v>
       </c>
       <c r="H1445" t="s">
         <v>8</v>
@@ -37965,7 +37965,7 @@
         <v>4.31199979782104</v>
       </c>
       <c r="G1446" t="n">
-        <v>3.11135506629944</v>
+        <v>3.11135482788086</v>
       </c>
       <c r="H1446" t="s">
         <v>8</v>
@@ -37991,7 +37991,7 @@
         <v>4.31599998474121</v>
       </c>
       <c r="G1447" t="n">
-        <v>3.11424112319946</v>
+        <v>3.11424136161804</v>
       </c>
       <c r="H1447" t="s">
         <v>8</v>
@@ -38017,7 +38017,7 @@
         <v>4.26700019836426</v>
       </c>
       <c r="G1448" t="n">
-        <v>3.07888507843018</v>
+        <v>3.0788848400116</v>
       </c>
       <c r="H1448" t="s">
         <v>8</v>
@@ -38095,7 +38095,7 @@
         <v>4.28700017929077</v>
       </c>
       <c r="G1451" t="n">
-        <v>3.09331631660461</v>
+        <v>3.09331607818604</v>
       </c>
       <c r="H1451" t="s">
         <v>8</v>
@@ -38147,7 +38147,7 @@
         <v>4.23400020599365</v>
       </c>
       <c r="G1453" t="n">
-        <v>3.05507349967957</v>
+        <v>3.05507373809814</v>
       </c>
       <c r="H1453" t="s">
         <v>8</v>
@@ -38225,7 +38225,7 @@
         <v>4.18300008773804</v>
       </c>
       <c r="G1456" t="n">
-        <v>3.0182740688324</v>
+        <v>3.01827430725098</v>
       </c>
       <c r="H1456" t="s">
         <v>8</v>
@@ -38251,7 +38251,7 @@
         <v>4.23799991607666</v>
       </c>
       <c r="G1457" t="n">
-        <v>3.05795979499817</v>
+        <v>3.05795955657959</v>
       </c>
       <c r="H1457" t="s">
         <v>8</v>
@@ -38277,7 +38277,7 @@
         <v>4.23000001907349</v>
       </c>
       <c r="G1458" t="n">
-        <v>3.05218744277954</v>
+        <v>3.05218720436096</v>
       </c>
       <c r="H1458" t="s">
         <v>8</v>
@@ -38381,7 +38381,7 @@
         <v>4.13500022888184</v>
       </c>
       <c r="G1462" t="n">
-        <v>2.98363971710205</v>
+        <v>2.98363947868347</v>
       </c>
       <c r="H1462" t="s">
         <v>8</v>
@@ -38511,7 +38511,7 @@
         <v>4.33400011062622</v>
       </c>
       <c r="G1467" t="n">
-        <v>3.1272292137146</v>
+        <v>3.12722945213318</v>
       </c>
       <c r="H1467" t="s">
         <v>8</v>
@@ -38589,7 +38589,7 @@
         <v>4.41800022125244</v>
       </c>
       <c r="G1470" t="n">
-        <v>3.18784022331238</v>
+        <v>3.1878399848938</v>
       </c>
       <c r="H1470" t="s">
         <v>8</v>
@@ -38615,7 +38615,7 @@
         <v>4.42999982833862</v>
       </c>
       <c r="G1471" t="n">
-        <v>3.19649839401245</v>
+        <v>3.19649863243103</v>
       </c>
       <c r="H1471" t="s">
         <v>8</v>
@@ -38771,7 +38771,7 @@
         <v>4.60500001907349</v>
       </c>
       <c r="G1477" t="n">
-        <v>3.32277131080627</v>
+        <v>3.32277154922485</v>
       </c>
       <c r="H1477" t="s">
         <v>8</v>
@@ -39005,7 +39005,7 @@
         <v>4.74599981307983</v>
       </c>
       <c r="G1486" t="n">
-        <v>3.42451071739197</v>
+        <v>3.42451047897339</v>
       </c>
       <c r="H1486" t="s">
         <v>8</v>
@@ -39031,7 +39031,7 @@
         <v>4.67799997329712</v>
       </c>
       <c r="G1487" t="n">
-        <v>3.37544512748718</v>
+        <v>3.3754448890686</v>
       </c>
       <c r="H1487" t="s">
         <v>8</v>
@@ -39057,7 +39057,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G1488" t="n">
-        <v>3.39131903648376</v>
+        <v>3.39131927490234</v>
       </c>
       <c r="H1488" t="s">
         <v>8</v>
@@ -39161,7 +39161,7 @@
         <v>4.67799997329712</v>
       </c>
       <c r="G1492" t="n">
-        <v>3.37544512748718</v>
+        <v>3.3754448890686</v>
       </c>
       <c r="H1492" t="s">
         <v>8</v>
@@ -39213,7 +39213,7 @@
         <v>4.65000009536743</v>
       </c>
       <c r="G1494" t="n">
-        <v>3.35524129867554</v>
+        <v>3.35524153709412</v>
       </c>
       <c r="H1494" t="s">
         <v>8</v>
@@ -39265,7 +39265,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G1496" t="n">
-        <v>3.31916332244873</v>
+        <v>3.31916308403015</v>
       </c>
       <c r="H1496" t="s">
         <v>8</v>
@@ -39421,7 +39421,7 @@
         <v>4.36999988555908</v>
       </c>
       <c r="G1502" t="n">
-        <v>3.15320515632629</v>
+        <v>3.15320539474487</v>
       </c>
       <c r="H1502" t="s">
         <v>8</v>
@@ -39525,7 +39525,7 @@
         <v>4.26700019836426</v>
       </c>
       <c r="G1506" t="n">
-        <v>3.07888507843018</v>
+        <v>3.0788848400116</v>
       </c>
       <c r="H1506" t="s">
         <v>8</v>
@@ -39603,7 +39603,7 @@
         <v>4.29899978637695</v>
       </c>
       <c r="G1509" t="n">
-        <v>3.10197448730469</v>
+        <v>3.10197472572327</v>
       </c>
       <c r="H1509" t="s">
         <v>8</v>
@@ -39629,7 +39629,7 @@
         <v>4.37599992752075</v>
       </c>
       <c r="G1510" t="n">
-        <v>3.1575345993042</v>
+        <v>3.15753483772278</v>
       </c>
       <c r="H1510" t="s">
         <v>8</v>
@@ -39681,7 +39681,7 @@
         <v>4.33400011062622</v>
       </c>
       <c r="G1512" t="n">
-        <v>3.1272292137146</v>
+        <v>3.12722945213318</v>
       </c>
       <c r="H1512" t="s">
         <v>8</v>
@@ -39785,7 +39785,7 @@
         <v>4.34200000762939</v>
       </c>
       <c r="G1516" t="n">
-        <v>3.13300180435181</v>
+        <v>3.13300204277039</v>
       </c>
       <c r="H1516" t="s">
         <v>8</v>
@@ -39863,7 +39863,7 @@
         <v>4.2649998664856</v>
       </c>
       <c r="G1519" t="n">
-        <v>3.07744169235229</v>
+        <v>3.07744193077087</v>
       </c>
       <c r="H1519" t="s">
         <v>8</v>
@@ -39889,7 +39889,7 @@
         <v>4.40199995040894</v>
       </c>
       <c r="G1520" t="n">
-        <v>3.17629504203796</v>
+        <v>3.17629528045654</v>
       </c>
       <c r="H1520" t="s">
         <v>8</v>
@@ -39915,7 +39915,7 @@
         <v>4.40199995040894</v>
       </c>
       <c r="G1521" t="n">
-        <v>3.17629504203796</v>
+        <v>3.17629528045654</v>
       </c>
       <c r="H1521" t="s">
         <v>8</v>
@@ -39941,7 +39941,7 @@
         <v>4.41400003433228</v>
       </c>
       <c r="G1522" t="n">
-        <v>3.1849536895752</v>
+        <v>3.18495392799377</v>
       </c>
       <c r="H1522" t="s">
         <v>8</v>
@@ -39967,7 +39967,7 @@
         <v>4.48099994659424</v>
       </c>
       <c r="G1523" t="n">
-        <v>3.23329830169678</v>
+        <v>3.2332980632782</v>
       </c>
       <c r="H1523" t="s">
         <v>8</v>
@@ -40071,7 +40071,7 @@
         <v>4.52799987792969</v>
       </c>
       <c r="G1527" t="n">
-        <v>3.26721143722534</v>
+        <v>3.26721119880676</v>
       </c>
       <c r="H1527" t="s">
         <v>8</v>
@@ -40123,7 +40123,7 @@
         <v>4.53599977493286</v>
       </c>
       <c r="G1529" t="n">
-        <v>3.27298378944397</v>
+        <v>3.27298402786255</v>
       </c>
       <c r="H1529" t="s">
         <v>8</v>
@@ -40149,7 +40149,7 @@
         <v>4.47399997711182</v>
       </c>
       <c r="G1530" t="n">
-        <v>3.22824692726135</v>
+        <v>3.22824716567993</v>
       </c>
       <c r="H1530" t="s">
         <v>8</v>
@@ -40175,7 +40175,7 @@
         <v>4.48600006103516</v>
       </c>
       <c r="G1531" t="n">
-        <v>3.23690581321716</v>
+        <v>3.23690605163574</v>
       </c>
       <c r="H1531" t="s">
         <v>8</v>
@@ -40201,7 +40201,7 @@
         <v>4.5019998550415</v>
       </c>
       <c r="G1532" t="n">
-        <v>3.248450756073</v>
+        <v>3.24845099449158</v>
       </c>
       <c r="H1532" t="s">
         <v>8</v>
@@ -40383,7 +40383,7 @@
         <v>4.5019998550415</v>
       </c>
       <c r="G1539" t="n">
-        <v>3.248450756073</v>
+        <v>3.24845099449158</v>
       </c>
       <c r="H1539" t="s">
         <v>8</v>
@@ -40409,7 +40409,7 @@
         <v>4.54099988937378</v>
       </c>
       <c r="G1540" t="n">
-        <v>3.27659153938293</v>
+        <v>3.27659130096436</v>
       </c>
       <c r="H1540" t="s">
         <v>8</v>
@@ -40435,7 +40435,7 @@
         <v>4.5</v>
       </c>
       <c r="G1541" t="n">
-        <v>3.24700784683228</v>
+        <v>3.2470076084137</v>
       </c>
       <c r="H1541" t="s">
         <v>8</v>
@@ -40461,7 +40461,7 @@
         <v>4.31699991226196</v>
       </c>
       <c r="G1542" t="n">
-        <v>3.1149628162384</v>
+        <v>3.11496257781982</v>
       </c>
       <c r="H1542" t="s">
         <v>8</v>
@@ -40487,7 +40487,7 @@
         <v>4.28700017929077</v>
       </c>
       <c r="G1543" t="n">
-        <v>3.09331631660461</v>
+        <v>3.09331607818604</v>
       </c>
       <c r="H1543" t="s">
         <v>8</v>
@@ -40539,7 +40539,7 @@
         <v>4.3899998664856</v>
       </c>
       <c r="G1545" t="n">
-        <v>3.16763663291931</v>
+        <v>3.16763639450073</v>
       </c>
       <c r="H1545" t="s">
         <v>8</v>
@@ -40565,7 +40565,7 @@
         <v>4.39599990844727</v>
       </c>
       <c r="G1546" t="n">
-        <v>3.17196559906006</v>
+        <v>3.17196583747864</v>
       </c>
       <c r="H1546" t="s">
         <v>8</v>
@@ -40617,7 +40617,7 @@
         <v>4.48199987411499</v>
       </c>
       <c r="G1548" t="n">
-        <v>3.23401951789856</v>
+        <v>3.23401975631714</v>
       </c>
       <c r="H1548" t="s">
         <v>8</v>
@@ -40643,7 +40643,7 @@
         <v>4.48600006103516</v>
       </c>
       <c r="G1549" t="n">
-        <v>3.23690581321716</v>
+        <v>3.23690605163574</v>
       </c>
       <c r="H1549" t="s">
         <v>8</v>
@@ -40669,7 +40669,7 @@
         <v>4.49200010299683</v>
       </c>
       <c r="G1550" t="n">
-        <v>3.24123525619507</v>
+        <v>3.24123549461365</v>
       </c>
       <c r="H1550" t="s">
         <v>8</v>
@@ -40747,7 +40747,7 @@
         <v>4.40199995040894</v>
       </c>
       <c r="G1553" t="n">
-        <v>3.17629504203796</v>
+        <v>3.17629528045654</v>
       </c>
       <c r="H1553" t="s">
         <v>8</v>
@@ -40825,7 +40825,7 @@
         <v>4.83900022506714</v>
       </c>
       <c r="G1556" t="n">
-        <v>3.49161601066589</v>
+        <v>3.49161577224731</v>
       </c>
       <c r="H1556" t="s">
         <v>8</v>
@@ -40903,7 +40903,7 @@
         <v>4.82800006866455</v>
       </c>
       <c r="G1559" t="n">
-        <v>3.48367857933044</v>
+        <v>3.48367834091187</v>
       </c>
       <c r="H1559" t="s">
         <v>8</v>
@@ -40929,7 +40929,7 @@
         <v>4.70900011062622</v>
       </c>
       <c r="G1560" t="n">
-        <v>3.39781355857849</v>
+        <v>3.39781332015991</v>
       </c>
       <c r="H1560" t="s">
         <v>8</v>
@@ -41033,7 +41033,7 @@
         <v>4.65000009536743</v>
       </c>
       <c r="G1564" t="n">
-        <v>3.35524129867554</v>
+        <v>3.35524153709412</v>
       </c>
       <c r="H1564" t="s">
         <v>8</v>
@@ -41059,7 +41059,7 @@
         <v>4.35500001907349</v>
       </c>
       <c r="G1565" t="n">
-        <v>3.14238238334656</v>
+        <v>3.14238214492798</v>
       </c>
       <c r="H1565" t="s">
         <v>8</v>
@@ -41111,7 +41111,7 @@
         <v>4.23000001907349</v>
       </c>
       <c r="G1567" t="n">
-        <v>3.05218744277954</v>
+        <v>3.05218720436096</v>
       </c>
       <c r="H1567" t="s">
         <v>8</v>
@@ -41137,7 +41137,7 @@
         <v>4.07200002670288</v>
       </c>
       <c r="G1568" t="n">
-        <v>2.93818140029907</v>
+        <v>2.93818116188049</v>
       </c>
       <c r="H1568" t="s">
         <v>8</v>
@@ -41163,7 +41163,7 @@
         <v>3.94300007820129</v>
       </c>
       <c r="G1569" t="n">
-        <v>2.84510040283203</v>
+        <v>2.84510064125061</v>
       </c>
       <c r="H1569" t="s">
         <v>8</v>
@@ -41215,7 +41215,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G1571" t="n">
-        <v>2.44607949256897</v>
+        <v>2.44607925415039</v>
       </c>
       <c r="H1571" t="s">
         <v>8</v>
@@ -41241,7 +41241,7 @@
         <v>3.34500002861023</v>
       </c>
       <c r="G1572" t="n">
-        <v>2.41360926628113</v>
+        <v>2.41360902786255</v>
       </c>
       <c r="H1572" t="s">
         <v>8</v>
@@ -41267,7 +41267,7 @@
         <v>3.40700006484985</v>
       </c>
       <c r="G1573" t="n">
-        <v>2.45834565162659</v>
+        <v>2.45834589004517</v>
       </c>
       <c r="H1573" t="s">
         <v>8</v>
@@ -41371,7 +41371,7 @@
         <v>3.77500009536743</v>
       </c>
       <c r="G1577" t="n">
-        <v>2.72387862205505</v>
+        <v>2.72387886047363</v>
       </c>
       <c r="H1577" t="s">
         <v>8</v>
@@ -41397,7 +41397,7 @@
         <v>3.75</v>
       </c>
       <c r="G1578" t="n">
-        <v>2.70583963394165</v>
+        <v>2.70583987236023</v>
       </c>
       <c r="H1578" t="s">
         <v>8</v>
@@ -41423,7 +41423,7 @@
         <v>3.96199989318848</v>
       </c>
       <c r="G1579" t="n">
-        <v>2.85880994796753</v>
+        <v>2.85880970954895</v>
       </c>
       <c r="H1579" t="s">
         <v>8</v>
@@ -41475,7 +41475,7 @@
         <v>3.93700003623962</v>
       </c>
       <c r="G1581" t="n">
-        <v>2.84077095985413</v>
+        <v>2.84077119827271</v>
       </c>
       <c r="H1581" t="s">
         <v>8</v>
@@ -41501,7 +41501,7 @@
         <v>3.94199991226196</v>
       </c>
       <c r="G1582" t="n">
-        <v>2.84437870979309</v>
+        <v>2.84437847137451</v>
       </c>
       <c r="H1582" t="s">
         <v>8</v>
@@ -41579,7 +41579,7 @@
         <v>3.99300003051758</v>
       </c>
       <c r="G1585" t="n">
-        <v>2.88117814064026</v>
+        <v>2.88117837905884</v>
       </c>
       <c r="H1585" t="s">
         <v>8</v>
@@ -41631,7 +41631,7 @@
         <v>4.0310001373291</v>
       </c>
       <c r="G1587" t="n">
-        <v>2.90859746932983</v>
+        <v>2.90859770774841</v>
       </c>
       <c r="H1587" t="s">
         <v>8</v>
@@ -41657,7 +41657,7 @@
         <v>4.16800022125244</v>
       </c>
       <c r="G1588" t="n">
-        <v>3.0074508190155</v>
+        <v>3.00745105743408</v>
       </c>
       <c r="H1588" t="s">
         <v>8</v>
@@ -41761,7 +41761,7 @@
         <v>4.12200021743774</v>
       </c>
       <c r="G1592" t="n">
-        <v>2.9742591381073</v>
+        <v>2.97425889968872</v>
       </c>
       <c r="H1592" t="s">
         <v>8</v>
@@ -41813,7 +41813,7 @@
         <v>3.96199989318848</v>
       </c>
       <c r="G1594" t="n">
-        <v>2.85880994796753</v>
+        <v>2.85880970954895</v>
       </c>
       <c r="H1594" t="s">
         <v>8</v>
@@ -42021,7 +42021,7 @@
         <v>4.54400014877319</v>
       </c>
       <c r="G1602" t="n">
-        <v>3.27875638008118</v>
+        <v>3.2787561416626</v>
       </c>
       <c r="H1602" t="s">
         <v>8</v>
@@ -42099,7 +42099,7 @@
         <v>4.53999996185303</v>
       </c>
       <c r="G1605" t="n">
-        <v>3.27587032318115</v>
+        <v>3.27587008476257</v>
       </c>
       <c r="H1605" t="s">
         <v>8</v>
@@ -42125,7 +42125,7 @@
         <v>4.63000011444092</v>
       </c>
       <c r="G1606" t="n">
-        <v>3.34081029891968</v>
+        <v>3.34081053733826</v>
       </c>
       <c r="H1606" t="s">
         <v>8</v>
@@ -42281,7 +42281,7 @@
         <v>4.52799987792969</v>
       </c>
       <c r="G1612" t="n">
-        <v>3.26721143722534</v>
+        <v>3.26721119880676</v>
       </c>
       <c r="H1612" t="s">
         <v>8</v>
@@ -42307,7 +42307,7 @@
         <v>4.32999992370605</v>
       </c>
       <c r="G1613" t="n">
-        <v>3.12434339523315</v>
+        <v>3.12434315681458</v>
       </c>
       <c r="H1613" t="s">
         <v>8</v>
@@ -42385,7 +42385,7 @@
         <v>4.35200023651123</v>
       </c>
       <c r="G1616" t="n">
-        <v>3.14021730422974</v>
+        <v>3.14021754264832</v>
       </c>
       <c r="H1616" t="s">
         <v>8</v>
@@ -42411,7 +42411,7 @@
         <v>4.46199989318848</v>
       </c>
       <c r="G1617" t="n">
-        <v>3.21958827972412</v>
+        <v>3.2195885181427</v>
       </c>
       <c r="H1617" t="s">
         <v>8</v>
@@ -42489,7 +42489,7 @@
         <v>4.57000017166138</v>
       </c>
       <c r="G1620" t="n">
-        <v>3.29751682281494</v>
+        <v>3.29751706123352</v>
       </c>
       <c r="H1620" t="s">
         <v>8</v>
@@ -42567,7 +42567,7 @@
         <v>4.48199987411499</v>
       </c>
       <c r="G1623" t="n">
-        <v>3.23401951789856</v>
+        <v>3.23401975631714</v>
       </c>
       <c r="H1623" t="s">
         <v>8</v>
@@ -42697,7 +42697,7 @@
         <v>4.48400020599365</v>
       </c>
       <c r="G1628" t="n">
-        <v>3.44912552833557</v>
+        <v>3.44912576675415</v>
       </c>
       <c r="H1628" t="s">
         <v>8</v>
@@ -42723,7 +42723,7 @@
         <v>4.47599983215332</v>
       </c>
       <c r="G1629" t="n">
-        <v>3.44297170639038</v>
+        <v>3.44297194480896</v>
       </c>
       <c r="H1629" t="s">
         <v>8</v>
@@ -42931,7 +42931,7 @@
         <v>4.20599985122681</v>
       </c>
       <c r="G1637" t="n">
-        <v>3.23528599739075</v>
+        <v>3.23528575897217</v>
       </c>
       <c r="H1637" t="s">
         <v>8</v>
@@ -42983,7 +42983,7 @@
         <v>3.7739999294281</v>
       </c>
       <c r="G1639" t="n">
-        <v>2.90298819541931</v>
+        <v>2.90298843383789</v>
       </c>
       <c r="H1639" t="s">
         <v>8</v>
@@ -43009,7 +43009,7 @@
         <v>3.59400010108948</v>
       </c>
       <c r="G1640" t="n">
-        <v>2.7645308971405</v>
+        <v>2.76453113555908</v>
       </c>
       <c r="H1640" t="s">
         <v>8</v>
@@ -43035,7 +43035,7 @@
         <v>3.64599990844727</v>
       </c>
       <c r="G1641" t="n">
-        <v>2.80452990531921</v>
+        <v>2.80452966690063</v>
       </c>
       <c r="H1641" t="s">
         <v>8</v>
@@ -43113,7 +43113,7 @@
         <v>3.58200001716614</v>
       </c>
       <c r="G1644" t="n">
-        <v>2.75530052185059</v>
+        <v>2.75530076026917</v>
       </c>
       <c r="H1644" t="s">
         <v>8</v>
@@ -43217,7 +43217,7 @@
         <v>3.57599997520447</v>
       </c>
       <c r="G1648" t="n">
-        <v>2.75068521499634</v>
+        <v>2.75068545341492</v>
       </c>
       <c r="H1648" t="s">
         <v>8</v>
@@ -43373,7 +43373,7 @@
         <v>3.50600004196167</v>
       </c>
       <c r="G1654" t="n">
-        <v>2.69684100151062</v>
+        <v>2.69684076309204</v>
       </c>
       <c r="H1654" t="s">
         <v>8</v>
@@ -43425,7 +43425,7 @@
         <v>3.25600004196167</v>
       </c>
       <c r="G1656" t="n">
-        <v>2.50453925132751</v>
+        <v>2.50453901290894</v>
       </c>
       <c r="H1656" t="s">
         <v>8</v>
@@ -43451,7 +43451,7 @@
         <v>3.21000003814697</v>
       </c>
       <c r="G1657" t="n">
-        <v>2.46915555000305</v>
+        <v>2.46915578842163</v>
       </c>
       <c r="H1657" t="s">
         <v>8</v>
@@ -43503,7 +43503,7 @@
         <v>3.38599991798401</v>
       </c>
       <c r="G1659" t="n">
-        <v>2.60453581809998</v>
+        <v>2.60453605651855</v>
       </c>
       <c r="H1659" t="s">
         <v>8</v>
@@ -43555,7 +43555,7 @@
         <v>3.26799988746643</v>
       </c>
       <c r="G1661" t="n">
-        <v>2.51376938819885</v>
+        <v>2.51376914978027</v>
       </c>
       <c r="H1661" t="s">
         <v>8</v>
@@ -43581,7 +43581,7 @@
         <v>3.25</v>
       </c>
       <c r="G1662" t="n">
-        <v>2.49992370605469</v>
+        <v>2.49992394447327</v>
       </c>
       <c r="H1662" t="s">
         <v>8</v>
@@ -43659,7 +43659,7 @@
         <v>3.27600002288818</v>
       </c>
       <c r="G1665" t="n">
-        <v>2.51992321014404</v>
+        <v>2.51992297172546</v>
       </c>
       <c r="H1665" t="s">
         <v>8</v>
@@ -43763,7 +43763,7 @@
         <v>3.37400007247925</v>
       </c>
       <c r="G1669" t="n">
-        <v>2.59530544281006</v>
+        <v>2.59530568122864</v>
       </c>
       <c r="H1669" t="s">
         <v>8</v>
@@ -43789,7 +43789,7 @@
         <v>3.34200000762939</v>
       </c>
       <c r="G1670" t="n">
-        <v>2.57069063186646</v>
+        <v>2.57069087028503</v>
       </c>
       <c r="H1670" t="s">
         <v>8</v>
@@ -43815,7 +43815,7 @@
         <v>3.28200006484985</v>
       </c>
       <c r="G1671" t="n">
-        <v>2.52453851699829</v>
+        <v>2.52453827857971</v>
       </c>
       <c r="H1671" t="s">
         <v>8</v>
@@ -43841,7 +43841,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G1672" t="n">
-        <v>2.52300000190735</v>
+        <v>2.52299976348877</v>
       </c>
       <c r="H1672" t="s">
         <v>8</v>
@@ -43893,7 +43893,7 @@
         <v>3.41799998283386</v>
       </c>
       <c r="G1674" t="n">
-        <v>2.62915062904358</v>
+        <v>2.629150390625</v>
       </c>
       <c r="H1674" t="s">
         <v>8</v>
@@ -43997,7 +43997,7 @@
         <v>3.58999991416931</v>
       </c>
       <c r="G1678" t="n">
-        <v>2.7614541053772</v>
+        <v>2.76145434379578</v>
       </c>
       <c r="H1678" t="s">
         <v>8</v>
@@ -44127,7 +44127,7 @@
         <v>3.53800010681152</v>
       </c>
       <c r="G1683" t="n">
-        <v>2.72145557403564</v>
+        <v>2.72145581245422</v>
       </c>
       <c r="H1683" t="s">
         <v>8</v>
@@ -44153,7 +44153,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G1684" t="n">
-        <v>2.76914620399475</v>
+        <v>2.76914596557617</v>
       </c>
       <c r="H1684" t="s">
         <v>8</v>
@@ -44283,7 +44283,7 @@
         <v>3.33200001716614</v>
       </c>
       <c r="G1689" t="n">
-        <v>2.56299877166748</v>
+        <v>2.56299901008606</v>
       </c>
       <c r="H1689" t="s">
         <v>8</v>
@@ -44309,7 +44309,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G1690" t="n">
-        <v>2.59992074966431</v>
+        <v>2.59992098808289</v>
       </c>
       <c r="H1690" t="s">
         <v>8</v>
@@ -44335,7 +44335,7 @@
         <v>3.36199998855591</v>
       </c>
       <c r="G1691" t="n">
-        <v>2.58607506752014</v>
+        <v>2.58607482910156</v>
       </c>
       <c r="H1691" t="s">
         <v>8</v>
@@ -44387,7 +44387,7 @@
         <v>3.26799988746643</v>
       </c>
       <c r="G1693" t="n">
-        <v>2.51376938819885</v>
+        <v>2.51376914978027</v>
       </c>
       <c r="H1693" t="s">
         <v>8</v>
@@ -44491,7 +44491,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G1697" t="n">
-        <v>2.52300000190735</v>
+        <v>2.52299976348877</v>
       </c>
       <c r="H1697" t="s">
         <v>8</v>
@@ -44517,7 +44517,7 @@
         <v>3.39599990844727</v>
       </c>
       <c r="G1698" t="n">
-        <v>2.61222815513611</v>
+        <v>2.61222791671753</v>
       </c>
       <c r="H1698" t="s">
         <v>8</v>
@@ -44543,7 +44543,7 @@
         <v>3.24399995803833</v>
       </c>
       <c r="G1699" t="n">
-        <v>2.49530863761902</v>
+        <v>2.49530839920044</v>
       </c>
       <c r="H1699" t="s">
         <v>8</v>
@@ -44595,7 +44595,7 @@
         <v>3.19000005722046</v>
       </c>
       <c r="G1701" t="n">
-        <v>2.45377111434937</v>
+        <v>2.45377135276794</v>
       </c>
       <c r="H1701" t="s">
         <v>8</v>
@@ -44647,7 +44647,7 @@
         <v>3.29800009727478</v>
       </c>
       <c r="G1703" t="n">
-        <v>2.53684568405151</v>
+        <v>2.53684592247009</v>
       </c>
       <c r="H1703" t="s">
         <v>8</v>
@@ -44699,7 +44699,7 @@
         <v>3.37599992752075</v>
       </c>
       <c r="G1705" t="n">
-        <v>2.59684348106384</v>
+        <v>2.59684371948242</v>
       </c>
       <c r="H1705" t="s">
         <v>8</v>
@@ -44725,7 +44725,7 @@
         <v>3.33400011062622</v>
       </c>
       <c r="G1706" t="n">
-        <v>2.56453704833984</v>
+        <v>2.56453728675842</v>
       </c>
       <c r="H1706" t="s">
         <v>8</v>
@@ -44777,7 +44777,7 @@
         <v>3.25</v>
       </c>
       <c r="G1708" t="n">
-        <v>2.49992370605469</v>
+        <v>2.49992394447327</v>
       </c>
       <c r="H1708" t="s">
         <v>8</v>
@@ -44881,7 +44881,7 @@
         <v>3.11199998855591</v>
       </c>
       <c r="G1712" t="n">
-        <v>2.39377331733704</v>
+        <v>2.39377307891846</v>
       </c>
       <c r="H1712" t="s">
         <v>8</v>
@@ -44933,7 +44933,7 @@
         <v>3.06200003623962</v>
       </c>
       <c r="G1714" t="n">
-        <v>2.35531258583069</v>
+        <v>2.35531282424927</v>
       </c>
       <c r="H1714" t="s">
         <v>8</v>
@@ -44985,7 +44985,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G1716" t="n">
-        <v>2.26916170120239</v>
+        <v>2.26916146278381</v>
       </c>
       <c r="H1716" t="s">
         <v>8</v>
@@ -45011,7 +45011,7 @@
         <v>2.86400008201599</v>
       </c>
       <c r="G1717" t="n">
-        <v>2.20300960540771</v>
+        <v>2.20300984382629</v>
       </c>
       <c r="H1717" t="s">
         <v>8</v>
@@ -45063,7 +45063,7 @@
         <v>3.06200003623962</v>
       </c>
       <c r="G1719" t="n">
-        <v>2.35531258583069</v>
+        <v>2.35531282424927</v>
       </c>
       <c r="H1719" t="s">
         <v>8</v>
@@ -45219,7 +45219,7 @@
         <v>3.04800009727478</v>
       </c>
       <c r="G1725" t="n">
-        <v>2.34454417228699</v>
+        <v>2.34454393386841</v>
       </c>
       <c r="H1725" t="s">
         <v>8</v>
@@ -45271,7 +45271,7 @@
         <v>3.00200009346008</v>
       </c>
       <c r="G1727" t="n">
-        <v>2.30916047096252</v>
+        <v>2.30916023254395</v>
       </c>
       <c r="H1727" t="s">
         <v>8</v>
@@ -45297,7 +45297,7 @@
         <v>2.99600005149841</v>
       </c>
       <c r="G1728" t="n">
-        <v>2.30454516410828</v>
+        <v>2.3045449256897</v>
       </c>
       <c r="H1728" t="s">
         <v>8</v>
@@ -45427,7 +45427,7 @@
         <v>3.00399994850159</v>
       </c>
       <c r="G1733" t="n">
-        <v>2.31069874763489</v>
+        <v>2.31069850921631</v>
       </c>
       <c r="H1733" t="s">
         <v>8</v>
@@ -45609,7 +45609,7 @@
         <v>3.15599989891052</v>
       </c>
       <c r="G1740" t="n">
-        <v>2.4276180267334</v>
+        <v>2.42761826515198</v>
       </c>
       <c r="H1740" t="s">
         <v>8</v>
@@ -45739,7 +45739,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G1745" t="n">
-        <v>2.64607310295105</v>
+        <v>2.64607334136963</v>
       </c>
       <c r="H1745" t="s">
         <v>8</v>
@@ -45791,7 +45791,7 @@
         <v>3.56599998474121</v>
       </c>
       <c r="G1747" t="n">
-        <v>2.74299335479736</v>
+        <v>2.74299311637878</v>
       </c>
       <c r="H1747" t="s">
         <v>8</v>
@@ -45817,7 +45817,7 @@
         <v>3.64599990844727</v>
       </c>
       <c r="G1748" t="n">
-        <v>2.80452990531921</v>
+        <v>2.80452966690063</v>
       </c>
       <c r="H1748" t="s">
         <v>8</v>
@@ -45973,7 +45973,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G1754" t="n">
-        <v>2.76914620399475</v>
+        <v>2.76914596557617</v>
       </c>
       <c r="H1754" t="s">
         <v>8</v>
@@ -46051,7 +46051,7 @@
         <v>3.57599997520447</v>
       </c>
       <c r="G1757" t="n">
-        <v>2.75068521499634</v>
+        <v>2.75068545341492</v>
       </c>
       <c r="H1757" t="s">
         <v>8</v>
@@ -46077,7 +46077,7 @@
         <v>3.58999991416931</v>
       </c>
       <c r="G1758" t="n">
-        <v>2.7614541053772</v>
+        <v>2.76145434379578</v>
       </c>
       <c r="H1758" t="s">
         <v>8</v>
@@ -46129,7 +46129,7 @@
         <v>3.62400007247925</v>
       </c>
       <c r="G1760" t="n">
-        <v>2.78760719299316</v>
+        <v>2.78760743141174</v>
       </c>
       <c r="H1760" t="s">
         <v>8</v>
@@ -46155,7 +46155,7 @@
         <v>3.63199996948242</v>
       </c>
       <c r="G1761" t="n">
-        <v>2.79376077651978</v>
+        <v>2.79376101493835</v>
       </c>
       <c r="H1761" t="s">
         <v>8</v>
@@ -46311,7 +46311,7 @@
         <v>3.66400003433228</v>
       </c>
       <c r="G1767" t="n">
-        <v>2.81837558746338</v>
+        <v>2.81837582588196</v>
       </c>
       <c r="H1767" t="s">
         <v>8</v>
@@ -46519,7 +46519,7 @@
         <v>3.5</v>
       </c>
       <c r="G1775" t="n">
-        <v>2.69222569465637</v>
+        <v>2.69222545623779</v>
       </c>
       <c r="H1775" t="s">
         <v>8</v>
@@ -46571,7 +46571,7 @@
         <v>3.62400007247925</v>
       </c>
       <c r="G1777" t="n">
-        <v>2.78760719299316</v>
+        <v>2.78760743141174</v>
       </c>
       <c r="H1777" t="s">
         <v>8</v>
@@ -46623,7 +46623,7 @@
         <v>3.66599988937378</v>
       </c>
       <c r="G1779" t="n">
-        <v>2.81991362571716</v>
+        <v>2.81991386413574</v>
       </c>
       <c r="H1779" t="s">
         <v>8</v>
@@ -46675,7 +46675,7 @@
         <v>3.71600008010864</v>
       </c>
       <c r="G1781" t="n">
-        <v>2.85837459564209</v>
+        <v>2.85837435722351</v>
       </c>
       <c r="H1781" t="s">
         <v>8</v>
@@ -46727,7 +46727,7 @@
         <v>3.7739999294281</v>
       </c>
       <c r="G1783" t="n">
-        <v>2.90298819541931</v>
+        <v>2.90298843383789</v>
       </c>
       <c r="H1783" t="s">
         <v>8</v>
@@ -46753,7 +46753,7 @@
         <v>3.78800010681152</v>
       </c>
       <c r="G1784" t="n">
-        <v>2.91375756263733</v>
+        <v>2.91375732421875</v>
       </c>
       <c r="H1784" t="s">
         <v>8</v>
@@ -46779,7 +46779,7 @@
         <v>3.85199999809265</v>
       </c>
       <c r="G1785" t="n">
-        <v>2.96298670768738</v>
+        <v>2.9629864692688</v>
       </c>
       <c r="H1785" t="s">
         <v>8</v>
@@ -46857,7 +46857,7 @@
         <v>3.92600011825562</v>
       </c>
       <c r="G1788" t="n">
-        <v>3.01990795135498</v>
+        <v>3.0199077129364</v>
       </c>
       <c r="H1788" t="s">
         <v>8</v>
@@ -46935,7 +46935,7 @@
         <v>3.93600010871887</v>
       </c>
       <c r="G1791" t="n">
-        <v>3.02760028839111</v>
+        <v>3.02760004997253</v>
       </c>
       <c r="H1791" t="s">
         <v>8</v>
@@ -47221,7 +47221,7 @@
         <v>4.01800012588501</v>
       </c>
       <c r="G1802" t="n">
-        <v>3.09067535400391</v>
+        <v>3.09067511558533</v>
       </c>
       <c r="H1802" t="s">
         <v>8</v>
@@ -47325,7 +47325,7 @@
         <v>4.15199995040894</v>
       </c>
       <c r="G1806" t="n">
-        <v>3.19374871253967</v>
+        <v>3.19374895095825</v>
       </c>
       <c r="H1806" t="s">
         <v>8</v>
@@ -47403,7 +47403,7 @@
         <v>3.97399997711182</v>
       </c>
       <c r="G1809" t="n">
-        <v>3.05682992935181</v>
+        <v>3.05682945251465</v>
       </c>
       <c r="H1809" t="s">
         <v>8</v>
@@ -47559,7 +47559,7 @@
         <v>4.17000007629395</v>
       </c>
       <c r="G1815" t="n">
-        <v>3.20759463310242</v>
+        <v>3.20759439468384</v>
       </c>
       <c r="H1815" t="s">
         <v>8</v>
@@ -47585,7 +47585,7 @@
         <v>4.16599988937378</v>
       </c>
       <c r="G1816" t="n">
-        <v>3.20451784133911</v>
+        <v>3.20451760292053</v>
       </c>
       <c r="H1816" t="s">
         <v>8</v>
@@ -47611,7 +47611,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G1817" t="n">
-        <v>3.24605464935303</v>
+        <v>3.24605488777161</v>
       </c>
       <c r="H1817" t="s">
         <v>8</v>
@@ -47663,7 +47663,7 @@
         <v>4.08599996566772</v>
       </c>
       <c r="G1819" t="n">
-        <v>3.14298129081726</v>
+        <v>3.14298105239868</v>
       </c>
       <c r="H1819" t="s">
         <v>8</v>
@@ -47689,7 +47689,7 @@
         <v>4.0019998550415</v>
       </c>
       <c r="G1820" t="n">
-        <v>3.07836747169495</v>
+        <v>3.07836771011353</v>
       </c>
       <c r="H1820" t="s">
         <v>8</v>
@@ -47741,7 +47741,7 @@
         <v>4.04400014877319</v>
       </c>
       <c r="G1822" t="n">
-        <v>3.1106743812561</v>
+        <v>3.11067461967468</v>
       </c>
       <c r="H1822" t="s">
         <v>8</v>
@@ -47767,7 +47767,7 @@
         <v>4.08199977874756</v>
       </c>
       <c r="G1823" t="n">
-        <v>3.1399040222168</v>
+        <v>3.13990378379822</v>
       </c>
       <c r="H1823" t="s">
         <v>8</v>
@@ -47871,7 +47871,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G1827" t="n">
-        <v>3.1768262386322</v>
+        <v>3.17682600021362</v>
       </c>
       <c r="H1827" t="s">
         <v>8</v>
@@ -47897,7 +47897,7 @@
         <v>4.13199996948242</v>
       </c>
       <c r="G1828" t="n">
-        <v>3.17836475372314</v>
+        <v>3.17836451530457</v>
       </c>
       <c r="H1828" t="s">
         <v>8</v>
@@ -47923,7 +47923,7 @@
         <v>4.07600021362305</v>
       </c>
       <c r="G1829" t="n">
-        <v>3.13528919219971</v>
+        <v>3.13528895378113</v>
       </c>
       <c r="H1829" t="s">
         <v>8</v>
@@ -48027,7 +48027,7 @@
         <v>3.74600005149841</v>
       </c>
       <c r="G1833" t="n">
-        <v>2.88145041465759</v>
+        <v>2.88145065307617</v>
       </c>
       <c r="H1833" t="s">
         <v>8</v>
@@ -48053,7 +48053,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G1834" t="n">
-        <v>2.90760350227356</v>
+        <v>2.90760374069214</v>
       </c>
       <c r="H1834" t="s">
         <v>8</v>
@@ -48105,7 +48105,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G1836" t="n">
-        <v>2.8076069355011</v>
+        <v>2.80760669708252</v>
       </c>
       <c r="H1836" t="s">
         <v>8</v>
@@ -48183,7 +48183,7 @@
         <v>3.83200001716614</v>
       </c>
       <c r="G1839" t="n">
-        <v>2.94760251045227</v>
+        <v>2.94760227203369</v>
       </c>
       <c r="H1839" t="s">
         <v>8</v>
@@ -48209,7 +48209,7 @@
         <v>3.78399991989136</v>
       </c>
       <c r="G1840" t="n">
-        <v>2.91068053245544</v>
+        <v>2.91068029403687</v>
       </c>
       <c r="H1840" t="s">
         <v>8</v>
@@ -48235,7 +48235,7 @@
         <v>3.75</v>
       </c>
       <c r="G1841" t="n">
-        <v>2.88452744483948</v>
+        <v>2.8845272064209</v>
       </c>
       <c r="H1841" t="s">
         <v>8</v>
@@ -48313,7 +48313,7 @@
         <v>3.63599991798401</v>
       </c>
       <c r="G1844" t="n">
-        <v>2.79683756828308</v>
+        <v>2.79683780670166</v>
       </c>
       <c r="H1844" t="s">
         <v>8</v>
@@ -48339,7 +48339,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G1845" t="n">
-        <v>2.84606695175171</v>
+        <v>2.84606719017029</v>
       </c>
       <c r="H1845" t="s">
         <v>8</v>
@@ -48365,7 +48365,7 @@
         <v>3.78399991989136</v>
       </c>
       <c r="G1846" t="n">
-        <v>2.91068053245544</v>
+        <v>2.91068029403687</v>
       </c>
       <c r="H1846" t="s">
         <v>8</v>
@@ -48391,7 +48391,7 @@
         <v>3.74600005149841</v>
       </c>
       <c r="G1847" t="n">
-        <v>2.88145041465759</v>
+        <v>2.88145065307617</v>
       </c>
       <c r="H1847" t="s">
         <v>8</v>
@@ -48417,7 +48417,7 @@
         <v>3.75399994850159</v>
       </c>
       <c r="G1848" t="n">
-        <v>2.88760447502136</v>
+        <v>2.88760423660278</v>
       </c>
       <c r="H1848" t="s">
         <v>8</v>
@@ -48469,7 +48469,7 @@
         <v>3.71199989318848</v>
       </c>
       <c r="G1850" t="n">
-        <v>2.85529732704163</v>
+        <v>2.85529756546021</v>
       </c>
       <c r="H1850" t="s">
         <v>8</v>
@@ -48573,7 +48573,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G1854" t="n">
-        <v>2.92298793792725</v>
+        <v>2.92298769950867</v>
       </c>
       <c r="H1854" t="s">
         <v>8</v>
@@ -48755,7 +48755,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G1861" t="n">
-        <v>2.96914005279541</v>
+        <v>2.96914029121399</v>
       </c>
       <c r="H1861" t="s">
         <v>8</v>
@@ -48781,7 +48781,7 @@
         <v>3.83800005912781</v>
       </c>
       <c r="G1862" t="n">
-        <v>2.95221781730652</v>
+        <v>2.95221757888794</v>
       </c>
       <c r="H1862" t="s">
         <v>8</v>
@@ -48807,7 +48807,7 @@
         <v>3.79800009727478</v>
       </c>
       <c r="G1863" t="n">
-        <v>2.9214494228363</v>
+        <v>2.92144918441772</v>
       </c>
       <c r="H1863" t="s">
         <v>8</v>
@@ -48963,7 +48963,7 @@
         <v>3.7279999256134</v>
       </c>
       <c r="G1869" t="n">
-        <v>2.86760497093201</v>
+        <v>2.86760473251343</v>
       </c>
       <c r="H1869" t="s">
         <v>8</v>
@@ -49067,7 +49067,7 @@
         <v>3.59400010108948</v>
       </c>
       <c r="G1873" t="n">
-        <v>2.7645308971405</v>
+        <v>2.76453113555908</v>
       </c>
       <c r="H1873" t="s">
         <v>8</v>
@@ -49171,7 +49171,7 @@
         <v>3.58999991416931</v>
       </c>
       <c r="G1877" t="n">
-        <v>2.7614541053772</v>
+        <v>2.76145434379578</v>
       </c>
       <c r="H1877" t="s">
         <v>8</v>
@@ -49197,7 +49197,7 @@
         <v>3.63599991798401</v>
       </c>
       <c r="G1878" t="n">
-        <v>2.79683756828308</v>
+        <v>2.79683780670166</v>
       </c>
       <c r="H1878" t="s">
         <v>8</v>
@@ -49223,7 +49223,7 @@
         <v>3.68199992179871</v>
       </c>
       <c r="G1879" t="n">
-        <v>2.83222150802612</v>
+        <v>2.83222126960754</v>
       </c>
       <c r="H1879" t="s">
         <v>8</v>
@@ -71274,6 +71274,32 @@
         <v>7.07000017166138</v>
       </c>
       <c r="H2727" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2728">
+      <c r="A2728" s="1" t="n">
+        <v>46289.2916666667</v>
+      </c>
+      <c r="B2728" t="n">
+        <v>188883</v>
+      </c>
+      <c r="C2728" t="n">
+        <v>7.15999984741211</v>
+      </c>
+      <c r="D2728" t="n">
+        <v>7</v>
+      </c>
+      <c r="E2728" t="n">
+        <v>7.11999988555908</v>
+      </c>
+      <c r="F2728" t="n">
+        <v>7.13000011444092</v>
+      </c>
+      <c r="G2728" t="n">
+        <v>7.13000011444092</v>
+      </c>
+      <c r="H2728" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/ANIM.MI.xlsx
+++ b/data/ANIM.MI.xlsx
@@ -63270,8 +63270,31 @@
       <c r="E2735" t="n">
         <v>7.09999990463257</v>
       </c>
-      <c r="F2735"/>
+      <c r="F2735" t="n">
+        <v>7.32000017166138</v>
+      </c>
       <c r="G2735" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2736">
+      <c r="A2736" s="1" t="n">
+        <v>46301.2916666667</v>
+      </c>
+      <c r="B2736" t="n">
+        <v>751069</v>
+      </c>
+      <c r="C2736" t="n">
+        <v>7.48999977111816</v>
+      </c>
+      <c r="D2736" t="n">
+        <v>7.26000022888184</v>
+      </c>
+      <c r="E2736" t="n">
+        <v>7.26000022888184</v>
+      </c>
+      <c r="F2736"/>
+      <c r="G2736" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/ANIM.MI.xlsx
+++ b/data/ANIM.MI.xlsx
@@ -63293,8 +63293,31 @@
       <c r="E2736" t="n">
         <v>7.26000022888184</v>
       </c>
-      <c r="F2736"/>
+      <c r="F2736" t="n">
+        <v>7.46999979019165</v>
+      </c>
       <c r="G2736" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2737">
+      <c r="A2737" s="1" t="n">
+        <v>46302.2916666667</v>
+      </c>
+      <c r="B2737" t="n">
+        <v>808579</v>
+      </c>
+      <c r="C2737" t="n">
+        <v>7.67000007629395</v>
+      </c>
+      <c r="D2737" t="n">
+        <v>7.13000011444092</v>
+      </c>
+      <c r="E2737" t="n">
+        <v>7.32000017166138</v>
+      </c>
+      <c r="F2737"/>
+      <c r="G2737" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/ANIM.MI.xlsx
+++ b/data/ANIM.MI.xlsx
@@ -63316,8 +63316,31 @@
       <c r="E2737" t="n">
         <v>7.32000017166138</v>
       </c>
-      <c r="F2737"/>
+      <c r="F2737" t="n">
+        <v>7.44999980926514</v>
+      </c>
       <c r="G2737" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2738">
+      <c r="A2738" s="1" t="n">
+        <v>46303.2916666667</v>
+      </c>
+      <c r="B2738" t="n">
+        <v>408127</v>
+      </c>
+      <c r="C2738" t="n">
+        <v>7.40000009536743</v>
+      </c>
+      <c r="D2738" t="n">
+        <v>7.19999980926514</v>
+      </c>
+      <c r="E2738" t="n">
+        <v>7.40000009536743</v>
+      </c>
+      <c r="F2738"/>
+      <c r="G2738" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/ANIM.MI.xlsx
+++ b/data/ANIM.MI.xlsx
@@ -63339,8 +63339,31 @@
       <c r="E2738" t="n">
         <v>7.40000009536743</v>
       </c>
-      <c r="F2738"/>
+      <c r="F2738" t="n">
+        <v>7.23999977111816</v>
+      </c>
       <c r="G2738" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2739">
+      <c r="A2739" s="1" t="n">
+        <v>46304.2916666667</v>
+      </c>
+      <c r="B2739" t="n">
+        <v>195876</v>
+      </c>
+      <c r="C2739" t="n">
+        <v>7.34999990463257</v>
+      </c>
+      <c r="D2739" t="n">
+        <v>7.25</v>
+      </c>
+      <c r="E2739" t="n">
+        <v>7.28000020980835</v>
+      </c>
+      <c r="F2739"/>
+      <c r="G2739" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/ANIM.MI.xlsx
+++ b/data/ANIM.MI.xlsx
@@ -63369,6 +63369,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2740">
+      <c r="A2740" s="1" t="n">
+        <v>46307.2916666667</v>
+      </c>
+      <c r="B2740" t="n">
+        <v>293084</v>
+      </c>
+      <c r="C2740" t="n">
+        <v>7.48000001907349</v>
+      </c>
+      <c r="D2740" t="n">
+        <v>7.28000020980835</v>
+      </c>
+      <c r="E2740" t="n">
+        <v>7.30000019073486</v>
+      </c>
+      <c r="F2740" t="n">
+        <v>7.32000017166138</v>
+      </c>
+      <c r="G2740" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
